--- a/Design/config/CityDevConfig.xlsx
+++ b/Design/config/CityDevConfig.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$4:$K$4</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$4:$N$4</definedName>
   </definedNames>
   <calcPr calcId="162913"/>
   <extLst>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="83">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="124" uniqueCount="96">
   <si>
     <t>序列</t>
     <phoneticPr fontId="3" type="noConversion"/>
@@ -150,10 +150,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>DevAttrs</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>ArchFood</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -194,30 +190,10 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>AddMin</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>int</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>cs</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>提升最大</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>AddMax</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>int</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>加固城墙</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -350,6 +326,82 @@
   </si>
   <si>
     <t>提升士兵数量</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>DevAttr1Value</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>int[]</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>4,10</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>DevAttr2</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>DevAttr2Value</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>DevAttr3</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>DevAttr3Value</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>200,600</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>ArchPeople</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>300,800</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>1,3</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>50,250</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>3,9</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>2,6</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>-2,-5</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>6,15</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>200,500</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>DevAttr1</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>-500,-1500</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -450,7 +502,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" textRotation="255" wrapText="1"/>
@@ -465,6 +517,9 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="49" fontId="1" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -745,19 +800,22 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AG11"/>
+  <dimension ref="A1:AJ11"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9.5" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="9.5" customWidth="1"/>
-    <col min="3" max="6" width="14" customWidth="1"/>
-    <col min="7" max="7" width="7.875" customWidth="1"/>
-    <col min="8" max="8" width="8.375" customWidth="1"/>
-    <col min="9" max="10" width="14" customWidth="1"/>
-    <col min="11" max="11" width="9.5" customWidth="1"/>
+    <col min="3" max="7" width="14" customWidth="1"/>
+    <col min="8" max="8" width="13.75" customWidth="1"/>
+    <col min="9" max="9" width="14" customWidth="1"/>
+    <col min="10" max="10" width="13.75" customWidth="1"/>
+    <col min="11" max="11" width="14" customWidth="1"/>
+    <col min="12" max="12" width="13.75" customWidth="1"/>
+    <col min="13" max="13" width="14" customWidth="1"/>
+    <col min="14" max="14" width="9.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:33" ht="57" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:36" ht="57" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -768,31 +826,40 @@
         <v>10</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E1" s="3" t="s">
         <v>29</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>42</v>
+        <v>14</v>
       </c>
       <c r="H1" s="3" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="I1" s="3" t="s">
         <v>14</v>
       </c>
       <c r="J1" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="K1" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="K1" s="3" t="s">
+      <c r="L1" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="M1" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="N1" s="3" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="2" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
@@ -803,31 +870,40 @@
         <v>9</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>30</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>43</v>
+        <v>94</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>47</v>
+        <v>77</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>32</v>
+        <v>80</v>
       </c>
       <c r="J2" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="K2" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="L2" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="M2" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="K2" s="2" t="s">
+      <c r="N2" s="2" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="3" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A3" s="2" t="s">
         <v>7</v>
       </c>
@@ -844,25 +920,34 @@
         <v>3</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>44</v>
+        <v>3</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>48</v>
+        <v>78</v>
       </c>
       <c r="I3" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="J3" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="K3" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="L3" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="M3" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="J3" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="K3" s="2" t="s">
+      <c r="N3" s="2" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A4" s="2" t="s">
         <v>2</v>
       </c>
@@ -873,31 +958,40 @@
         <v>5</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>4</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>45</v>
+        <v>4</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="I4" s="2" t="s">
         <v>4</v>
       </c>
       <c r="J4" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="K4" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="L4" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="M4" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="K4" s="2" t="s">
+      <c r="N4" s="2" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="5" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A5" s="4">
         <v>21001</v>
       </c>
@@ -908,7 +1002,7 @@
         <v>27</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="E5" s="4" t="s">
         <v>22</v>
@@ -916,23 +1010,28 @@
       <c r="F5" s="4">
         <v>300</v>
       </c>
-      <c r="G5" s="4">
-        <v>4</v>
-      </c>
-      <c r="H5" s="4">
-        <v>10</v>
-      </c>
-      <c r="I5" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="J5" s="4" t="s">
+      <c r="G5" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="H5" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="I5" s="6" t="s">
+        <v>85</v>
+      </c>
+      <c r="J5" s="6" t="s">
+        <v>86</v>
+      </c>
+      <c r="K5" s="6"/>
+      <c r="L5" s="6"/>
+      <c r="M5" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="K5" s="4" t="s">
+      <c r="N5" s="4" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="6" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A6" s="4">
         <v>21002</v>
       </c>
@@ -943,68 +1042,78 @@
         <v>28</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="E6" s="4" t="s">
         <v>31</v>
       </c>
       <c r="F6" s="4">
-        <v>200</v>
-      </c>
-      <c r="G6" s="4">
-        <v>4</v>
-      </c>
-      <c r="H6" s="4">
-        <v>10</v>
-      </c>
-      <c r="I6" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="J6" s="4" t="s">
+        <v>300</v>
+      </c>
+      <c r="G6" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="H6" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="I6" s="6" t="s">
+        <v>85</v>
+      </c>
+      <c r="J6" s="6" t="s">
+        <v>86</v>
+      </c>
+      <c r="K6" s="6"/>
+      <c r="L6" s="6"/>
+      <c r="M6" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="K6" s="4" t="s">
+      <c r="N6" s="4" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="7" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A7" s="4">
         <v>21003</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="F7" s="4">
         <v>200</v>
       </c>
-      <c r="G7" s="4">
-        <v>4</v>
-      </c>
-      <c r="H7" s="4">
-        <v>10</v>
-      </c>
-      <c r="I7" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="J7" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="K7" s="4" t="s">
+      <c r="G7" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="H7" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="I7" s="6" t="s">
         <v>53</v>
       </c>
-      <c r="AF7" s="5"/>
-      <c r="AG7" s="5"/>
+      <c r="J7" s="6" t="s">
+        <v>87</v>
+      </c>
+      <c r="K7" s="6"/>
+      <c r="L7" s="6"/>
+      <c r="M7" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="N7" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="AI7" s="5"/>
+      <c r="AJ7" s="5"/>
     </row>
-    <row r="8" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A8" s="4">
         <v>21004</v>
       </c>
@@ -1012,138 +1121,154 @@
         <v>22</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="F8" s="4">
-        <v>200</v>
-      </c>
-      <c r="G8" s="4">
-        <v>4</v>
-      </c>
-      <c r="H8" s="4">
-        <v>10</v>
-      </c>
-      <c r="I8" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="J8" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="K8" s="4" t="s">
-        <v>75</v>
-      </c>
-      <c r="AF8" s="5"/>
-      <c r="AG8" s="5"/>
+        <v>150</v>
+      </c>
+      <c r="G8" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="H8" s="6" t="s">
+        <v>90</v>
+      </c>
+      <c r="I8" s="6" t="s">
+        <v>85</v>
+      </c>
+      <c r="J8" s="6" t="s">
+        <v>93</v>
+      </c>
+      <c r="K8" s="6"/>
+      <c r="L8" s="6"/>
+      <c r="M8" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="N8" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="AI8" s="5"/>
+      <c r="AJ8" s="5"/>
     </row>
-    <row r="9" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A9" s="4">
         <v>21005</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="F9" s="4">
         <v>0</v>
       </c>
-      <c r="G9" s="4">
-        <v>100</v>
-      </c>
-      <c r="H9" s="4">
-        <v>200</v>
-      </c>
-      <c r="I9" s="4" t="s">
-        <v>69</v>
-      </c>
-      <c r="J9" s="4" t="s">
-        <v>67</v>
-      </c>
-      <c r="K9" s="4" t="s">
-        <v>66</v>
+      <c r="G9" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="H9" s="6" t="s">
+        <v>88</v>
+      </c>
+      <c r="I9" s="6"/>
+      <c r="J9" s="6"/>
+      <c r="K9" s="6"/>
+      <c r="L9" s="6"/>
+      <c r="M9" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="N9" s="4" t="s">
+        <v>60</v>
       </c>
     </row>
-    <row r="10" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A10" s="4">
         <v>21006</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>72</v>
+        <v>66</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="F10" s="4">
         <v>0</v>
       </c>
-      <c r="G10" s="4">
-        <v>4</v>
-      </c>
-      <c r="H10" s="4">
-        <v>10</v>
-      </c>
-      <c r="I10" s="4" t="s">
-        <v>71</v>
-      </c>
-      <c r="J10" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="K10" s="4" t="s">
-        <v>70</v>
+      <c r="G10" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="H10" s="6" t="s">
+        <v>89</v>
+      </c>
+      <c r="I10" s="6"/>
+      <c r="J10" s="6"/>
+      <c r="K10" s="6"/>
+      <c r="L10" s="6"/>
+      <c r="M10" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="N10" s="4" t="s">
+        <v>64</v>
       </c>
     </row>
-    <row r="11" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A11" s="4">
         <v>21007</v>
       </c>
       <c r="B11" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="C11" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="D11" s="4" t="s">
         <v>76</v>
       </c>
-      <c r="C11" s="4" t="s">
-        <v>81</v>
-      </c>
-      <c r="D11" s="4" t="s">
-        <v>82</v>
-      </c>
       <c r="E11" s="4" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="F11" s="4">
-        <v>0</v>
-      </c>
-      <c r="G11" s="4">
-        <v>100</v>
-      </c>
-      <c r="H11" s="4">
-        <v>200</v>
-      </c>
-      <c r="I11" s="4" t="s">
-        <v>80</v>
-      </c>
-      <c r="J11" s="4" t="s">
-        <v>79</v>
-      </c>
-      <c r="K11" s="4" t="s">
-        <v>78</v>
+        <v>300</v>
+      </c>
+      <c r="G11" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="H11" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="I11" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="J11" s="6" t="s">
+        <v>91</v>
+      </c>
+      <c r="K11" s="6" t="s">
+        <v>85</v>
+      </c>
+      <c r="L11" s="6" t="s">
+        <v>95</v>
+      </c>
+      <c r="M11" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="N11" s="4" t="s">
+        <v>72</v>
       </c>
     </row>
   </sheetData>

--- a/Design/config/CityDevConfig.xlsx
+++ b/Design/config/CityDevConfig.xlsx
@@ -373,10 +373,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>50,250</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>3,9</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -402,6 +398,10 @@
   </si>
   <si>
     <t>-500,-1500</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>20,100</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -879,7 +879,7 @@
         <v>35</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="H2" s="2" t="s">
         <v>77</v>
@@ -1094,7 +1094,7 @@
         <v>50</v>
       </c>
       <c r="H7" s="6" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="I7" s="6" t="s">
         <v>53</v>
@@ -1136,13 +1136,13 @@
         <v>53</v>
       </c>
       <c r="H8" s="6" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="I8" s="6" t="s">
         <v>85</v>
       </c>
       <c r="J8" s="6" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="K8" s="6"/>
       <c r="L8" s="6"/>
@@ -1178,7 +1178,7 @@
         <v>63</v>
       </c>
       <c r="H9" s="6" t="s">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="I9" s="6"/>
       <c r="J9" s="6"/>
@@ -1214,7 +1214,7 @@
         <v>65</v>
       </c>
       <c r="H10" s="6" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="I10" s="6"/>
       <c r="J10" s="6"/>
@@ -1256,13 +1256,13 @@
         <v>53</v>
       </c>
       <c r="J11" s="6" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="K11" s="6" t="s">
         <v>85</v>
       </c>
       <c r="L11" s="6" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="M11" s="4" t="s">
         <v>73</v>

--- a/Design/config/CityDevConfig.xlsx
+++ b/Design/config/CityDevConfig.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="124" uniqueCount="96">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="136" uniqueCount="98">
   <si>
     <t>序列</t>
     <phoneticPr fontId="3" type="noConversion"/>
@@ -402,6 +402,14 @@
   </si>
   <si>
     <t>20,100</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>出战</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>出兵攻打敌人</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -800,7 +808,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AJ11"/>
+  <dimension ref="A1:AJ12"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9.5" bestFit="1" customWidth="1"/>
@@ -1271,6 +1279,50 @@
         <v>72</v>
       </c>
     </row>
+    <row r="12" spans="1:36" x14ac:dyDescent="0.2">
+      <c r="A12" s="4">
+        <v>21008</v>
+      </c>
+      <c r="B12" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="C12" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="D12" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="E12" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="F12" s="4">
+        <v>300</v>
+      </c>
+      <c r="G12" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="H12" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="I12" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="J12" s="6" t="s">
+        <v>90</v>
+      </c>
+      <c r="K12" s="6" t="s">
+        <v>85</v>
+      </c>
+      <c r="L12" s="6" t="s">
+        <v>94</v>
+      </c>
+      <c r="M12" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="N12" s="4" t="s">
+        <v>72</v>
+      </c>
+    </row>
   </sheetData>
   <sortState ref="A5:Q43">
     <sortCondition ref="A41"/>

--- a/Design/config/CityDevConfig.xlsx
+++ b/Design/config/CityDevConfig.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$4:$N$4</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$4:$O$4</definedName>
   </definedNames>
   <calcPr calcId="162913"/>
   <extLst>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="136" uniqueCount="98">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="142" uniqueCount="104">
   <si>
     <t>序列</t>
     <phoneticPr fontId="3" type="noConversion"/>
@@ -410,6 +410,29 @@
   </si>
   <si>
     <t>出兵攻打敌人</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Prefab</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>string</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>cs</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>CityDevNormal</t>
+  </si>
+  <si>
+    <t>CityDevBattle</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>对象</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -808,22 +831,22 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AJ12"/>
+  <dimension ref="A1:AK12"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9.5" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="9.5" customWidth="1"/>
-    <col min="3" max="7" width="14" customWidth="1"/>
-    <col min="8" max="8" width="13.75" customWidth="1"/>
-    <col min="9" max="9" width="14" customWidth="1"/>
-    <col min="10" max="10" width="13.75" customWidth="1"/>
-    <col min="11" max="11" width="14" customWidth="1"/>
-    <col min="12" max="12" width="13.75" customWidth="1"/>
-    <col min="13" max="13" width="14" customWidth="1"/>
-    <col min="14" max="14" width="9.5" customWidth="1"/>
+    <col min="3" max="8" width="14" customWidth="1"/>
+    <col min="9" max="9" width="13.75" customWidth="1"/>
+    <col min="10" max="10" width="14" customWidth="1"/>
+    <col min="11" max="11" width="13.75" customWidth="1"/>
+    <col min="12" max="12" width="14" customWidth="1"/>
+    <col min="13" max="13" width="13.75" customWidth="1"/>
+    <col min="14" max="14" width="14" customWidth="1"/>
+    <col min="15" max="15" width="9.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:36" ht="57" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:37" ht="57" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -837,37 +860,40 @@
         <v>38</v>
       </c>
       <c r="E1" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="F1" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="G1" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="H1" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="I1" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="I1" s="3" t="s">
+      <c r="J1" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="J1" s="3" t="s">
+      <c r="K1" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="K1" s="3" t="s">
+      <c r="L1" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="L1" s="3" t="s">
+      <c r="M1" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="M1" s="3" t="s">
+      <c r="N1" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="N1" s="3" t="s">
+      <c r="O1" s="3" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="2" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:37" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
@@ -881,37 +907,40 @@
         <v>39</v>
       </c>
       <c r="E2" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="F2" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="F2" s="2" t="s">
+      <c r="G2" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="G2" s="2" t="s">
+      <c r="H2" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="H2" s="2" t="s">
+      <c r="I2" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="I2" s="2" t="s">
+      <c r="J2" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="J2" s="2" t="s">
+      <c r="K2" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="K2" s="2" t="s">
+      <c r="L2" s="2" t="s">
         <v>82</v>
       </c>
-      <c r="L2" s="2" t="s">
+      <c r="M2" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="M2" s="2" t="s">
+      <c r="N2" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="N2" s="2" t="s">
+      <c r="O2" s="2" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="3" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:37" x14ac:dyDescent="0.2">
       <c r="A3" s="2" t="s">
         <v>7</v>
       </c>
@@ -925,37 +954,40 @@
         <v>25</v>
       </c>
       <c r="E3" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="F3" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="F3" s="2" t="s">
+      <c r="G3" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="G3" s="2" t="s">
+      <c r="H3" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="H3" s="2" t="s">
+      <c r="I3" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="I3" s="2" t="s">
+      <c r="J3" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="J3" s="2" t="s">
+      <c r="K3" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="K3" s="2" t="s">
+      <c r="L3" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="L3" s="2" t="s">
+      <c r="M3" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="M3" s="2" t="s">
+      <c r="N3" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="N3" s="2" t="s">
+      <c r="O3" s="2" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:37" x14ac:dyDescent="0.2">
       <c r="A4" s="2" t="s">
         <v>2</v>
       </c>
@@ -969,19 +1001,19 @@
         <v>40</v>
       </c>
       <c r="E4" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="F4" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F4" s="2" t="s">
+      <c r="G4" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="G4" s="2" t="s">
+      <c r="H4" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="H4" s="2" t="s">
+      <c r="I4" s="2" t="s">
         <v>42</v>
-      </c>
-      <c r="I4" s="2" t="s">
-        <v>4</v>
       </c>
       <c r="J4" s="2" t="s">
         <v>4</v>
@@ -993,13 +1025,16 @@
         <v>4</v>
       </c>
       <c r="M4" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="N4" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="N4" s="2" t="s">
+      <c r="O4" s="2" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="5" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:37" x14ac:dyDescent="0.2">
       <c r="A5" s="4">
         <v>21001</v>
       </c>
@@ -1013,33 +1048,36 @@
         <v>44</v>
       </c>
       <c r="E5" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="F5" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="F5" s="4">
+      <c r="G5" s="4">
         <v>300</v>
       </c>
-      <c r="G5" s="4" t="s">
+      <c r="H5" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="H5" s="6" t="s">
+      <c r="I5" s="6" t="s">
         <v>79</v>
       </c>
-      <c r="I5" s="6" t="s">
+      <c r="J5" s="6" t="s">
         <v>85</v>
       </c>
-      <c r="J5" s="6" t="s">
+      <c r="K5" s="6" t="s">
         <v>86</v>
       </c>
-      <c r="K5" s="6"/>
       <c r="L5" s="6"/>
-      <c r="M5" s="4" t="s">
+      <c r="M5" s="6"/>
+      <c r="N5" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="N5" s="4" t="s">
+      <c r="O5" s="4" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="6" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:37" x14ac:dyDescent="0.2">
       <c r="A6" s="4">
         <v>21002</v>
       </c>
@@ -1053,33 +1091,36 @@
         <v>45</v>
       </c>
       <c r="E6" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="F6" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="F6" s="4">
+      <c r="G6" s="4">
         <v>300</v>
       </c>
-      <c r="G6" s="4" t="s">
+      <c r="H6" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="H6" s="6" t="s">
+      <c r="I6" s="6" t="s">
         <v>79</v>
       </c>
-      <c r="I6" s="6" t="s">
+      <c r="J6" s="6" t="s">
         <v>85</v>
       </c>
-      <c r="J6" s="6" t="s">
+      <c r="K6" s="6" t="s">
         <v>86</v>
       </c>
-      <c r="K6" s="6"/>
       <c r="L6" s="6"/>
-      <c r="M6" s="4" t="s">
+      <c r="M6" s="6"/>
+      <c r="N6" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="N6" s="4" t="s">
+      <c r="O6" s="4" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="7" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:37" x14ac:dyDescent="0.2">
       <c r="A7" s="4">
         <v>21003</v>
       </c>
@@ -1093,35 +1134,38 @@
         <v>46</v>
       </c>
       <c r="E7" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="F7" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="F7" s="4">
+      <c r="G7" s="4">
         <v>200</v>
       </c>
-      <c r="G7" s="4" t="s">
+      <c r="H7" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="H7" s="6" t="s">
+      <c r="I7" s="6" t="s">
         <v>91</v>
       </c>
-      <c r="I7" s="6" t="s">
+      <c r="J7" s="6" t="s">
         <v>53</v>
       </c>
-      <c r="J7" s="6" t="s">
+      <c r="K7" s="6" t="s">
         <v>87</v>
       </c>
-      <c r="K7" s="6"/>
       <c r="L7" s="6"/>
-      <c r="M7" s="4" t="s">
+      <c r="M7" s="6"/>
+      <c r="N7" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="N7" s="4" t="s">
+      <c r="O7" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="AI7" s="5"/>
       <c r="AJ7" s="5"/>
+      <c r="AK7" s="5"/>
     </row>
-    <row r="8" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:37" x14ac:dyDescent="0.2">
       <c r="A8" s="4">
         <v>21004</v>
       </c>
@@ -1135,35 +1179,38 @@
         <v>56</v>
       </c>
       <c r="E8" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="F8" s="4" t="s">
         <v>54</v>
       </c>
-      <c r="F8" s="4">
+      <c r="G8" s="4">
         <v>150</v>
       </c>
-      <c r="G8" s="4" t="s">
+      <c r="H8" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="H8" s="6" t="s">
+      <c r="I8" s="6" t="s">
         <v>89</v>
       </c>
-      <c r="I8" s="6" t="s">
+      <c r="J8" s="6" t="s">
         <v>85</v>
       </c>
-      <c r="J8" s="6" t="s">
+      <c r="K8" s="6" t="s">
         <v>92</v>
       </c>
-      <c r="K8" s="6"/>
       <c r="L8" s="6"/>
-      <c r="M8" s="4" t="s">
+      <c r="M8" s="6"/>
+      <c r="N8" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="N8" s="4" t="s">
+      <c r="O8" s="4" t="s">
         <v>69</v>
       </c>
-      <c r="AI8" s="5"/>
       <c r="AJ8" s="5"/>
+      <c r="AK8" s="5"/>
     </row>
-    <row r="9" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:37" x14ac:dyDescent="0.2">
       <c r="A9" s="4">
         <v>21005</v>
       </c>
@@ -1177,29 +1224,32 @@
         <v>59</v>
       </c>
       <c r="E9" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="F9" s="4" t="s">
         <v>62</v>
       </c>
-      <c r="F9" s="4">
+      <c r="G9" s="4">
         <v>0</v>
       </c>
-      <c r="G9" s="4" t="s">
+      <c r="H9" s="4" t="s">
         <v>63</v>
       </c>
-      <c r="H9" s="6" t="s">
+      <c r="I9" s="6" t="s">
         <v>95</v>
       </c>
-      <c r="I9" s="6"/>
       <c r="J9" s="6"/>
       <c r="K9" s="6"/>
       <c r="L9" s="6"/>
-      <c r="M9" s="4" t="s">
+      <c r="M9" s="6"/>
+      <c r="N9" s="4" t="s">
         <v>61</v>
       </c>
-      <c r="N9" s="4" t="s">
+      <c r="O9" s="4" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="10" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:37" x14ac:dyDescent="0.2">
       <c r="A10" s="4">
         <v>21006</v>
       </c>
@@ -1213,29 +1263,32 @@
         <v>67</v>
       </c>
       <c r="E10" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="F10" s="4" t="s">
         <v>68</v>
       </c>
-      <c r="F10" s="4">
+      <c r="G10" s="4">
         <v>0</v>
       </c>
-      <c r="G10" s="4" t="s">
+      <c r="H10" s="4" t="s">
         <v>65</v>
       </c>
-      <c r="H10" s="6" t="s">
+      <c r="I10" s="6" t="s">
         <v>88</v>
       </c>
-      <c r="I10" s="6"/>
       <c r="J10" s="6"/>
       <c r="K10" s="6"/>
       <c r="L10" s="6"/>
-      <c r="M10" s="4" t="s">
+      <c r="M10" s="6"/>
+      <c r="N10" s="4" t="s">
         <v>52</v>
       </c>
-      <c r="N10" s="4" t="s">
+      <c r="O10" s="4" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="11" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:37" x14ac:dyDescent="0.2">
       <c r="A11" s="4">
         <v>21007</v>
       </c>
@@ -1249,37 +1302,40 @@
         <v>76</v>
       </c>
       <c r="E11" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="F11" s="4" t="s">
         <v>71</v>
       </c>
-      <c r="F11" s="4">
+      <c r="G11" s="4">
         <v>300</v>
       </c>
-      <c r="G11" s="4" t="s">
+      <c r="H11" s="4" t="s">
         <v>74</v>
       </c>
-      <c r="H11" s="6" t="s">
+      <c r="I11" s="6" t="s">
         <v>84</v>
       </c>
-      <c r="I11" s="6" t="s">
+      <c r="J11" s="6" t="s">
         <v>53</v>
       </c>
-      <c r="J11" s="6" t="s">
+      <c r="K11" s="6" t="s">
         <v>90</v>
       </c>
-      <c r="K11" s="6" t="s">
+      <c r="L11" s="6" t="s">
         <v>85</v>
       </c>
-      <c r="L11" s="6" t="s">
+      <c r="M11" s="6" t="s">
         <v>94</v>
       </c>
-      <c r="M11" s="4" t="s">
+      <c r="N11" s="4" t="s">
         <v>73</v>
       </c>
-      <c r="N11" s="4" t="s">
+      <c r="O11" s="4" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="12" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:37" x14ac:dyDescent="0.2">
       <c r="A12" s="4">
         <v>21008</v>
       </c>
@@ -1293,33 +1349,24 @@
         <v>97</v>
       </c>
       <c r="E12" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="F12" s="4" t="s">
         <v>71</v>
       </c>
-      <c r="F12" s="4">
-        <v>300</v>
-      </c>
-      <c r="G12" s="4" t="s">
-        <v>74</v>
-      </c>
-      <c r="H12" s="6" t="s">
-        <v>84</v>
-      </c>
-      <c r="I12" s="6" t="s">
-        <v>53</v>
-      </c>
-      <c r="J12" s="6" t="s">
-        <v>90</v>
-      </c>
-      <c r="K12" s="6" t="s">
-        <v>85</v>
-      </c>
-      <c r="L12" s="6" t="s">
-        <v>94</v>
-      </c>
-      <c r="M12" s="4" t="s">
-        <v>73</v>
-      </c>
+      <c r="G12" s="4">
+        <v>0</v>
+      </c>
+      <c r="H12" s="4"/>
+      <c r="I12" s="6"/>
+      <c r="J12" s="6"/>
+      <c r="K12" s="6"/>
+      <c r="L12" s="6"/>
+      <c r="M12" s="6"/>
       <c r="N12" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="O12" s="4" t="s">
         <v>72</v>
       </c>
     </row>

--- a/Design/config/CityDevConfig.xlsx
+++ b/Design/config/CityDevConfig.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$4:$O$4</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$4:$P$4</definedName>
   </definedNames>
   <calcPr calcId="162913"/>
   <extLst>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="142" uniqueCount="104">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="146" uniqueCount="110">
   <si>
     <t>序列</t>
     <phoneticPr fontId="3" type="noConversion"/>
@@ -158,10 +158,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>消耗黄金</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>GoldCost</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -433,6 +429,34 @@
   </si>
   <si>
     <t>对象</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>人均消耗黄金</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>最大参与人数</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>HeroCount</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>int</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>cs</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>battle</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>atk.mp4</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -831,22 +855,22 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AK12"/>
+  <dimension ref="A1:AL12"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9.5" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="9.5" customWidth="1"/>
-    <col min="3" max="8" width="14" customWidth="1"/>
-    <col min="9" max="9" width="13.75" customWidth="1"/>
-    <col min="10" max="10" width="14" customWidth="1"/>
-    <col min="11" max="11" width="13.75" customWidth="1"/>
-    <col min="12" max="12" width="14" customWidth="1"/>
-    <col min="13" max="13" width="13.75" customWidth="1"/>
-    <col min="14" max="14" width="14" customWidth="1"/>
-    <col min="15" max="15" width="9.5" customWidth="1"/>
+    <col min="3" max="9" width="14" customWidth="1"/>
+    <col min="10" max="10" width="13.75" customWidth="1"/>
+    <col min="11" max="11" width="14" customWidth="1"/>
+    <col min="12" max="12" width="13.75" customWidth="1"/>
+    <col min="13" max="13" width="14" customWidth="1"/>
+    <col min="14" max="14" width="13.75" customWidth="1"/>
+    <col min="15" max="15" width="14" customWidth="1"/>
+    <col min="16" max="16" width="9.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:37" ht="57" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:38" ht="57" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -857,43 +881,46 @@
         <v>10</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="F1" s="3" t="s">
         <v>29</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>34</v>
+        <v>103</v>
       </c>
       <c r="H1" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="I1" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="I1" s="3" t="s">
-        <v>41</v>
-      </c>
       <c r="J1" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="K1" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="K1" s="3" t="s">
-        <v>41</v>
-      </c>
       <c r="L1" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="M1" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="M1" s="3" t="s">
-        <v>41</v>
-      </c>
       <c r="N1" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="O1" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="O1" s="3" t="s">
+      <c r="P1" s="3" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="2" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
@@ -904,43 +931,46 @@
         <v>9</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>30</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>93</v>
+        <v>105</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>77</v>
+        <v>92</v>
       </c>
       <c r="J2" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="K2" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="L2" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="K2" s="2" t="s">
+      <c r="M2" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="L2" s="2" t="s">
+      <c r="N2" s="2" t="s">
         <v>82</v>
       </c>
-      <c r="M2" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="N2" s="2" t="s">
+      <c r="O2" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="O2" s="2" t="s">
+      <c r="P2" s="2" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="3" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A3" s="2" t="s">
         <v>7</v>
       </c>
@@ -954,40 +984,43 @@
         <v>25</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="F3" s="2" t="s">
         <v>3</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="H3" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="I3" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="I3" s="2" t="s">
-        <v>78</v>
-      </c>
       <c r="J3" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="K3" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="K3" s="2" t="s">
-        <v>78</v>
-      </c>
       <c r="L3" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="M3" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="M3" s="2" t="s">
-        <v>78</v>
-      </c>
       <c r="N3" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="O3" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="O3" s="2" t="s">
+      <c r="P3" s="2" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A4" s="2" t="s">
         <v>2</v>
       </c>
@@ -998,25 +1031,25 @@
         <v>5</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="F4" s="2" t="s">
         <v>4</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="H4" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="I4" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="I4" s="2" t="s">
-        <v>42</v>
-      </c>
       <c r="J4" s="2" t="s">
-        <v>4</v>
+        <v>41</v>
       </c>
       <c r="K4" s="2" t="s">
         <v>4</v>
@@ -1028,13 +1061,16 @@
         <v>4</v>
       </c>
       <c r="N4" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="O4" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="O4" s="2" t="s">
+      <c r="P4" s="2" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="5" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A5" s="4">
         <v>21001</v>
       </c>
@@ -1045,10 +1081,10 @@
         <v>27</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="F5" s="4" t="s">
         <v>22</v>
@@ -1056,28 +1092,31 @@
       <c r="G5" s="4">
         <v>300</v>
       </c>
-      <c r="H5" s="4" t="s">
+      <c r="H5" s="4">
+        <v>3</v>
+      </c>
+      <c r="I5" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="I5" s="6" t="s">
-        <v>79</v>
-      </c>
       <c r="J5" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="K5" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="L5" s="6" t="s">
         <v>85</v>
       </c>
-      <c r="K5" s="6" t="s">
-        <v>86</v>
-      </c>
-      <c r="L5" s="6"/>
       <c r="M5" s="6"/>
-      <c r="N5" s="4" t="s">
+      <c r="N5" s="6"/>
+      <c r="O5" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="O5" s="4" t="s">
+      <c r="P5" s="4" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="6" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A6" s="4">
         <v>21002</v>
       </c>
@@ -1088,10 +1127,10 @@
         <v>28</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="F6" s="4" t="s">
         <v>31</v>
@@ -1099,73 +1138,79 @@
       <c r="G6" s="4">
         <v>300</v>
       </c>
-      <c r="H6" s="4" t="s">
+      <c r="H6" s="4">
+        <v>3</v>
+      </c>
+      <c r="I6" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="I6" s="6" t="s">
-        <v>79</v>
-      </c>
       <c r="J6" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="K6" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="L6" s="6" t="s">
         <v>85</v>
       </c>
-      <c r="K6" s="6" t="s">
-        <v>86</v>
-      </c>
-      <c r="L6" s="6"/>
       <c r="M6" s="6"/>
-      <c r="N6" s="4" t="s">
+      <c r="N6" s="6"/>
+      <c r="O6" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="O6" s="4" t="s">
+      <c r="P6" s="4" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="7" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A7" s="4">
         <v>21003</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="G7" s="4">
         <v>200</v>
       </c>
-      <c r="H7" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="I7" s="6" t="s">
-        <v>91</v>
+      <c r="H7" s="4">
+        <v>3</v>
+      </c>
+      <c r="I7" s="4" t="s">
+        <v>49</v>
       </c>
       <c r="J7" s="6" t="s">
-        <v>53</v>
+        <v>90</v>
       </c>
       <c r="K7" s="6" t="s">
-        <v>87</v>
-      </c>
-      <c r="L7" s="6"/>
+        <v>52</v>
+      </c>
+      <c r="L7" s="6" t="s">
+        <v>86</v>
+      </c>
       <c r="M7" s="6"/>
-      <c r="N7" s="4" t="s">
-        <v>49</v>
-      </c>
+      <c r="N7" s="6"/>
       <c r="O7" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="AJ7" s="5"/>
+        <v>48</v>
+      </c>
+      <c r="P7" s="4" t="s">
+        <v>46</v>
+      </c>
       <c r="AK7" s="5"/>
+      <c r="AL7" s="5"/>
     </row>
-    <row r="8" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A8" s="4">
         <v>21004</v>
       </c>
@@ -1173,201 +1218,216 @@
         <v>22</v>
       </c>
       <c r="C8" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="D8" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="D8" s="4" t="s">
-        <v>56</v>
-      </c>
       <c r="E8" s="4" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="G8" s="4">
         <v>150</v>
       </c>
-      <c r="H8" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="I8" s="6" t="s">
-        <v>89</v>
+      <c r="H8" s="4">
+        <v>3</v>
+      </c>
+      <c r="I8" s="4" t="s">
+        <v>52</v>
       </c>
       <c r="J8" s="6" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="K8" s="6" t="s">
-        <v>92</v>
-      </c>
-      <c r="L8" s="6"/>
+        <v>84</v>
+      </c>
+      <c r="L8" s="6" t="s">
+        <v>91</v>
+      </c>
       <c r="M8" s="6"/>
-      <c r="N8" s="4" t="s">
-        <v>48</v>
-      </c>
+      <c r="N8" s="6"/>
       <c r="O8" s="4" t="s">
-        <v>69</v>
-      </c>
-      <c r="AJ8" s="5"/>
+        <v>47</v>
+      </c>
+      <c r="P8" s="4" t="s">
+        <v>68</v>
+      </c>
       <c r="AK8" s="5"/>
+      <c r="AL8" s="5"/>
     </row>
-    <row r="9" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A9" s="4">
         <v>21005</v>
       </c>
       <c r="B9" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="C9" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="C9" s="4" t="s">
+      <c r="D9" s="4" t="s">
         <v>58</v>
       </c>
-      <c r="D9" s="4" t="s">
-        <v>59</v>
-      </c>
       <c r="E9" s="4" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="F9" s="4" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="G9" s="4">
         <v>0</v>
       </c>
-      <c r="H9" s="4" t="s">
-        <v>63</v>
-      </c>
-      <c r="I9" s="6" t="s">
-        <v>95</v>
-      </c>
-      <c r="J9" s="6"/>
+      <c r="H9" s="4">
+        <v>3</v>
+      </c>
+      <c r="I9" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="J9" s="6" t="s">
+        <v>94</v>
+      </c>
       <c r="K9" s="6"/>
       <c r="L9" s="6"/>
       <c r="M9" s="6"/>
-      <c r="N9" s="4" t="s">
-        <v>61</v>
-      </c>
+      <c r="N9" s="6"/>
       <c r="O9" s="4" t="s">
         <v>60</v>
       </c>
+      <c r="P9" s="4" t="s">
+        <v>59</v>
+      </c>
     </row>
-    <row r="10" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A10" s="4">
         <v>21006</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C10" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="D10" s="4" t="s">
         <v>66</v>
       </c>
-      <c r="D10" s="4" t="s">
+      <c r="E10" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="F10" s="4" t="s">
         <v>67</v>
-      </c>
-      <c r="E10" s="4" t="s">
-        <v>101</v>
-      </c>
-      <c r="F10" s="4" t="s">
-        <v>68</v>
       </c>
       <c r="G10" s="4">
         <v>0</v>
       </c>
-      <c r="H10" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="I10" s="6" t="s">
-        <v>88</v>
-      </c>
-      <c r="J10" s="6"/>
+      <c r="H10" s="4">
+        <v>3</v>
+      </c>
+      <c r="I10" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="J10" s="6" t="s">
+        <v>87</v>
+      </c>
       <c r="K10" s="6"/>
       <c r="L10" s="6"/>
       <c r="M10" s="6"/>
-      <c r="N10" s="4" t="s">
-        <v>52</v>
-      </c>
+      <c r="N10" s="6"/>
       <c r="O10" s="4" t="s">
-        <v>64</v>
+        <v>51</v>
+      </c>
+      <c r="P10" s="4" t="s">
+        <v>63</v>
       </c>
     </row>
-    <row r="11" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A11" s="4">
         <v>21007</v>
       </c>
       <c r="B11" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="C11" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="D11" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="E11" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="F11" s="4" t="s">
         <v>70</v>
-      </c>
-      <c r="C11" s="4" t="s">
-        <v>75</v>
-      </c>
-      <c r="D11" s="4" t="s">
-        <v>76</v>
-      </c>
-      <c r="E11" s="4" t="s">
-        <v>101</v>
-      </c>
-      <c r="F11" s="4" t="s">
-        <v>71</v>
       </c>
       <c r="G11" s="4">
         <v>300</v>
       </c>
-      <c r="H11" s="4" t="s">
-        <v>74</v>
-      </c>
-      <c r="I11" s="6" t="s">
+      <c r="H11" s="4">
+        <v>3</v>
+      </c>
+      <c r="I11" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="J11" s="6" t="s">
+        <v>83</v>
+      </c>
+      <c r="K11" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="L11" s="6" t="s">
+        <v>89</v>
+      </c>
+      <c r="M11" s="6" t="s">
         <v>84</v>
       </c>
-      <c r="J11" s="6" t="s">
-        <v>53</v>
-      </c>
-      <c r="K11" s="6" t="s">
-        <v>90</v>
-      </c>
-      <c r="L11" s="6" t="s">
-        <v>85</v>
-      </c>
-      <c r="M11" s="6" t="s">
-        <v>94</v>
-      </c>
-      <c r="N11" s="4" t="s">
-        <v>73</v>
+      <c r="N11" s="6" t="s">
+        <v>93</v>
       </c>
       <c r="O11" s="4" t="s">
         <v>72</v>
       </c>
+      <c r="P11" s="4" t="s">
+        <v>71</v>
+      </c>
     </row>
-    <row r="12" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A12" s="4">
         <v>21008</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C12" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="D12" s="4" t="s">
         <v>96</v>
       </c>
-      <c r="D12" s="4" t="s">
-        <v>97</v>
-      </c>
       <c r="E12" s="4" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="F12" s="4" t="s">
-        <v>71</v>
+        <v>108</v>
       </c>
       <c r="G12" s="4">
         <v>0</v>
       </c>
-      <c r="H12" s="4"/>
-      <c r="I12" s="6"/>
+      <c r="H12" s="4">
+        <v>10</v>
+      </c>
+      <c r="I12" s="4"/>
       <c r="J12" s="6"/>
       <c r="K12" s="6"/>
       <c r="L12" s="6"/>
       <c r="M12" s="6"/>
-      <c r="N12" s="4" t="s">
-        <v>52</v>
-      </c>
+      <c r="N12" s="6"/>
       <c r="O12" s="4" t="s">
-        <v>72</v>
+        <v>51</v>
+      </c>
+      <c r="P12" s="4" t="s">
+        <v>109</v>
       </c>
     </row>
   </sheetData>

--- a/Design/config/CityDevConfig.xlsx
+++ b/Design/config/CityDevConfig.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$4:$P$4</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$4:$Q$4</definedName>
   </definedNames>
   <calcPr calcId="162913"/>
   <extLst>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="146" uniqueCount="110">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="158" uniqueCount="118">
   <si>
     <t>序列</t>
     <phoneticPr fontId="3" type="noConversion"/>
@@ -457,6 +457,38 @@
   </si>
   <si>
     <t>atk.mp4</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>army</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>移动</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>move</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>move.mp4</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>敌人</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>FindEnemy</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>bool</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>true</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -855,22 +887,23 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AL12"/>
+  <dimension ref="A1:AM13"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9.5" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="9.5" customWidth="1"/>
-    <col min="3" max="9" width="14" customWidth="1"/>
-    <col min="10" max="10" width="13.75" customWidth="1"/>
-    <col min="11" max="11" width="14" customWidth="1"/>
-    <col min="12" max="12" width="13.75" customWidth="1"/>
-    <col min="13" max="13" width="14" customWidth="1"/>
-    <col min="14" max="14" width="13.75" customWidth="1"/>
-    <col min="15" max="15" width="14" customWidth="1"/>
-    <col min="16" max="16" width="9.5" customWidth="1"/>
+    <col min="3" max="3" width="9.125" customWidth="1"/>
+    <col min="4" max="10" width="14" customWidth="1"/>
+    <col min="11" max="11" width="13.75" customWidth="1"/>
+    <col min="12" max="12" width="14" customWidth="1"/>
+    <col min="13" max="13" width="13.75" customWidth="1"/>
+    <col min="14" max="14" width="14" customWidth="1"/>
+    <col min="15" max="15" width="13.75" customWidth="1"/>
+    <col min="16" max="16" width="14" customWidth="1"/>
+    <col min="17" max="17" width="9.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:38" ht="57" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:39" ht="57" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -887,40 +920,43 @@
         <v>102</v>
       </c>
       <c r="F1" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="G1" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="H1" s="3" t="s">
         <v>103</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="I1" s="3" t="s">
         <v>104</v>
       </c>
-      <c r="I1" s="3" t="s">
+      <c r="J1" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="J1" s="3" t="s">
+      <c r="K1" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="K1" s="3" t="s">
+      <c r="L1" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="L1" s="3" t="s">
+      <c r="M1" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="M1" s="3" t="s">
+      <c r="N1" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="N1" s="3" t="s">
+      <c r="O1" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="O1" s="3" t="s">
+      <c r="P1" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="3" t="s">
+      <c r="Q1" s="3" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="2" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
@@ -937,40 +973,43 @@
         <v>97</v>
       </c>
       <c r="F2" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="G2" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="G2" s="2" t="s">
+      <c r="H2" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="H2" s="2" t="s">
+      <c r="I2" s="2" t="s">
         <v>105</v>
       </c>
-      <c r="I2" s="2" t="s">
+      <c r="J2" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="J2" s="2" t="s">
+      <c r="K2" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="K2" s="2" t="s">
+      <c r="L2" s="2" t="s">
         <v>79</v>
       </c>
-      <c r="L2" s="2" t="s">
+      <c r="M2" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="M2" s="2" t="s">
+      <c r="N2" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="N2" s="2" t="s">
+      <c r="O2" s="2" t="s">
         <v>82</v>
       </c>
-      <c r="O2" s="2" t="s">
+      <c r="P2" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="P2" s="2" t="s">
+      <c r="Q2" s="2" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="3" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A3" s="2" t="s">
         <v>7</v>
       </c>
@@ -987,40 +1026,43 @@
         <v>98</v>
       </c>
       <c r="F3" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="G3" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="G3" s="2" t="s">
+      <c r="H3" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="H3" s="2" t="s">
+      <c r="I3" s="2" t="s">
         <v>106</v>
       </c>
-      <c r="I3" s="2" t="s">
+      <c r="J3" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="J3" s="2" t="s">
+      <c r="K3" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="K3" s="2" t="s">
+      <c r="L3" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="L3" s="2" t="s">
+      <c r="M3" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="M3" s="2" t="s">
+      <c r="N3" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="N3" s="2" t="s">
+      <c r="O3" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="O3" s="2" t="s">
+      <c r="P3" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="P3" s="2" t="s">
+      <c r="Q3" s="2" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A4" s="2" t="s">
         <v>2</v>
       </c>
@@ -1037,22 +1079,22 @@
         <v>99</v>
       </c>
       <c r="F4" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="G4" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="G4" s="2" t="s">
+      <c r="H4" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="H4" s="2" t="s">
+      <c r="I4" s="2" t="s">
         <v>107</v>
       </c>
-      <c r="I4" s="2" t="s">
+      <c r="J4" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="J4" s="2" t="s">
+      <c r="K4" s="2" t="s">
         <v>41</v>
-      </c>
-      <c r="K4" s="2" t="s">
-        <v>4</v>
       </c>
       <c r="L4" s="2" t="s">
         <v>4</v>
@@ -1064,13 +1106,16 @@
         <v>4</v>
       </c>
       <c r="O4" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="P4" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="P4" s="2" t="s">
+      <c r="Q4" s="2" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="5" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A5" s="4">
         <v>21001</v>
       </c>
@@ -1086,37 +1131,38 @@
       <c r="E5" s="4" t="s">
         <v>100</v>
       </c>
-      <c r="F5" s="4" t="s">
+      <c r="F5" s="6"/>
+      <c r="G5" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="G5" s="4">
+      <c r="H5" s="4">
         <v>300</v>
       </c>
-      <c r="H5" s="4">
+      <c r="I5" s="4">
         <v>3</v>
       </c>
-      <c r="I5" s="4" t="s">
+      <c r="J5" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="J5" s="6" t="s">
+      <c r="K5" s="6" t="s">
         <v>78</v>
       </c>
-      <c r="K5" s="6" t="s">
+      <c r="L5" s="6" t="s">
         <v>84</v>
       </c>
-      <c r="L5" s="6" t="s">
+      <c r="M5" s="6" t="s">
         <v>85</v>
       </c>
-      <c r="M5" s="6"/>
       <c r="N5" s="6"/>
-      <c r="O5" s="4" t="s">
+      <c r="O5" s="6"/>
+      <c r="P5" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="P5" s="4" t="s">
+      <c r="Q5" s="4" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="6" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A6" s="4">
         <v>21002</v>
       </c>
@@ -1132,37 +1178,38 @@
       <c r="E6" s="4" t="s">
         <v>100</v>
       </c>
-      <c r="F6" s="4" t="s">
+      <c r="F6" s="6"/>
+      <c r="G6" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="G6" s="4">
+      <c r="H6" s="4">
         <v>300</v>
       </c>
-      <c r="H6" s="4">
+      <c r="I6" s="4">
         <v>3</v>
       </c>
-      <c r="I6" s="4" t="s">
+      <c r="J6" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="J6" s="6" t="s">
+      <c r="K6" s="6" t="s">
         <v>78</v>
       </c>
-      <c r="K6" s="6" t="s">
+      <c r="L6" s="6" t="s">
         <v>84</v>
       </c>
-      <c r="L6" s="6" t="s">
+      <c r="M6" s="6" t="s">
         <v>85</v>
       </c>
-      <c r="M6" s="6"/>
       <c r="N6" s="6"/>
-      <c r="O6" s="4" t="s">
+      <c r="O6" s="6"/>
+      <c r="P6" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="P6" s="4" t="s">
+      <c r="Q6" s="4" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="7" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A7" s="4">
         <v>21003</v>
       </c>
@@ -1178,39 +1225,40 @@
       <c r="E7" s="4" t="s">
         <v>100</v>
       </c>
-      <c r="F7" s="4" t="s">
+      <c r="F7" s="6"/>
+      <c r="G7" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="G7" s="4">
+      <c r="H7" s="4">
         <v>200</v>
       </c>
-      <c r="H7" s="4">
+      <c r="I7" s="4">
         <v>3</v>
       </c>
-      <c r="I7" s="4" t="s">
+      <c r="J7" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="J7" s="6" t="s">
+      <c r="K7" s="6" t="s">
         <v>90</v>
       </c>
-      <c r="K7" s="6" t="s">
+      <c r="L7" s="6" t="s">
         <v>52</v>
       </c>
-      <c r="L7" s="6" t="s">
+      <c r="M7" s="6" t="s">
         <v>86</v>
       </c>
-      <c r="M7" s="6"/>
       <c r="N7" s="6"/>
-      <c r="O7" s="4" t="s">
+      <c r="O7" s="6"/>
+      <c r="P7" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="P7" s="4" t="s">
+      <c r="Q7" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="AK7" s="5"/>
       <c r="AL7" s="5"/>
+      <c r="AM7" s="5"/>
     </row>
-    <row r="8" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A8" s="4">
         <v>21004</v>
       </c>
@@ -1226,39 +1274,40 @@
       <c r="E8" s="4" t="s">
         <v>100</v>
       </c>
-      <c r="F8" s="4" t="s">
+      <c r="F8" s="6"/>
+      <c r="G8" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="G8" s="4">
+      <c r="H8" s="4">
         <v>150</v>
       </c>
-      <c r="H8" s="4">
+      <c r="I8" s="4">
         <v>3</v>
       </c>
-      <c r="I8" s="4" t="s">
+      <c r="J8" s="4" t="s">
         <v>52</v>
       </c>
-      <c r="J8" s="6" t="s">
+      <c r="K8" s="6" t="s">
         <v>88</v>
       </c>
-      <c r="K8" s="6" t="s">
+      <c r="L8" s="6" t="s">
         <v>84</v>
       </c>
-      <c r="L8" s="6" t="s">
+      <c r="M8" s="6" t="s">
         <v>91</v>
       </c>
-      <c r="M8" s="6"/>
       <c r="N8" s="6"/>
-      <c r="O8" s="4" t="s">
+      <c r="O8" s="6"/>
+      <c r="P8" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="P8" s="4" t="s">
+      <c r="Q8" s="4" t="s">
         <v>68</v>
       </c>
-      <c r="AK8" s="5"/>
       <c r="AL8" s="5"/>
+      <c r="AM8" s="5"/>
     </row>
-    <row r="9" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A9" s="4">
         <v>21005</v>
       </c>
@@ -1274,38 +1323,39 @@
       <c r="E9" s="4" t="s">
         <v>100</v>
       </c>
-      <c r="F9" s="4" t="s">
+      <c r="F9" s="6"/>
+      <c r="G9" s="4" t="s">
         <v>61</v>
       </c>
-      <c r="G9" s="4">
+      <c r="H9" s="4">
         <v>0</v>
       </c>
-      <c r="H9" s="4">
+      <c r="I9" s="4">
         <v>3</v>
       </c>
-      <c r="I9" s="4" t="s">
+      <c r="J9" s="4" t="s">
         <v>62</v>
       </c>
-      <c r="J9" s="6" t="s">
+      <c r="K9" s="6" t="s">
         <v>94</v>
       </c>
-      <c r="K9" s="6"/>
       <c r="L9" s="6"/>
       <c r="M9" s="6"/>
       <c r="N9" s="6"/>
-      <c r="O9" s="4" t="s">
+      <c r="O9" s="6"/>
+      <c r="P9" s="4" t="s">
         <v>60</v>
       </c>
-      <c r="P9" s="4" t="s">
+      <c r="Q9" s="4" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="10" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A10" s="4">
         <v>21006</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>69</v>
+        <v>110</v>
       </c>
       <c r="C10" s="4" t="s">
         <v>65</v>
@@ -1316,38 +1366,39 @@
       <c r="E10" s="4" t="s">
         <v>100</v>
       </c>
-      <c r="F10" s="4" t="s">
+      <c r="F10" s="6"/>
+      <c r="G10" s="4" t="s">
         <v>67</v>
       </c>
-      <c r="G10" s="4">
+      <c r="H10" s="4">
         <v>0</v>
       </c>
-      <c r="H10" s="4">
+      <c r="I10" s="4">
         <v>3</v>
       </c>
-      <c r="I10" s="4" t="s">
+      <c r="J10" s="4" t="s">
         <v>64</v>
       </c>
-      <c r="J10" s="6" t="s">
+      <c r="K10" s="6" t="s">
         <v>87</v>
       </c>
-      <c r="K10" s="6"/>
       <c r="L10" s="6"/>
       <c r="M10" s="6"/>
       <c r="N10" s="6"/>
-      <c r="O10" s="4" t="s">
+      <c r="O10" s="6"/>
+      <c r="P10" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="P10" s="4" t="s">
+      <c r="Q10" s="4" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="11" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A11" s="4">
         <v>21007</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>69</v>
+        <v>110</v>
       </c>
       <c r="C11" s="4" t="s">
         <v>74</v>
@@ -1358,46 +1409,47 @@
       <c r="E11" s="4" t="s">
         <v>100</v>
       </c>
-      <c r="F11" s="4" t="s">
+      <c r="F11" s="6"/>
+      <c r="G11" s="4" t="s">
         <v>70</v>
       </c>
-      <c r="G11" s="4">
+      <c r="H11" s="4">
         <v>300</v>
       </c>
-      <c r="H11" s="4">
+      <c r="I11" s="4">
         <v>3</v>
       </c>
-      <c r="I11" s="4" t="s">
+      <c r="J11" s="4" t="s">
         <v>73</v>
       </c>
-      <c r="J11" s="6" t="s">
+      <c r="K11" s="6" t="s">
         <v>83</v>
       </c>
-      <c r="K11" s="6" t="s">
+      <c r="L11" s="6" t="s">
         <v>52</v>
       </c>
-      <c r="L11" s="6" t="s">
+      <c r="M11" s="6" t="s">
         <v>89</v>
       </c>
-      <c r="M11" s="6" t="s">
+      <c r="N11" s="6" t="s">
         <v>84</v>
       </c>
-      <c r="N11" s="6" t="s">
+      <c r="O11" s="6" t="s">
         <v>93</v>
       </c>
-      <c r="O11" s="4" t="s">
+      <c r="P11" s="4" t="s">
         <v>72</v>
       </c>
-      <c r="P11" s="4" t="s">
+      <c r="Q11" s="4" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="12" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A12" s="4">
         <v>21008</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>69</v>
+        <v>110</v>
       </c>
       <c r="C12" s="4" t="s">
         <v>95</v>
@@ -1408,26 +1460,68 @@
       <c r="E12" s="4" t="s">
         <v>101</v>
       </c>
-      <c r="F12" s="4" t="s">
+      <c r="F12" s="6" t="s">
+        <v>117</v>
+      </c>
+      <c r="G12" s="4" t="s">
         <v>108</v>
       </c>
-      <c r="G12" s="4">
+      <c r="H12" s="4">
         <v>0</v>
       </c>
-      <c r="H12" s="4">
+      <c r="I12" s="4">
         <v>10</v>
       </c>
-      <c r="I12" s="4"/>
-      <c r="J12" s="6"/>
+      <c r="J12" s="4"/>
       <c r="K12" s="6"/>
       <c r="L12" s="6"/>
       <c r="M12" s="6"/>
       <c r="N12" s="6"/>
-      <c r="O12" s="4" t="s">
+      <c r="O12" s="6"/>
+      <c r="P12" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="P12" s="4" t="s">
+      <c r="Q12" s="4" t="s">
         <v>109</v>
+      </c>
+    </row>
+    <row r="13" spans="1:39" x14ac:dyDescent="0.2">
+      <c r="A13" s="4">
+        <v>21009</v>
+      </c>
+      <c r="B13" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="C13" s="4" t="s">
+        <v>111</v>
+      </c>
+      <c r="D13" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="E13" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="F13" s="6"/>
+      <c r="G13" s="4" t="s">
+        <v>112</v>
+      </c>
+      <c r="H13" s="4">
+        <v>0</v>
+      </c>
+      <c r="I13" s="4">
+        <v>10</v>
+      </c>
+      <c r="J13" s="4"/>
+      <c r="K13" s="6"/>
+      <c r="L13" s="6"/>
+      <c r="M13" s="6"/>
+      <c r="N13" s="6"/>
+      <c r="O13" s="6"/>
+      <c r="P13" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="Q13" s="4" t="s">
+        <v>113</v>
       </c>
     </row>
   </sheetData>

--- a/Design/config/CityDevConfig.xlsx
+++ b/Design/config/CityDevConfig.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="158" uniqueCount="118">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="158" uniqueCount="119">
   <si>
     <t>序列</t>
     <phoneticPr fontId="3" type="noConversion"/>
@@ -94,14 +94,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>harve.mp4</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>shop2.mp4</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>Fair|Str</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -206,10 +198,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>fix2.mp4</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>Str</t>
   </si>
   <si>
@@ -257,10 +245,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>search.mp4</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>Charm|Inte</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -273,10 +257,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>train2.mp4</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>Power</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -293,10 +273,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>secure.mp4</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>gate</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -305,10 +281,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>zhengbing.mp4</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>LeadShip|Charm</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -456,10 +428,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>atk.mp4</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>army</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -472,10 +440,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>move.mp4</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>敌人</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -489,6 +453,46 @@
   </si>
   <si>
     <t>true</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>move2.mp4</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>atk2.mp4</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>zhengbing2.mp4</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>secure2.mp4</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>train3.mp4</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>search2.mp4</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>fix3.mp4</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>harve2.mp4</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>shop3.mp4</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>移动到其他城市</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -893,7 +897,9 @@
     <col min="1" max="1" width="9.5" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="9.5" customWidth="1"/>
     <col min="3" max="3" width="9.125" customWidth="1"/>
-    <col min="4" max="10" width="14" customWidth="1"/>
+    <col min="4" max="5" width="14" customWidth="1"/>
+    <col min="6" max="6" width="8.625" customWidth="1"/>
+    <col min="7" max="10" width="14" customWidth="1"/>
     <col min="11" max="11" width="13.75" customWidth="1"/>
     <col min="12" max="12" width="14" customWidth="1"/>
     <col min="13" max="13" width="13.75" customWidth="1"/>
@@ -908,46 +914,46 @@
         <v>0</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C1" s="3" t="s">
         <v>10</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>102</v>
+        <v>95</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>114</v>
+        <v>105</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="H1" s="3" t="s">
-        <v>103</v>
+        <v>96</v>
       </c>
       <c r="I1" s="3" t="s">
-        <v>104</v>
+        <v>97</v>
       </c>
       <c r="J1" s="3" t="s">
         <v>14</v>
       </c>
       <c r="K1" s="3" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="L1" s="3" t="s">
         <v>14</v>
       </c>
       <c r="M1" s="3" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="N1" s="3" t="s">
         <v>14</v>
       </c>
       <c r="O1" s="3" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="P1" s="3" t="s">
         <v>14</v>
@@ -961,46 +967,46 @@
         <v>1</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>97</v>
+        <v>90</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>115</v>
+        <v>106</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>105</v>
+        <v>98</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>92</v>
+        <v>85</v>
       </c>
       <c r="K2" s="2" t="s">
-        <v>76</v>
+        <v>69</v>
       </c>
       <c r="L2" s="2" t="s">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="M2" s="2" t="s">
-        <v>80</v>
+        <v>73</v>
       </c>
       <c r="N2" s="2" t="s">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="O2" s="2" t="s">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="P2" s="2" t="s">
         <v>15</v>
@@ -1014,46 +1020,46 @@
         <v>7</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>6</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>98</v>
+        <v>91</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>116</v>
+        <v>107</v>
       </c>
       <c r="G3" s="2" t="s">
         <v>3</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>106</v>
+        <v>99</v>
       </c>
       <c r="J3" s="2" t="s">
         <v>3</v>
       </c>
       <c r="K3" s="2" t="s">
-        <v>77</v>
+        <v>70</v>
       </c>
       <c r="L3" s="2" t="s">
         <v>3</v>
       </c>
       <c r="M3" s="2" t="s">
-        <v>77</v>
+        <v>70</v>
       </c>
       <c r="N3" s="2" t="s">
         <v>3</v>
       </c>
       <c r="O3" s="2" t="s">
-        <v>77</v>
+        <v>70</v>
       </c>
       <c r="P3" s="2" t="s">
         <v>16</v>
@@ -1067,34 +1073,34 @@
         <v>2</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>5</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>99</v>
+        <v>92</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>99</v>
+        <v>92</v>
       </c>
       <c r="G4" s="2" t="s">
         <v>4</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>107</v>
+        <v>100</v>
       </c>
       <c r="J4" s="2" t="s">
         <v>4</v>
       </c>
       <c r="K4" s="2" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="L4" s="2" t="s">
         <v>4</v>
@@ -1120,20 +1126,20 @@
         <v>21001</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>100</v>
+        <v>93</v>
       </c>
       <c r="F5" s="6"/>
       <c r="G5" s="4" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="H5" s="4">
         <v>300</v>
@@ -1142,24 +1148,24 @@
         <v>3</v>
       </c>
       <c r="J5" s="4" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="K5" s="6" t="s">
+        <v>71</v>
+      </c>
+      <c r="L5" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="M5" s="6" t="s">
         <v>78</v>
-      </c>
-      <c r="L5" s="6" t="s">
-        <v>84</v>
-      </c>
-      <c r="M5" s="6" t="s">
-        <v>85</v>
       </c>
       <c r="N5" s="6"/>
       <c r="O5" s="6"/>
       <c r="P5" s="4" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="Q5" s="4" t="s">
-        <v>18</v>
+        <v>116</v>
       </c>
     </row>
     <row r="6" spans="1:39" x14ac:dyDescent="0.2">
@@ -1167,20 +1173,20 @@
         <v>21002</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>100</v>
+        <v>93</v>
       </c>
       <c r="F6" s="6"/>
       <c r="G6" s="4" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="H6" s="4">
         <v>300</v>
@@ -1189,24 +1195,24 @@
         <v>3</v>
       </c>
       <c r="J6" s="4" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="K6" s="6" t="s">
+        <v>71</v>
+      </c>
+      <c r="L6" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="M6" s="6" t="s">
         <v>78</v>
-      </c>
-      <c r="L6" s="6" t="s">
-        <v>84</v>
-      </c>
-      <c r="M6" s="6" t="s">
-        <v>85</v>
       </c>
       <c r="N6" s="6"/>
       <c r="O6" s="6"/>
       <c r="P6" s="4" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="Q6" s="4" t="s">
-        <v>19</v>
+        <v>117</v>
       </c>
     </row>
     <row r="7" spans="1:39" x14ac:dyDescent="0.2">
@@ -1214,20 +1220,20 @@
         <v>21003</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>69</v>
+        <v>63</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>100</v>
+        <v>93</v>
       </c>
       <c r="F7" s="6"/>
       <c r="G7" s="4" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="H7" s="4">
         <v>200</v>
@@ -1236,24 +1242,24 @@
         <v>3</v>
       </c>
       <c r="J7" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="K7" s="6" t="s">
+        <v>83</v>
+      </c>
+      <c r="L7" s="6" t="s">
         <v>49</v>
       </c>
-      <c r="K7" s="6" t="s">
-        <v>90</v>
-      </c>
-      <c r="L7" s="6" t="s">
-        <v>52</v>
-      </c>
       <c r="M7" s="6" t="s">
-        <v>86</v>
+        <v>79</v>
       </c>
       <c r="N7" s="6"/>
       <c r="O7" s="6"/>
       <c r="P7" s="4" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="Q7" s="4" t="s">
-        <v>46</v>
+        <v>115</v>
       </c>
       <c r="AL7" s="5"/>
       <c r="AM7" s="5"/>
@@ -1263,20 +1269,20 @@
         <v>21004</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>100</v>
+        <v>93</v>
       </c>
       <c r="F8" s="6"/>
       <c r="G8" s="4" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="H8" s="4">
         <v>150</v>
@@ -1285,24 +1291,24 @@
         <v>3</v>
       </c>
       <c r="J8" s="4" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="K8" s="6" t="s">
-        <v>88</v>
+        <v>81</v>
       </c>
       <c r="L8" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="M8" s="6" t="s">
         <v>84</v>
-      </c>
-      <c r="M8" s="6" t="s">
-        <v>91</v>
       </c>
       <c r="N8" s="6"/>
       <c r="O8" s="6"/>
       <c r="P8" s="4" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="Q8" s="4" t="s">
-        <v>68</v>
+        <v>112</v>
       </c>
       <c r="AL8" s="5"/>
       <c r="AM8" s="5"/>
@@ -1312,42 +1318,42 @@
         <v>21005</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>100</v>
+        <v>93</v>
       </c>
       <c r="F9" s="6"/>
       <c r="G9" s="4" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="H9" s="4">
         <v>0</v>
       </c>
       <c r="I9" s="4">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="J9" s="4" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="K9" s="6" t="s">
-        <v>94</v>
+        <v>87</v>
       </c>
       <c r="L9" s="6"/>
       <c r="M9" s="6"/>
       <c r="N9" s="6"/>
       <c r="O9" s="6"/>
       <c r="P9" s="4" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="Q9" s="4" t="s">
-        <v>59</v>
+        <v>114</v>
       </c>
     </row>
     <row r="10" spans="1:39" x14ac:dyDescent="0.2">
@@ -1355,20 +1361,20 @@
         <v>21006</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>110</v>
+        <v>102</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>100</v>
+        <v>93</v>
       </c>
       <c r="F10" s="6"/>
       <c r="G10" s="4" t="s">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="H10" s="4">
         <v>0</v>
@@ -1377,20 +1383,20 @@
         <v>3</v>
       </c>
       <c r="J10" s="4" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="K10" s="6" t="s">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="L10" s="6"/>
       <c r="M10" s="6"/>
       <c r="N10" s="6"/>
       <c r="O10" s="6"/>
       <c r="P10" s="4" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="Q10" s="4" t="s">
-        <v>63</v>
+        <v>113</v>
       </c>
     </row>
     <row r="11" spans="1:39" x14ac:dyDescent="0.2">
@@ -1398,20 +1404,20 @@
         <v>21007</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>110</v>
+        <v>102</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>74</v>
+        <v>67</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>75</v>
+        <v>68</v>
       </c>
       <c r="E11" s="4" t="s">
-        <v>100</v>
+        <v>93</v>
       </c>
       <c r="F11" s="6"/>
       <c r="G11" s="4" t="s">
-        <v>70</v>
+        <v>64</v>
       </c>
       <c r="H11" s="4">
         <v>300</v>
@@ -1420,28 +1426,28 @@
         <v>3</v>
       </c>
       <c r="J11" s="4" t="s">
-        <v>73</v>
+        <v>66</v>
       </c>
       <c r="K11" s="6" t="s">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="L11" s="6" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="M11" s="6" t="s">
-        <v>89</v>
+        <v>82</v>
       </c>
       <c r="N11" s="6" t="s">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="O11" s="6" t="s">
-        <v>93</v>
+        <v>86</v>
       </c>
       <c r="P11" s="4" t="s">
-        <v>72</v>
+        <v>65</v>
       </c>
       <c r="Q11" s="4" t="s">
-        <v>71</v>
+        <v>111</v>
       </c>
     </row>
     <row r="12" spans="1:39" x14ac:dyDescent="0.2">
@@ -1449,22 +1455,22 @@
         <v>21008</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>110</v>
+        <v>102</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>95</v>
+        <v>88</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>96</v>
+        <v>89</v>
       </c>
       <c r="E12" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="F12" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="G12" s="4" t="s">
         <v>101</v>
-      </c>
-      <c r="F12" s="6" t="s">
-        <v>117</v>
-      </c>
-      <c r="G12" s="4" t="s">
-        <v>108</v>
       </c>
       <c r="H12" s="4">
         <v>0</v>
@@ -1479,10 +1485,10 @@
       <c r="N12" s="6"/>
       <c r="O12" s="6"/>
       <c r="P12" s="4" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="Q12" s="4" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
     </row>
     <row r="13" spans="1:39" x14ac:dyDescent="0.2">
@@ -1490,20 +1496,20 @@
         <v>21009</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>69</v>
+        <v>63</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>111</v>
+        <v>103</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>96</v>
+        <v>118</v>
       </c>
       <c r="E13" s="4" t="s">
-        <v>101</v>
+        <v>94</v>
       </c>
       <c r="F13" s="6"/>
       <c r="G13" s="4" t="s">
-        <v>112</v>
+        <v>104</v>
       </c>
       <c r="H13" s="4">
         <v>0</v>
@@ -1518,10 +1524,10 @@
       <c r="N13" s="6"/>
       <c r="O13" s="6"/>
       <c r="P13" s="4" t="s">
-        <v>72</v>
+        <v>65</v>
       </c>
       <c r="Q13" s="4" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
     </row>
   </sheetData>

--- a/Design/config/CityDevConfig.xlsx
+++ b/Design/config/CityDevConfig.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$4:$Q$4</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$4:$R$4</definedName>
   </definedNames>
   <calcPr calcId="162913"/>
   <extLst>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="158" uniqueCount="119">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="169" uniqueCount="127">
   <si>
     <t>序列</t>
     <phoneticPr fontId="3" type="noConversion"/>
@@ -493,6 +493,38 @@
   </si>
   <si>
     <t>移动到其他城市</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>图标</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>string</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>cs</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>dev</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>def</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>find</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>sod</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>ActionName</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -891,7 +923,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AM13"/>
+  <dimension ref="A1:AN13"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9.5" bestFit="1" customWidth="1"/>
@@ -899,17 +931,19 @@
     <col min="3" max="3" width="9.125" customWidth="1"/>
     <col min="4" max="5" width="14" customWidth="1"/>
     <col min="6" max="6" width="8.625" customWidth="1"/>
-    <col min="7" max="10" width="14" customWidth="1"/>
+    <col min="7" max="9" width="9.125" customWidth="1"/>
+    <col min="10" max="10" width="14" customWidth="1"/>
     <col min="11" max="11" width="13.75" customWidth="1"/>
     <col min="12" max="12" width="14" customWidth="1"/>
     <col min="13" max="13" width="13.75" customWidth="1"/>
     <col min="14" max="14" width="14" customWidth="1"/>
     <col min="15" max="15" width="13.75" customWidth="1"/>
     <col min="16" max="16" width="14" customWidth="1"/>
-    <col min="17" max="17" width="9.5" customWidth="1"/>
+    <col min="17" max="17" width="8" customWidth="1"/>
+    <col min="18" max="18" width="9.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:39" ht="57" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:40" ht="57" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -959,10 +993,13 @@
         <v>14</v>
       </c>
       <c r="Q1" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="R1" s="3" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="2" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:40" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
@@ -1012,10 +1049,13 @@
         <v>15</v>
       </c>
       <c r="Q2" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="R2" s="2" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="3" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:40" x14ac:dyDescent="0.2">
       <c r="A3" s="2" t="s">
         <v>7</v>
       </c>
@@ -1065,10 +1105,13 @@
         <v>16</v>
       </c>
       <c r="Q3" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="R3" s="2" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:40" x14ac:dyDescent="0.2">
       <c r="A4" s="2" t="s">
         <v>2</v>
       </c>
@@ -1118,10 +1161,13 @@
         <v>17</v>
       </c>
       <c r="Q4" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="R4" s="2" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="5" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:40" x14ac:dyDescent="0.2">
       <c r="A5" s="4">
         <v>21001</v>
       </c>
@@ -1165,10 +1211,13 @@
         <v>18</v>
       </c>
       <c r="Q5" s="4" t="s">
+        <v>122</v>
+      </c>
+      <c r="R5" s="4" t="s">
         <v>116</v>
       </c>
     </row>
-    <row r="6" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:40" x14ac:dyDescent="0.2">
       <c r="A6" s="4">
         <v>21002</v>
       </c>
@@ -1212,10 +1261,13 @@
         <v>19</v>
       </c>
       <c r="Q6" s="4" t="s">
+        <v>122</v>
+      </c>
+      <c r="R6" s="4" t="s">
         <v>117</v>
       </c>
     </row>
-    <row r="7" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:40" x14ac:dyDescent="0.2">
       <c r="A7" s="4">
         <v>21003</v>
       </c>
@@ -1259,12 +1311,15 @@
         <v>45</v>
       </c>
       <c r="Q7" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="R7" s="4" t="s">
         <v>115</v>
       </c>
-      <c r="AL7" s="5"/>
       <c r="AM7" s="5"/>
+      <c r="AN7" s="5"/>
     </row>
-    <row r="8" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:40" x14ac:dyDescent="0.2">
       <c r="A8" s="4">
         <v>21004</v>
       </c>
@@ -1308,12 +1363,15 @@
         <v>44</v>
       </c>
       <c r="Q8" s="4" t="s">
+        <v>122</v>
+      </c>
+      <c r="R8" s="4" t="s">
         <v>112</v>
       </c>
-      <c r="AL8" s="5"/>
       <c r="AM8" s="5"/>
+      <c r="AN8" s="5"/>
     </row>
-    <row r="9" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:40" x14ac:dyDescent="0.2">
       <c r="A9" s="4">
         <v>21005</v>
       </c>
@@ -1353,10 +1411,13 @@
         <v>56</v>
       </c>
       <c r="Q9" s="4" t="s">
+        <v>124</v>
+      </c>
+      <c r="R9" s="4" t="s">
         <v>114</v>
       </c>
     </row>
-    <row r="10" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:40" x14ac:dyDescent="0.2">
       <c r="A10" s="4">
         <v>21006</v>
       </c>
@@ -1396,10 +1457,13 @@
         <v>48</v>
       </c>
       <c r="Q10" s="4" t="s">
+        <v>125</v>
+      </c>
+      <c r="R10" s="4" t="s">
         <v>113</v>
       </c>
     </row>
-    <row r="11" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:40" x14ac:dyDescent="0.2">
       <c r="A11" s="4">
         <v>21007</v>
       </c>
@@ -1447,10 +1511,13 @@
         <v>65</v>
       </c>
       <c r="Q11" s="4" t="s">
+        <v>125</v>
+      </c>
+      <c r="R11" s="4" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="12" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:40" x14ac:dyDescent="0.2">
       <c r="A12" s="4">
         <v>21008</v>
       </c>
@@ -1487,11 +1554,12 @@
       <c r="P12" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="Q12" s="4" t="s">
+      <c r="Q12" s="4"/>
+      <c r="R12" s="4" t="s">
         <v>110</v>
       </c>
     </row>
-    <row r="13" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:40" x14ac:dyDescent="0.2">
       <c r="A13" s="4">
         <v>21009</v>
       </c>
@@ -1526,7 +1594,8 @@
       <c r="P13" s="4" t="s">
         <v>65</v>
       </c>
-      <c r="Q13" s="4" t="s">
+      <c r="Q13" s="4"/>
+      <c r="R13" s="4" t="s">
         <v>109</v>
       </c>
     </row>

--- a/Design/config/CityDevConfig.xlsx
+++ b/Design/config/CityDevConfig.xlsx
@@ -484,10 +484,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>harve2.mp4</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>shop3.mp4</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -525,6 +521,10 @@
   </si>
   <si>
     <t>ActionName</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>farm.mp4</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -993,7 +993,7 @@
         <v>14</v>
       </c>
       <c r="Q1" s="3" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="R1" s="3" t="s">
         <v>11</v>
@@ -1049,7 +1049,7 @@
         <v>15</v>
       </c>
       <c r="Q2" s="2" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="R2" s="2" t="s">
         <v>12</v>
@@ -1105,7 +1105,7 @@
         <v>16</v>
       </c>
       <c r="Q3" s="2" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="R3" s="2" t="s">
         <v>13</v>
@@ -1161,7 +1161,7 @@
         <v>17</v>
       </c>
       <c r="Q4" s="2" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="R4" s="2" t="s">
         <v>8</v>
@@ -1211,10 +1211,10 @@
         <v>18</v>
       </c>
       <c r="Q5" s="4" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="R5" s="4" t="s">
-        <v>116</v>
+        <v>126</v>
       </c>
     </row>
     <row r="6" spans="1:40" x14ac:dyDescent="0.2">
@@ -1261,10 +1261,10 @@
         <v>19</v>
       </c>
       <c r="Q6" s="4" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="R6" s="4" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
     <row r="7" spans="1:40" x14ac:dyDescent="0.2">
@@ -1311,7 +1311,7 @@
         <v>45</v>
       </c>
       <c r="Q7" s="4" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="R7" s="4" t="s">
         <v>115</v>
@@ -1363,7 +1363,7 @@
         <v>44</v>
       </c>
       <c r="Q8" s="4" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="R8" s="4" t="s">
         <v>112</v>
@@ -1411,7 +1411,7 @@
         <v>56</v>
       </c>
       <c r="Q9" s="4" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="R9" s="4" t="s">
         <v>114</v>
@@ -1457,7 +1457,7 @@
         <v>48</v>
       </c>
       <c r="Q10" s="4" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="R10" s="4" t="s">
         <v>113</v>
@@ -1511,7 +1511,7 @@
         <v>65</v>
       </c>
       <c r="Q11" s="4" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="R11" s="4" t="s">
         <v>111</v>
@@ -1570,7 +1570,7 @@
         <v>103</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="E13" s="4" t="s">
         <v>94</v>

--- a/Design/config/CityDevConfig.xlsx
+++ b/Design/config/CityDevConfig.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$4:$R$4</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$4:$R$14</definedName>
   </definedNames>
   <calcPr calcId="162913"/>
   <extLst>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="169" uniqueCount="127">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="176" uniqueCount="133">
   <si>
     <t>序列</t>
     <phoneticPr fontId="3" type="noConversion"/>
@@ -480,10 +480,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>fix3.mp4</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>shop3.mp4</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -492,10 +488,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>图标</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>string</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -525,6 +517,38 @@
   </si>
   <si>
     <t>farm.mp4</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>CityDevChange</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>交易钱粮</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>行动</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Inte</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>交易</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>change</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>change.mp4</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>fix4.mp4</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -923,7 +947,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AN13"/>
+  <dimension ref="A1:AN14"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9.5" bestFit="1" customWidth="1"/>
@@ -993,7 +1017,7 @@
         <v>14</v>
       </c>
       <c r="Q1" s="3" t="s">
-        <v>118</v>
+        <v>127</v>
       </c>
       <c r="R1" s="3" t="s">
         <v>11</v>
@@ -1049,7 +1073,7 @@
         <v>15</v>
       </c>
       <c r="Q2" s="2" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="R2" s="2" t="s">
         <v>12</v>
@@ -1105,7 +1129,7 @@
         <v>16</v>
       </c>
       <c r="Q3" s="2" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="R3" s="2" t="s">
         <v>13</v>
@@ -1161,7 +1185,7 @@
         <v>17</v>
       </c>
       <c r="Q4" s="2" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="R4" s="2" t="s">
         <v>8</v>
@@ -1211,10 +1235,10 @@
         <v>18</v>
       </c>
       <c r="Q5" s="4" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="R5" s="4" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
     </row>
     <row r="6" spans="1:40" x14ac:dyDescent="0.2">
@@ -1222,7 +1246,7 @@
         <v>21002</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="C6" s="4" t="s">
         <v>26</v>
@@ -1261,15 +1285,15 @@
         <v>19</v>
       </c>
       <c r="Q6" s="4" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="R6" s="4" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
     </row>
     <row r="7" spans="1:40" x14ac:dyDescent="0.2">
       <c r="A7" s="4">
-        <v>21003</v>
+        <v>21101</v>
       </c>
       <c r="B7" s="4" t="s">
         <v>63</v>
@@ -1311,85 +1335,77 @@
         <v>45</v>
       </c>
       <c r="Q7" s="4" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="R7" s="4" t="s">
-        <v>115</v>
+        <v>132</v>
       </c>
       <c r="AM7" s="5"/>
       <c r="AN7" s="5"/>
     </row>
     <row r="8" spans="1:40" x14ac:dyDescent="0.2">
       <c r="A8" s="4">
-        <v>21004</v>
+        <v>21102</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>29</v>
+        <v>63</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>51</v>
+        <v>103</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>52</v>
+        <v>116</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="F8" s="6"/>
       <c r="G8" s="4" t="s">
-        <v>50</v>
+        <v>104</v>
       </c>
       <c r="H8" s="4">
-        <v>150</v>
+        <v>0</v>
       </c>
       <c r="I8" s="4">
-        <v>3</v>
-      </c>
-      <c r="J8" s="4" t="s">
-        <v>49</v>
-      </c>
-      <c r="K8" s="6" t="s">
-        <v>81</v>
-      </c>
-      <c r="L8" s="6" t="s">
-        <v>77</v>
-      </c>
-      <c r="M8" s="6" t="s">
-        <v>84</v>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="J8" s="4"/>
+      <c r="K8" s="6"/>
+      <c r="L8" s="6"/>
+      <c r="M8" s="6"/>
       <c r="N8" s="6"/>
       <c r="O8" s="6"/>
       <c r="P8" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="Q8" s="4" t="s">
-        <v>121</v>
-      </c>
+        <v>65</v>
+      </c>
+      <c r="Q8" s="4"/>
       <c r="R8" s="4" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="AM8" s="5"/>
       <c r="AN8" s="5"/>
     </row>
     <row r="9" spans="1:40" x14ac:dyDescent="0.2">
       <c r="A9" s="4">
-        <v>21005</v>
+        <v>21103</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>53</v>
+        <v>102</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>54</v>
+        <v>88</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>55</v>
+        <v>89</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>93</v>
-      </c>
-      <c r="F9" s="6"/>
+        <v>94</v>
+      </c>
+      <c r="F9" s="6" t="s">
+        <v>108</v>
+      </c>
       <c r="G9" s="4" t="s">
-        <v>57</v>
+        <v>101</v>
       </c>
       <c r="H9" s="4">
         <v>0</v>
@@ -1397,153 +1413,141 @@
       <c r="I9" s="4">
         <v>10</v>
       </c>
-      <c r="J9" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="K9" s="6" t="s">
-        <v>87</v>
-      </c>
+      <c r="J9" s="4"/>
+      <c r="K9" s="6"/>
       <c r="L9" s="6"/>
       <c r="M9" s="6"/>
       <c r="N9" s="6"/>
       <c r="O9" s="6"/>
       <c r="P9" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="Q9" s="4" t="s">
-        <v>123</v>
-      </c>
+        <v>48</v>
+      </c>
+      <c r="Q9" s="4"/>
       <c r="R9" s="4" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
     </row>
     <row r="10" spans="1:40" x14ac:dyDescent="0.2">
       <c r="A10" s="4">
-        <v>21006</v>
+        <v>21201</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>102</v>
+        <v>29</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>60</v>
+        <v>51</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>61</v>
+        <v>52</v>
       </c>
       <c r="E10" s="4" t="s">
         <v>93</v>
       </c>
       <c r="F10" s="6"/>
       <c r="G10" s="4" t="s">
-        <v>62</v>
+        <v>50</v>
       </c>
       <c r="H10" s="4">
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="I10" s="4">
         <v>3</v>
       </c>
       <c r="J10" s="4" t="s">
-        <v>59</v>
+        <v>49</v>
       </c>
       <c r="K10" s="6" t="s">
-        <v>80</v>
-      </c>
-      <c r="L10" s="6"/>
-      <c r="M10" s="6"/>
+        <v>81</v>
+      </c>
+      <c r="L10" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="M10" s="6" t="s">
+        <v>84</v>
+      </c>
       <c r="N10" s="6"/>
       <c r="O10" s="6"/>
       <c r="P10" s="4" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="Q10" s="4" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
       <c r="R10" s="4" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="11" spans="1:40" x14ac:dyDescent="0.2">
       <c r="A11" s="4">
-        <v>21007</v>
+        <v>21202</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>102</v>
+        <v>53</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>67</v>
+        <v>54</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>68</v>
+        <v>55</v>
       </c>
       <c r="E11" s="4" t="s">
         <v>93</v>
       </c>
       <c r="F11" s="6"/>
       <c r="G11" s="4" t="s">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="H11" s="4">
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="I11" s="4">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="J11" s="4" t="s">
-        <v>66</v>
+        <v>58</v>
       </c>
       <c r="K11" s="6" t="s">
-        <v>76</v>
-      </c>
-      <c r="L11" s="6" t="s">
-        <v>49</v>
-      </c>
-      <c r="M11" s="6" t="s">
-        <v>82</v>
-      </c>
-      <c r="N11" s="6" t="s">
-        <v>77</v>
-      </c>
-      <c r="O11" s="6" t="s">
-        <v>86</v>
-      </c>
+        <v>87</v>
+      </c>
+      <c r="L11" s="6"/>
+      <c r="M11" s="6"/>
+      <c r="N11" s="6"/>
+      <c r="O11" s="6"/>
       <c r="P11" s="4" t="s">
-        <v>65</v>
+        <v>56</v>
       </c>
       <c r="Q11" s="4" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="R11" s="4" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
     </row>
     <row r="12" spans="1:40" x14ac:dyDescent="0.2">
       <c r="A12" s="4">
-        <v>21008</v>
+        <v>21203</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>102</v>
+        <v>53</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>88</v>
+        <v>129</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>89</v>
+        <v>126</v>
       </c>
       <c r="E12" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="F12" s="6" t="s">
-        <v>108</v>
-      </c>
+        <v>125</v>
+      </c>
+      <c r="F12" s="6"/>
       <c r="G12" s="4" t="s">
-        <v>101</v>
+        <v>130</v>
       </c>
       <c r="H12" s="4">
         <v>0</v>
       </c>
       <c r="I12" s="4">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="J12" s="4"/>
       <c r="K12" s="6"/>
@@ -1552,54 +1556,119 @@
       <c r="N12" s="6"/>
       <c r="O12" s="6"/>
       <c r="P12" s="4" t="s">
-        <v>48</v>
+        <v>128</v>
       </c>
       <c r="Q12" s="4"/>
       <c r="R12" s="4" t="s">
-        <v>110</v>
+        <v>131</v>
       </c>
     </row>
     <row r="13" spans="1:40" x14ac:dyDescent="0.2">
       <c r="A13" s="4">
-        <v>21009</v>
+        <v>21301</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>63</v>
+        <v>102</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>103</v>
+        <v>60</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>117</v>
+        <v>61</v>
       </c>
       <c r="E13" s="4" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="F13" s="6"/>
       <c r="G13" s="4" t="s">
-        <v>104</v>
+        <v>62</v>
       </c>
       <c r="H13" s="4">
         <v>0</v>
       </c>
       <c r="I13" s="4">
-        <v>10</v>
-      </c>
-      <c r="J13" s="4"/>
-      <c r="K13" s="6"/>
+        <v>3</v>
+      </c>
+      <c r="J13" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="K13" s="6" t="s">
+        <v>80</v>
+      </c>
       <c r="L13" s="6"/>
       <c r="M13" s="6"/>
       <c r="N13" s="6"/>
       <c r="O13" s="6"/>
       <c r="P13" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q13" s="4" t="s">
+        <v>122</v>
+      </c>
+      <c r="R13" s="4" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="14" spans="1:40" x14ac:dyDescent="0.2">
+      <c r="A14" s="4">
+        <v>21302</v>
+      </c>
+      <c r="B14" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="C14" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="D14" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="E14" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="F14" s="6"/>
+      <c r="G14" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="H14" s="4">
+        <v>300</v>
+      </c>
+      <c r="I14" s="4">
+        <v>3</v>
+      </c>
+      <c r="J14" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="K14" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="L14" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="M14" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="N14" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="O14" s="6" t="s">
+        <v>86</v>
+      </c>
+      <c r="P14" s="4" t="s">
         <v>65</v>
       </c>
-      <c r="Q13" s="4"/>
-      <c r="R13" s="4" t="s">
-        <v>109</v>
+      <c r="Q14" s="4" t="s">
+        <v>122</v>
+      </c>
+      <c r="R14" s="4" t="s">
+        <v>111</v>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A4:R14">
+    <sortState ref="A5:R13">
+      <sortCondition ref="A4:A13"/>
+    </sortState>
+  </autoFilter>
   <sortState ref="A5:Q43">
     <sortCondition ref="A41"/>
   </sortState>

--- a/Design/config/CityDevConfig.xlsx
+++ b/Design/config/CityDevConfig.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="176" uniqueCount="133">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="178" uniqueCount="134">
   <si>
     <t>序列</t>
     <phoneticPr fontId="3" type="noConversion"/>
@@ -549,6 +549,10 @@
   </si>
   <si>
     <t>fix4.mp4</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Food</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -1549,9 +1553,13 @@
       <c r="I12" s="4">
         <v>1</v>
       </c>
-      <c r="J12" s="4"/>
+      <c r="J12" s="4" t="s">
+        <v>58</v>
+      </c>
       <c r="K12" s="6"/>
-      <c r="L12" s="6"/>
+      <c r="L12" s="6" t="s">
+        <v>133</v>
+      </c>
       <c r="M12" s="6"/>
       <c r="N12" s="6"/>
       <c r="O12" s="6"/>

--- a/Design/config/CityDevConfig.xlsx
+++ b/Design/config/CityDevConfig.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="178" uniqueCount="134">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="185" uniqueCount="141">
   <si>
     <t>序列</t>
     <phoneticPr fontId="3" type="noConversion"/>
@@ -110,138 +110,469 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
+    <t>string</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>cs</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>发展农业</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>发展商业</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>图片</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Icon</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>market</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>ArchFood</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>ArchGold</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>GoldCost</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>int</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>cs</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>描述</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Des</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>cs</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>提升值</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>cs</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>加固城墙</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>发展农业,提升粮食产量</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>发展商业,提升金钱收入</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>提升城防</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Str</t>
+  </si>
+  <si>
+    <t>Str</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Wall</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>wall</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>LeadShip|Str</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Secure</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>secure</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>街道巡逻</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>提升治安</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>market</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>走访</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>搜集人才和宝物</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Charm|Inte</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>find</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Gold</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Power</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>训练</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>提升军队士气</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>train</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>gate</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>zhengbing</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>LeadShip|Charm</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Soldier</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>征兵</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>提升士兵数量</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>DevAttr1Value</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>int[]</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>4,10</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>DevAttr2</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>DevAttr2Value</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>DevAttr3</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>DevAttr3Value</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>200,600</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>ArchPeople</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>300,800</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>1,3</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>3,9</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>2,6</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>-2,-5</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>6,15</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>200,500</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>DevAttr1</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>-500,-1500</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>20,100</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>出战</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>出兵攻打敌人</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Prefab</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>string</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>cs</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>CityDevNormal</t>
+  </si>
+  <si>
+    <t>CityDevBattle</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>对象</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>人均消耗黄金</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>最大参与人数</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>HeroCount</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>int</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>cs</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>battle</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>army</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>移动</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>move</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>敌人</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>FindEnemy</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>bool</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>true</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>move2.mp4</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>atk2.mp4</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>zhengbing2.mp4</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>secure2.mp4</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>train3.mp4</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>search2.mp4</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>shop3.mp4</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>移动到其他城市</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>string</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>cs</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>dev</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>def</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>find</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>sod</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>ActionName</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>farm.mp4</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>CityDevChange</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>交易钱粮</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>行动</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Inte</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>交易</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>change</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>change.mp4</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>fix4.mp4</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Food</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
     <t>BuildingName</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>string</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>cs</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>发展农业</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>发展商业</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>图片</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Icon</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>market</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>ArchFood</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>ArchGold</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>GoldCost</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>int</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>cs</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>描述</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Des</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>cs</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>提升值</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>cs</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>加固城墙</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>发展农业,提升粮食产量</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>发展商业,提升金钱收入</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>提升城防</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Str</t>
-  </si>
-  <si>
-    <t>Str</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Wall</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>wall</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>LeadShip|Str</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Secure</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>secure</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>街道巡逻</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>提升治安</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>market</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>走访</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>搜集人才和宝物</t>
+    <t>house</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>登用</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>提拔在野武将</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>CityDevUseHero</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>wild</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
@@ -249,310 +580,7 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>find</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Gold</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Power</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>训练</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>提升军队士气</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>train</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>gate</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>zhengbing</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>LeadShip|Charm</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Soldier</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>征兵</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>提升士兵数量</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>DevAttr1Value</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>int[]</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>4,10</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>DevAttr2</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>DevAttr2Value</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>DevAttr3</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>DevAttr3Value</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>200,600</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>ArchPeople</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>300,800</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>1,3</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>3,9</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>2,6</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>-2,-5</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>6,15</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>200,500</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>DevAttr1</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>-500,-1500</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>20,100</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>出战</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>出兵攻打敌人</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Prefab</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>string</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>cs</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>CityDevNormal</t>
-  </si>
-  <si>
-    <t>CityDevBattle</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>对象</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>人均消耗黄金</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>最大参与人数</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>HeroCount</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>int</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>cs</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>battle</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>army</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>移动</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>move</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>敌人</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>FindEnemy</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>bool</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>true</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>move2.mp4</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>atk2.mp4</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>zhengbing2.mp4</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>secure2.mp4</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>train3.mp4</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>search2.mp4</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>shop3.mp4</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>移动到其他城市</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>string</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>cs</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>dev</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>def</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>find</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>sod</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>ActionName</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>farm.mp4</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>CityDevChange</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>交易钱粮</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>行动</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Inte</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>交易</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>change</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>change.mp4</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>fix4.mp4</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Food</t>
+    <t>wild.mp4</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -951,7 +979,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AN14"/>
+  <dimension ref="A1:AN15"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9.5" bestFit="1" customWidth="1"/>
@@ -982,46 +1010,46 @@
         <v>10</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E1" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="G1" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="H1" s="3" t="s">
         <v>95</v>
       </c>
-      <c r="F1" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="G1" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="H1" s="3" t="s">
+      <c r="I1" s="3" t="s">
         <v>96</v>
-      </c>
-      <c r="I1" s="3" t="s">
-        <v>97</v>
       </c>
       <c r="J1" s="3" t="s">
         <v>14</v>
       </c>
       <c r="K1" s="3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="L1" s="3" t="s">
         <v>14</v>
       </c>
       <c r="M1" s="3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="N1" s="3" t="s">
         <v>14</v>
       </c>
       <c r="O1" s="3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="P1" s="3" t="s">
         <v>14</v>
       </c>
       <c r="Q1" s="3" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="R1" s="3" t="s">
         <v>11</v>
@@ -1032,52 +1060,52 @@
         <v>1</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>22</v>
+        <v>133</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="K2" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="L2" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="M2" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="M2" s="2" t="s">
+      <c r="N2" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="N2" s="2" t="s">
+      <c r="O2" s="2" t="s">
         <v>74</v>
-      </c>
-      <c r="O2" s="2" t="s">
-        <v>75</v>
       </c>
       <c r="P2" s="2" t="s">
         <v>15</v>
       </c>
       <c r="Q2" s="2" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="R2" s="2" t="s">
         <v>12</v>
@@ -1088,52 +1116,52 @@
         <v>7</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>6</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="G3" s="2" t="s">
         <v>3</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="J3" s="2" t="s">
         <v>3</v>
       </c>
       <c r="K3" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="L3" s="2" t="s">
         <v>3</v>
       </c>
       <c r="M3" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="N3" s="2" t="s">
         <v>3</v>
       </c>
       <c r="O3" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="P3" s="2" t="s">
         <v>16</v>
       </c>
       <c r="Q3" s="2" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="R3" s="2" t="s">
         <v>13</v>
@@ -1144,34 +1172,34 @@
         <v>2</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>5</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="G4" s="2" t="s">
         <v>4</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="J4" s="2" t="s">
         <v>4</v>
       </c>
       <c r="K4" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="L4" s="2" t="s">
         <v>4</v>
@@ -1189,7 +1217,7 @@
         <v>17</v>
       </c>
       <c r="Q4" s="2" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="R4" s="2" t="s">
         <v>8</v>
@@ -1203,13 +1231,13 @@
         <v>20</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="F5" s="6"/>
       <c r="G5" s="4" t="s">
@@ -1222,16 +1250,16 @@
         <v>3</v>
       </c>
       <c r="J5" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="K5" s="6" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="L5" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="M5" s="6" t="s">
         <v>77</v>
-      </c>
-      <c r="M5" s="6" t="s">
-        <v>78</v>
       </c>
       <c r="N5" s="6"/>
       <c r="O5" s="6"/>
@@ -1239,10 +1267,10 @@
         <v>18</v>
       </c>
       <c r="Q5" s="4" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="R5" s="4" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="6" spans="1:40" x14ac:dyDescent="0.2">
@@ -1253,17 +1281,17 @@
         <v>20</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="F6" s="6"/>
       <c r="G6" s="4" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="H6" s="4">
         <v>300</v>
@@ -1272,16 +1300,16 @@
         <v>3</v>
       </c>
       <c r="J6" s="4" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="K6" s="6" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="L6" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="M6" s="6" t="s">
         <v>77</v>
-      </c>
-      <c r="M6" s="6" t="s">
-        <v>78</v>
       </c>
       <c r="N6" s="6"/>
       <c r="O6" s="6"/>
@@ -1289,10 +1317,10 @@
         <v>19</v>
       </c>
       <c r="Q6" s="4" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="R6" s="4" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
     </row>
     <row r="7" spans="1:40" x14ac:dyDescent="0.2">
@@ -1300,20 +1328,20 @@
         <v>21101</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="F7" s="6"/>
       <c r="G7" s="4" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="H7" s="4">
         <v>200</v>
@@ -1322,27 +1350,27 @@
         <v>3</v>
       </c>
       <c r="J7" s="4" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="K7" s="6" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="L7" s="6" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="M7" s="6" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="N7" s="6"/>
       <c r="O7" s="6"/>
       <c r="P7" s="4" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="Q7" s="4" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="R7" s="4" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="AM7" s="5"/>
       <c r="AN7" s="5"/>
@@ -1352,20 +1380,20 @@
         <v>21102</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="F8" s="6"/>
       <c r="G8" s="4" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="H8" s="4">
         <v>0</v>
@@ -1380,11 +1408,11 @@
       <c r="N8" s="6"/>
       <c r="O8" s="6"/>
       <c r="P8" s="4" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="Q8" s="4"/>
       <c r="R8" s="4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AM8" s="5"/>
       <c r="AN8" s="5"/>
@@ -1394,22 +1422,22 @@
         <v>21103</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C9" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="D9" s="4" t="s">
         <v>88</v>
       </c>
-      <c r="D9" s="4" t="s">
-        <v>89</v>
-      </c>
       <c r="E9" s="4" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="F9" s="6" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="G9" s="4" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="H9" s="4">
         <v>0</v>
@@ -1424,11 +1452,11 @@
       <c r="N9" s="6"/>
       <c r="O9" s="6"/>
       <c r="P9" s="4" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="Q9" s="4"/>
       <c r="R9" s="4" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="10" spans="1:40" x14ac:dyDescent="0.2">
@@ -1436,20 +1464,20 @@
         <v>21201</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C10" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="D10" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="D10" s="4" t="s">
-        <v>52</v>
-      </c>
       <c r="E10" s="4" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="F10" s="6"/>
       <c r="G10" s="4" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="H10" s="4">
         <v>150</v>
@@ -1458,27 +1486,27 @@
         <v>3</v>
       </c>
       <c r="J10" s="4" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="K10" s="6" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="L10" s="6" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="M10" s="6" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="N10" s="6"/>
       <c r="O10" s="6"/>
       <c r="P10" s="4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="Q10" s="4" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="R10" s="4" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="11" spans="1:40" x14ac:dyDescent="0.2">
@@ -1486,20 +1514,20 @@
         <v>21202</v>
       </c>
       <c r="B11" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="C11" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="C11" s="4" t="s">
+      <c r="D11" s="4" t="s">
         <v>54</v>
       </c>
-      <c r="D11" s="4" t="s">
-        <v>55</v>
-      </c>
       <c r="E11" s="4" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="F11" s="6"/>
       <c r="G11" s="4" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="H11" s="4">
         <v>0</v>
@@ -1508,23 +1536,23 @@
         <v>10</v>
       </c>
       <c r="J11" s="4" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="K11" s="6" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="L11" s="6"/>
       <c r="M11" s="6"/>
       <c r="N11" s="6"/>
       <c r="O11" s="6"/>
       <c r="P11" s="4" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="Q11" s="4" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="R11" s="4" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="12" spans="1:40" x14ac:dyDescent="0.2">
@@ -1532,20 +1560,20 @@
         <v>21203</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="E12" s="4" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F12" s="6"/>
       <c r="G12" s="4" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="H12" s="4">
         <v>0</v>
@@ -1554,21 +1582,21 @@
         <v>1</v>
       </c>
       <c r="J12" s="4" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="K12" s="6"/>
       <c r="L12" s="6" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="M12" s="6"/>
       <c r="N12" s="6"/>
       <c r="O12" s="6"/>
       <c r="P12" s="4" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="Q12" s="4"/>
       <c r="R12" s="4" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
     </row>
     <row r="13" spans="1:40" x14ac:dyDescent="0.2">
@@ -1576,20 +1604,20 @@
         <v>21301</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C13" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="D13" s="4" t="s">
         <v>60</v>
       </c>
-      <c r="D13" s="4" t="s">
-        <v>61</v>
-      </c>
       <c r="E13" s="4" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="F13" s="6"/>
       <c r="G13" s="4" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="H13" s="4">
         <v>0</v>
@@ -1598,23 +1626,23 @@
         <v>3</v>
       </c>
       <c r="J13" s="4" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="K13" s="6" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="L13" s="6"/>
       <c r="M13" s="6"/>
       <c r="N13" s="6"/>
       <c r="O13" s="6"/>
       <c r="P13" s="4" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="Q13" s="4" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="R13" s="4" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="14" spans="1:40" x14ac:dyDescent="0.2">
@@ -1622,20 +1650,20 @@
         <v>21302</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C14" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="D14" s="4" t="s">
         <v>67</v>
       </c>
-      <c r="D14" s="4" t="s">
-        <v>68</v>
-      </c>
       <c r="E14" s="4" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="F14" s="6"/>
       <c r="G14" s="4" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="H14" s="4">
         <v>300</v>
@@ -1644,31 +1672,71 @@
         <v>3</v>
       </c>
       <c r="J14" s="4" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="K14" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="L14" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="M14" s="6" t="s">
+        <v>81</v>
+      </c>
+      <c r="N14" s="6" t="s">
         <v>76</v>
       </c>
-      <c r="L14" s="6" t="s">
-        <v>49</v>
-      </c>
-      <c r="M14" s="6" t="s">
-        <v>82</v>
-      </c>
-      <c r="N14" s="6" t="s">
-        <v>77</v>
-      </c>
       <c r="O14" s="6" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="P14" s="4" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="Q14" s="4" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="R14" s="4" t="s">
-        <v>111</v>
+        <v>110</v>
+      </c>
+    </row>
+    <row r="15" spans="1:40" x14ac:dyDescent="0.2">
+      <c r="A15" s="4">
+        <v>21401</v>
+      </c>
+      <c r="B15" s="4" t="s">
+        <v>134</v>
+      </c>
+      <c r="C15" s="4" t="s">
+        <v>135</v>
+      </c>
+      <c r="D15" s="4" t="s">
+        <v>136</v>
+      </c>
+      <c r="E15" s="4" t="s">
+        <v>137</v>
+      </c>
+      <c r="F15" s="6"/>
+      <c r="G15" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="H15" s="4">
+        <v>0</v>
+      </c>
+      <c r="I15" s="4">
+        <v>1</v>
+      </c>
+      <c r="J15" s="4"/>
+      <c r="K15" s="6"/>
+      <c r="L15" s="6"/>
+      <c r="M15" s="6"/>
+      <c r="N15" s="6"/>
+      <c r="O15" s="6"/>
+      <c r="P15" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="Q15" s="4"/>
+      <c r="R15" s="4" t="s">
+        <v>140</v>
       </c>
     </row>
   </sheetData>

--- a/Design/config/CityDevConfig.xlsx
+++ b/Design/config/CityDevConfig.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="185" uniqueCount="141">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="192" uniqueCount="144">
   <si>
     <t>序列</t>
     <phoneticPr fontId="3" type="noConversion"/>
@@ -581,6 +581,18 @@
   </si>
   <si>
     <t>wild.mp4</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>CityDevPraiseHero</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>褒奖</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>提升武将忠心度</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -979,7 +991,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AN15"/>
+  <dimension ref="A1:AN16"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9.5" bestFit="1" customWidth="1"/>
@@ -1739,6 +1751,46 @@
         <v>140</v>
       </c>
     </row>
+    <row r="16" spans="1:40" x14ac:dyDescent="0.2">
+      <c r="A16" s="4">
+        <v>21402</v>
+      </c>
+      <c r="B16" s="4" t="s">
+        <v>134</v>
+      </c>
+      <c r="C16" s="4" t="s">
+        <v>142</v>
+      </c>
+      <c r="D16" s="4" t="s">
+        <v>143</v>
+      </c>
+      <c r="E16" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="F16" s="6"/>
+      <c r="G16" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="H16" s="4">
+        <v>100</v>
+      </c>
+      <c r="I16" s="4">
+        <v>10</v>
+      </c>
+      <c r="J16" s="4"/>
+      <c r="K16" s="6"/>
+      <c r="L16" s="6"/>
+      <c r="M16" s="6"/>
+      <c r="N16" s="6"/>
+      <c r="O16" s="6"/>
+      <c r="P16" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="Q16" s="4"/>
+      <c r="R16" s="4" t="s">
+        <v>140</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A4:R14">
     <sortState ref="A5:R13">

--- a/Design/config/CityDevConfig.xlsx
+++ b/Design/config/CityDevConfig.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$4:$R$14</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$4:$U$14</definedName>
   </definedNames>
   <calcPr calcId="162913"/>
   <extLst>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="192" uniqueCount="144">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="204" uniqueCount="152">
   <si>
     <t>序列</t>
     <phoneticPr fontId="3" type="noConversion"/>
@@ -593,6 +593,38 @@
   </si>
   <si>
     <t>提升武将忠心度</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>cs</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>战时优先级</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>AiPriotyAtk</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>int</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>AiPriotyDev</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>发展时ai</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>cs</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>AiPriotyDef</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -991,7 +1023,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AN16"/>
+  <dimension ref="A1:AQ16"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9.5" bestFit="1" customWidth="1"/>
@@ -1007,11 +1039,13 @@
     <col min="14" max="14" width="14" customWidth="1"/>
     <col min="15" max="15" width="13.75" customWidth="1"/>
     <col min="16" max="16" width="14" customWidth="1"/>
-    <col min="17" max="17" width="8" customWidth="1"/>
-    <col min="18" max="18" width="9.5" customWidth="1"/>
+    <col min="17" max="18" width="8" customWidth="1"/>
+    <col min="19" max="19" width="9" customWidth="1"/>
+    <col min="20" max="20" width="7.25" customWidth="1"/>
+    <col min="21" max="21" width="9.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:40" ht="57" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:43" ht="57" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1064,10 +1098,19 @@
         <v>126</v>
       </c>
       <c r="R1" s="3" t="s">
+        <v>149</v>
+      </c>
+      <c r="S1" s="3" t="s">
+        <v>145</v>
+      </c>
+      <c r="T1" s="3" t="s">
+        <v>145</v>
+      </c>
+      <c r="U1" s="3" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="2" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
@@ -1120,10 +1163,19 @@
         <v>122</v>
       </c>
       <c r="R2" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="S2" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="T2" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="U2" s="2" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="3" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A3" s="2" t="s">
         <v>7</v>
       </c>
@@ -1176,10 +1228,19 @@
         <v>116</v>
       </c>
       <c r="R3" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="S3" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="T3" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="U3" s="2" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A4" s="2" t="s">
         <v>2</v>
       </c>
@@ -1232,10 +1293,19 @@
         <v>117</v>
       </c>
       <c r="R4" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="S4" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="T4" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="U4" s="2" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="5" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A5" s="4">
         <v>21001</v>
       </c>
@@ -1281,11 +1351,16 @@
       <c r="Q5" s="4" t="s">
         <v>118</v>
       </c>
-      <c r="R5" s="4" t="s">
+      <c r="R5" s="4">
+        <v>4</v>
+      </c>
+      <c r="S5" s="4"/>
+      <c r="T5" s="4"/>
+      <c r="U5" s="4" t="s">
         <v>123</v>
       </c>
     </row>
-    <row r="6" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A6" s="4">
         <v>21002</v>
       </c>
@@ -1331,11 +1406,16 @@
       <c r="Q6" s="4" t="s">
         <v>118</v>
       </c>
-      <c r="R6" s="4" t="s">
+      <c r="R6" s="4">
+        <v>3</v>
+      </c>
+      <c r="S6" s="4"/>
+      <c r="T6" s="4"/>
+      <c r="U6" s="4" t="s">
         <v>114</v>
       </c>
     </row>
-    <row r="7" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A7" s="4">
         <v>21101</v>
       </c>
@@ -1381,13 +1461,20 @@
       <c r="Q7" s="4" t="s">
         <v>119</v>
       </c>
-      <c r="R7" s="4" t="s">
+      <c r="R7" s="4">
+        <v>7</v>
+      </c>
+      <c r="S7" s="4"/>
+      <c r="T7" s="4">
+        <v>3</v>
+      </c>
+      <c r="U7" s="4" t="s">
         <v>131</v>
       </c>
-      <c r="AM7" s="5"/>
-      <c r="AN7" s="5"/>
+      <c r="AP7" s="5"/>
+      <c r="AQ7" s="5"/>
     </row>
-    <row r="8" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A8" s="4">
         <v>21102</v>
       </c>
@@ -1423,13 +1510,18 @@
         <v>64</v>
       </c>
       <c r="Q8" s="4"/>
-      <c r="R8" s="4" t="s">
+      <c r="R8" s="4"/>
+      <c r="S8" s="4">
+        <v>2</v>
+      </c>
+      <c r="T8" s="4"/>
+      <c r="U8" s="4" t="s">
         <v>108</v>
       </c>
-      <c r="AM8" s="5"/>
-      <c r="AN8" s="5"/>
+      <c r="AP8" s="5"/>
+      <c r="AQ8" s="5"/>
     </row>
-    <row r="9" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A9" s="4">
         <v>21103</v>
       </c>
@@ -1467,11 +1559,16 @@
         <v>47</v>
       </c>
       <c r="Q9" s="4"/>
-      <c r="R9" s="4" t="s">
+      <c r="R9" s="4"/>
+      <c r="S9" s="4">
+        <v>1</v>
+      </c>
+      <c r="T9" s="4"/>
+      <c r="U9" s="4" t="s">
         <v>109</v>
       </c>
     </row>
-    <row r="10" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A10" s="4">
         <v>21201</v>
       </c>
@@ -1517,11 +1614,20 @@
       <c r="Q10" s="4" t="s">
         <v>118</v>
       </c>
-      <c r="R10" s="4" t="s">
+      <c r="R10" s="4">
+        <v>5</v>
+      </c>
+      <c r="S10" s="4">
+        <v>5</v>
+      </c>
+      <c r="T10" s="4">
+        <v>5</v>
+      </c>
+      <c r="U10" s="4" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="11" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A11" s="4">
         <v>21202</v>
       </c>
@@ -1563,11 +1669,18 @@
       <c r="Q11" s="4" t="s">
         <v>120</v>
       </c>
-      <c r="R11" s="4" t="s">
+      <c r="R11" s="4">
+        <v>6</v>
+      </c>
+      <c r="S11" s="4"/>
+      <c r="T11" s="4">
+        <v>4</v>
+      </c>
+      <c r="U11" s="4" t="s">
         <v>113</v>
       </c>
     </row>
-    <row r="12" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A12" s="4">
         <v>21203</v>
       </c>
@@ -1607,11 +1720,14 @@
         <v>127</v>
       </c>
       <c r="Q12" s="4"/>
-      <c r="R12" s="4" t="s">
+      <c r="R12" s="4"/>
+      <c r="S12" s="4"/>
+      <c r="T12" s="4"/>
+      <c r="U12" s="4" t="s">
         <v>130</v>
       </c>
     </row>
-    <row r="13" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A13" s="4">
         <v>21301</v>
       </c>
@@ -1653,11 +1769,18 @@
       <c r="Q13" s="4" t="s">
         <v>121</v>
       </c>
-      <c r="R13" s="4" t="s">
+      <c r="R13" s="4"/>
+      <c r="S13" s="4">
+        <v>4</v>
+      </c>
+      <c r="T13" s="4">
+        <v>2</v>
+      </c>
+      <c r="U13" s="4" t="s">
         <v>112</v>
       </c>
     </row>
-    <row r="14" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A14" s="4">
         <v>21302</v>
       </c>
@@ -1707,11 +1830,18 @@
       <c r="Q14" s="4" t="s">
         <v>121</v>
       </c>
-      <c r="R14" s="4" t="s">
+      <c r="R14" s="4"/>
+      <c r="S14" s="4">
+        <v>3</v>
+      </c>
+      <c r="T14" s="4">
+        <v>1</v>
+      </c>
+      <c r="U14" s="4" t="s">
         <v>110</v>
       </c>
     </row>
-    <row r="15" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A15" s="4">
         <v>21401</v>
       </c>
@@ -1747,11 +1877,16 @@
         <v>139</v>
       </c>
       <c r="Q15" s="4"/>
-      <c r="R15" s="4" t="s">
+      <c r="R15" s="4">
+        <v>1</v>
+      </c>
+      <c r="S15" s="4"/>
+      <c r="T15" s="4"/>
+      <c r="U15" s="4" t="s">
         <v>140</v>
       </c>
     </row>
-    <row r="16" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A16" s="4">
         <v>21402</v>
       </c>
@@ -1787,12 +1922,19 @@
         <v>55</v>
       </c>
       <c r="Q16" s="4"/>
-      <c r="R16" s="4" t="s">
+      <c r="R16" s="4">
+        <v>2</v>
+      </c>
+      <c r="S16" s="4">
+        <v>6</v>
+      </c>
+      <c r="T16" s="4"/>
+      <c r="U16" s="4" t="s">
         <v>140</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:R14">
+  <autoFilter ref="A4:U14">
     <sortState ref="A5:R13">
       <sortCondition ref="A4:A13"/>
     </sortState>

--- a/Design/config/CityDevConfig.xlsx
+++ b/Design/config/CityDevConfig.xlsx
@@ -1352,7 +1352,7 @@
         <v>118</v>
       </c>
       <c r="R5" s="4">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="S5" s="4"/>
       <c r="T5" s="4"/>
@@ -1407,7 +1407,7 @@
         <v>118</v>
       </c>
       <c r="R6" s="4">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="S6" s="4"/>
       <c r="T6" s="4"/>
@@ -1462,11 +1462,11 @@
         <v>119</v>
       </c>
       <c r="R7" s="4">
-        <v>7</v>
+        <v>30</v>
       </c>
       <c r="S7" s="4"/>
       <c r="T7" s="4">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="U7" s="4" t="s">
         <v>131</v>
@@ -1512,7 +1512,7 @@
       <c r="Q8" s="4"/>
       <c r="R8" s="4"/>
       <c r="S8" s="4">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="T8" s="4"/>
       <c r="U8" s="4" t="s">
@@ -1615,13 +1615,13 @@
         <v>118</v>
       </c>
       <c r="R10" s="4">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="S10" s="4">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T10" s="4">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="U10" s="4" t="s">
         <v>111</v>
@@ -1670,11 +1670,11 @@
         <v>120</v>
       </c>
       <c r="R11" s="4">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="S11" s="4"/>
       <c r="T11" s="4">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="U11" s="4" t="s">
         <v>113</v>
@@ -1720,9 +1720,15 @@
         <v>127</v>
       </c>
       <c r="Q12" s="4"/>
-      <c r="R12" s="4"/>
-      <c r="S12" s="4"/>
-      <c r="T12" s="4"/>
+      <c r="R12" s="4">
+        <v>1</v>
+      </c>
+      <c r="S12" s="4">
+        <v>3</v>
+      </c>
+      <c r="T12" s="4">
+        <v>1</v>
+      </c>
       <c r="U12" s="4" t="s">
         <v>130</v>
       </c>
@@ -1771,10 +1777,10 @@
       </c>
       <c r="R13" s="4"/>
       <c r="S13" s="4">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="T13" s="4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="U13" s="4" t="s">
         <v>112</v>
@@ -1832,10 +1838,10 @@
       </c>
       <c r="R14" s="4"/>
       <c r="S14" s="4">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="T14" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U14" s="4" t="s">
         <v>110</v>
@@ -1878,7 +1884,7 @@
       </c>
       <c r="Q15" s="4"/>
       <c r="R15" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S15" s="4"/>
       <c r="T15" s="4"/>
@@ -1923,10 +1929,10 @@
       </c>
       <c r="Q16" s="4"/>
       <c r="R16" s="4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S16" s="4">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="T16" s="4"/>
       <c r="U16" s="4" t="s">

--- a/Design/config/CityDevConfig.xlsx
+++ b/Design/config/CityDevConfig.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$4:$U$14</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$4:$T$14</definedName>
   </definedNames>
   <calcPr calcId="162913"/>
   <extLst>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="204" uniqueCount="152">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="199" uniqueCount="149">
   <si>
     <t>序列</t>
     <phoneticPr fontId="3" type="noConversion"/>
@@ -436,22 +436,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>敌人</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>FindEnemy</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>bool</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>true</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>move2.mp4</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -625,6 +609,10 @@
   </si>
   <si>
     <t>AiPriotyDef</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>CityDevMove</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -1023,29 +1011,28 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AQ16"/>
+  <dimension ref="A1:AP16"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9.5" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="9.5" customWidth="1"/>
     <col min="3" max="3" width="9.125" customWidth="1"/>
     <col min="4" max="5" width="14" customWidth="1"/>
-    <col min="6" max="6" width="8.625" customWidth="1"/>
-    <col min="7" max="9" width="9.125" customWidth="1"/>
-    <col min="10" max="10" width="14" customWidth="1"/>
-    <col min="11" max="11" width="13.75" customWidth="1"/>
-    <col min="12" max="12" width="14" customWidth="1"/>
-    <col min="13" max="13" width="13.75" customWidth="1"/>
-    <col min="14" max="14" width="14" customWidth="1"/>
-    <col min="15" max="15" width="13.75" customWidth="1"/>
-    <col min="16" max="16" width="14" customWidth="1"/>
-    <col min="17" max="18" width="8" customWidth="1"/>
-    <col min="19" max="19" width="9" customWidth="1"/>
-    <col min="20" max="20" width="7.25" customWidth="1"/>
-    <col min="21" max="21" width="9.5" customWidth="1"/>
+    <col min="6" max="8" width="9.125" customWidth="1"/>
+    <col min="9" max="9" width="14" customWidth="1"/>
+    <col min="10" max="10" width="13.75" customWidth="1"/>
+    <col min="11" max="11" width="14" customWidth="1"/>
+    <col min="12" max="12" width="13.75" customWidth="1"/>
+    <col min="13" max="13" width="14" customWidth="1"/>
+    <col min="14" max="14" width="13.75" customWidth="1"/>
+    <col min="15" max="15" width="14" customWidth="1"/>
+    <col min="16" max="17" width="8" customWidth="1"/>
+    <col min="18" max="18" width="9" customWidth="1"/>
+    <col min="19" max="19" width="7.25" customWidth="1"/>
+    <col min="20" max="20" width="9.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:43" ht="57" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:42" ht="57" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1062,60 +1049,57 @@
         <v>94</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>104</v>
+        <v>26</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>26</v>
+        <v>95</v>
       </c>
       <c r="H1" s="3" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="I1" s="3" t="s">
-        <v>96</v>
+        <v>14</v>
       </c>
       <c r="J1" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="K1" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="K1" s="3" t="s">
+      <c r="L1" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="L1" s="3" t="s">
+      <c r="M1" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="M1" s="3" t="s">
+      <c r="N1" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="N1" s="3" t="s">
+      <c r="O1" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="O1" s="3" t="s">
-        <v>37</v>
-      </c>
       <c r="P1" s="3" t="s">
-        <v>14</v>
+        <v>122</v>
       </c>
       <c r="Q1" s="3" t="s">
-        <v>126</v>
+        <v>145</v>
       </c>
       <c r="R1" s="3" t="s">
-        <v>149</v>
+        <v>141</v>
       </c>
       <c r="S1" s="3" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="T1" s="3" t="s">
-        <v>145</v>
-      </c>
-      <c r="U1" s="3" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="2" spans="1:43" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>9</v>
@@ -1127,55 +1111,52 @@
         <v>89</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>105</v>
+        <v>27</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>31</v>
+        <v>97</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>97</v>
+        <v>84</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>84</v>
+        <v>68</v>
       </c>
       <c r="K2" s="2" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="L2" s="2" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="M2" s="2" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="N2" s="2" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="O2" s="2" t="s">
-        <v>74</v>
+        <v>15</v>
       </c>
       <c r="P2" s="2" t="s">
-        <v>15</v>
+        <v>118</v>
       </c>
       <c r="Q2" s="2" t="s">
-        <v>122</v>
+        <v>144</v>
       </c>
       <c r="R2" s="2" t="s">
-        <v>148</v>
+        <v>142</v>
       </c>
       <c r="S2" s="2" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="T2" s="2" t="s">
-        <v>151</v>
-      </c>
-      <c r="U2" s="2" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="3" spans="1:43" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A3" s="2" t="s">
         <v>7</v>
       </c>
@@ -1192,55 +1173,52 @@
         <v>90</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>106</v>
+        <v>3</v>
       </c>
       <c r="G3" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="I3" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="H3" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="I3" s="2" t="s">
-        <v>98</v>
-      </c>
       <c r="J3" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="K3" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="K3" s="2" t="s">
+      <c r="L3" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="L3" s="2" t="s">
+      <c r="M3" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="M3" s="2" t="s">
+      <c r="N3" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="N3" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="O3" s="2" t="s">
-        <v>69</v>
+        <v>16</v>
       </c>
       <c r="P3" s="2" t="s">
-        <v>16</v>
+        <v>112</v>
       </c>
       <c r="Q3" s="2" t="s">
-        <v>116</v>
+        <v>143</v>
       </c>
       <c r="R3" s="2" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="S3" s="2" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="T3" s="2" t="s">
-        <v>147</v>
-      </c>
-      <c r="U3" s="2" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:43" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A4" s="2" t="s">
         <v>2</v>
       </c>
@@ -1257,22 +1235,22 @@
         <v>91</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>91</v>
+        <v>4</v>
       </c>
       <c r="G4" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="I4" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="H4" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="I4" s="2" t="s">
-        <v>99</v>
-      </c>
       <c r="J4" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="K4" s="2" t="s">
         <v>4</v>
-      </c>
-      <c r="K4" s="2" t="s">
-        <v>38</v>
       </c>
       <c r="L4" s="2" t="s">
         <v>4</v>
@@ -1284,28 +1262,25 @@
         <v>4</v>
       </c>
       <c r="O4" s="2" t="s">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="P4" s="2" t="s">
-        <v>17</v>
+        <v>113</v>
       </c>
       <c r="Q4" s="2" t="s">
-        <v>117</v>
+        <v>146</v>
       </c>
       <c r="R4" s="2" t="s">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="S4" s="2" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="T4" s="2" t="s">
-        <v>144</v>
-      </c>
-      <c r="U4" s="2" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="5" spans="1:43" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A5" s="4">
         <v>21001</v>
       </c>
@@ -1321,46 +1296,45 @@
       <c r="E5" s="4" t="s">
         <v>92</v>
       </c>
-      <c r="F5" s="6"/>
-      <c r="G5" s="4" t="s">
+      <c r="F5" s="4" t="s">
         <v>20</v>
       </c>
+      <c r="G5" s="4">
+        <v>300</v>
+      </c>
       <c r="H5" s="4">
-        <v>300</v>
-      </c>
-      <c r="I5" s="4">
         <v>3</v>
       </c>
-      <c r="J5" s="4" t="s">
+      <c r="I5" s="4" t="s">
         <v>29</v>
       </c>
+      <c r="J5" s="6" t="s">
+        <v>70</v>
+      </c>
       <c r="K5" s="6" t="s">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="L5" s="6" t="s">
-        <v>76</v>
-      </c>
-      <c r="M5" s="6" t="s">
         <v>77</v>
       </c>
+      <c r="M5" s="6"/>
       <c r="N5" s="6"/>
-      <c r="O5" s="6"/>
+      <c r="O5" s="4" t="s">
+        <v>18</v>
+      </c>
       <c r="P5" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="Q5" s="4" t="s">
-        <v>118</v>
-      </c>
-      <c r="R5" s="4">
+        <v>114</v>
+      </c>
+      <c r="Q5" s="4">
         <v>11</v>
       </c>
+      <c r="R5" s="4"/>
       <c r="S5" s="4"/>
-      <c r="T5" s="4"/>
-      <c r="U5" s="4" t="s">
-        <v>123</v>
+      <c r="T5" s="4" t="s">
+        <v>119</v>
       </c>
     </row>
-    <row r="6" spans="1:43" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A6" s="4">
         <v>21002</v>
       </c>
@@ -1376,46 +1350,45 @@
       <c r="E6" s="4" t="s">
         <v>92</v>
       </c>
-      <c r="F6" s="6"/>
-      <c r="G6" s="4" t="s">
+      <c r="F6" s="4" t="s">
         <v>28</v>
       </c>
+      <c r="G6" s="4">
+        <v>300</v>
+      </c>
       <c r="H6" s="4">
-        <v>300</v>
-      </c>
-      <c r="I6" s="4">
         <v>3</v>
       </c>
-      <c r="J6" s="4" t="s">
+      <c r="I6" s="4" t="s">
         <v>30</v>
       </c>
+      <c r="J6" s="6" t="s">
+        <v>70</v>
+      </c>
       <c r="K6" s="6" t="s">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="L6" s="6" t="s">
-        <v>76</v>
-      </c>
-      <c r="M6" s="6" t="s">
         <v>77</v>
       </c>
+      <c r="M6" s="6"/>
       <c r="N6" s="6"/>
-      <c r="O6" s="6"/>
+      <c r="O6" s="4" t="s">
+        <v>19</v>
+      </c>
       <c r="P6" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="Q6" s="4" t="s">
-        <v>118</v>
-      </c>
-      <c r="R6" s="4">
+        <v>114</v>
+      </c>
+      <c r="Q6" s="4">
         <v>10</v>
       </c>
+      <c r="R6" s="4"/>
       <c r="S6" s="4"/>
-      <c r="T6" s="4"/>
-      <c r="U6" s="4" t="s">
-        <v>114</v>
+      <c r="T6" s="4" t="s">
+        <v>110</v>
       </c>
     </row>
-    <row r="7" spans="1:43" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A7" s="4">
         <v>21101</v>
       </c>
@@ -1431,50 +1404,49 @@
       <c r="E7" s="4" t="s">
         <v>92</v>
       </c>
-      <c r="F7" s="6"/>
-      <c r="G7" s="4" t="s">
+      <c r="F7" s="4" t="s">
         <v>46</v>
       </c>
+      <c r="G7" s="4">
+        <v>200</v>
+      </c>
       <c r="H7" s="4">
-        <v>200</v>
-      </c>
-      <c r="I7" s="4">
         <v>3</v>
       </c>
-      <c r="J7" s="4" t="s">
+      <c r="I7" s="4" t="s">
         <v>45</v>
       </c>
+      <c r="J7" s="6" t="s">
+        <v>82</v>
+      </c>
       <c r="K7" s="6" t="s">
-        <v>82</v>
+        <v>48</v>
       </c>
       <c r="L7" s="6" t="s">
-        <v>48</v>
-      </c>
-      <c r="M7" s="6" t="s">
         <v>78</v>
       </c>
+      <c r="M7" s="6"/>
       <c r="N7" s="6"/>
-      <c r="O7" s="6"/>
+      <c r="O7" s="4" t="s">
+        <v>44</v>
+      </c>
       <c r="P7" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="Q7" s="4" t="s">
-        <v>119</v>
-      </c>
-      <c r="R7" s="4">
+        <v>115</v>
+      </c>
+      <c r="Q7" s="4">
         <v>30</v>
       </c>
-      <c r="S7" s="4"/>
-      <c r="T7" s="4">
+      <c r="R7" s="4"/>
+      <c r="S7" s="4">
         <v>10</v>
       </c>
-      <c r="U7" s="4" t="s">
-        <v>131</v>
-      </c>
+      <c r="T7" s="4" t="s">
+        <v>127</v>
+      </c>
+      <c r="AO7" s="5"/>
       <c r="AP7" s="5"/>
-      <c r="AQ7" s="5"/>
     </row>
-    <row r="8" spans="1:43" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A8" s="4">
         <v>21102</v>
       </c>
@@ -1485,43 +1457,42 @@
         <v>102</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>93</v>
-      </c>
-      <c r="F8" s="6"/>
-      <c r="G8" s="4" t="s">
+        <v>148</v>
+      </c>
+      <c r="F8" s="4" t="s">
         <v>103</v>
       </c>
+      <c r="G8" s="4">
+        <v>0</v>
+      </c>
       <c r="H8" s="4">
-        <v>0</v>
-      </c>
-      <c r="I8" s="4">
         <v>10</v>
       </c>
-      <c r="J8" s="4"/>
+      <c r="I8" s="4"/>
+      <c r="J8" s="6"/>
       <c r="K8" s="6"/>
       <c r="L8" s="6"/>
       <c r="M8" s="6"/>
       <c r="N8" s="6"/>
-      <c r="O8" s="6"/>
-      <c r="P8" s="4" t="s">
+      <c r="O8" s="4" t="s">
         <v>64</v>
       </c>
+      <c r="P8" s="4"/>
       <c r="Q8" s="4"/>
-      <c r="R8" s="4"/>
-      <c r="S8" s="4">
+      <c r="R8" s="4">
         <v>4</v>
       </c>
-      <c r="T8" s="4"/>
-      <c r="U8" s="4" t="s">
-        <v>108</v>
-      </c>
+      <c r="S8" s="4"/>
+      <c r="T8" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="AO8" s="5"/>
       <c r="AP8" s="5"/>
-      <c r="AQ8" s="5"/>
     </row>
-    <row r="9" spans="1:43" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A9" s="4">
         <v>21103</v>
       </c>
@@ -1537,38 +1508,35 @@
       <c r="E9" s="4" t="s">
         <v>93</v>
       </c>
-      <c r="F9" s="6" t="s">
-        <v>107</v>
-      </c>
-      <c r="G9" s="4" t="s">
+      <c r="F9" s="4" t="s">
         <v>100</v>
       </c>
+      <c r="G9" s="4">
+        <v>0</v>
+      </c>
       <c r="H9" s="4">
-        <v>0</v>
-      </c>
-      <c r="I9" s="4">
         <v>10</v>
       </c>
-      <c r="J9" s="4"/>
+      <c r="I9" s="4"/>
+      <c r="J9" s="6"/>
       <c r="K9" s="6"/>
       <c r="L9" s="6"/>
       <c r="M9" s="6"/>
       <c r="N9" s="6"/>
-      <c r="O9" s="6"/>
-      <c r="P9" s="4" t="s">
+      <c r="O9" s="4" t="s">
         <v>47</v>
       </c>
+      <c r="P9" s="4"/>
       <c r="Q9" s="4"/>
-      <c r="R9" s="4"/>
-      <c r="S9" s="4">
+      <c r="R9" s="4">
         <v>1</v>
       </c>
-      <c r="T9" s="4"/>
-      <c r="U9" s="4" t="s">
-        <v>109</v>
+      <c r="S9" s="4"/>
+      <c r="T9" s="4" t="s">
+        <v>105</v>
       </c>
     </row>
-    <row r="10" spans="1:43" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A10" s="4">
         <v>21201</v>
       </c>
@@ -1584,50 +1552,49 @@
       <c r="E10" s="4" t="s">
         <v>92</v>
       </c>
-      <c r="F10" s="6"/>
-      <c r="G10" s="4" t="s">
+      <c r="F10" s="4" t="s">
         <v>49</v>
       </c>
+      <c r="G10" s="4">
+        <v>150</v>
+      </c>
       <c r="H10" s="4">
-        <v>150</v>
-      </c>
-      <c r="I10" s="4">
         <v>3</v>
       </c>
-      <c r="J10" s="4" t="s">
+      <c r="I10" s="4" t="s">
         <v>48</v>
       </c>
+      <c r="J10" s="6" t="s">
+        <v>80</v>
+      </c>
       <c r="K10" s="6" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="L10" s="6" t="s">
-        <v>76</v>
-      </c>
-      <c r="M10" s="6" t="s">
         <v>83</v>
       </c>
+      <c r="M10" s="6"/>
       <c r="N10" s="6"/>
-      <c r="O10" s="6"/>
+      <c r="O10" s="4" t="s">
+        <v>43</v>
+      </c>
       <c r="P10" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="Q10" s="4" t="s">
-        <v>118</v>
+        <v>114</v>
+      </c>
+      <c r="Q10" s="4">
+        <v>20</v>
       </c>
       <c r="R10" s="4">
+        <v>10</v>
+      </c>
+      <c r="S10" s="4">
         <v>20</v>
       </c>
-      <c r="S10" s="4">
-        <v>10</v>
-      </c>
-      <c r="T10" s="4">
-        <v>20</v>
-      </c>
-      <c r="U10" s="4" t="s">
-        <v>111</v>
+      <c r="T10" s="4" t="s">
+        <v>107</v>
       </c>
     </row>
-    <row r="11" spans="1:43" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A11" s="4">
         <v>21202</v>
       </c>
@@ -1643,44 +1610,43 @@
       <c r="E11" s="4" t="s">
         <v>92</v>
       </c>
-      <c r="F11" s="6"/>
-      <c r="G11" s="4" t="s">
+      <c r="F11" s="4" t="s">
         <v>56</v>
       </c>
+      <c r="G11" s="4">
+        <v>0</v>
+      </c>
       <c r="H11" s="4">
-        <v>0</v>
-      </c>
-      <c r="I11" s="4">
         <v>10</v>
       </c>
-      <c r="J11" s="4" t="s">
+      <c r="I11" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="K11" s="6" t="s">
+      <c r="J11" s="6" t="s">
         <v>86</v>
       </c>
+      <c r="K11" s="6"/>
       <c r="L11" s="6"/>
       <c r="M11" s="6"/>
       <c r="N11" s="6"/>
-      <c r="O11" s="6"/>
+      <c r="O11" s="4" t="s">
+        <v>55</v>
+      </c>
       <c r="P11" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="Q11" s="4" t="s">
-        <v>120</v>
-      </c>
-      <c r="R11" s="4">
+        <v>116</v>
+      </c>
+      <c r="Q11" s="4">
         <v>21</v>
       </c>
-      <c r="S11" s="4"/>
-      <c r="T11" s="4">
+      <c r="R11" s="4"/>
+      <c r="S11" s="4">
         <v>11</v>
       </c>
-      <c r="U11" s="4" t="s">
-        <v>113</v>
+      <c r="T11" s="4" t="s">
+        <v>109</v>
       </c>
     </row>
-    <row r="12" spans="1:43" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A12" s="4">
         <v>21203</v>
       </c>
@@ -1688,52 +1654,51 @@
         <v>52</v>
       </c>
       <c r="C12" s="4" t="s">
+        <v>124</v>
+      </c>
+      <c r="D12" s="4" t="s">
+        <v>121</v>
+      </c>
+      <c r="E12" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="F12" s="4" t="s">
+        <v>125</v>
+      </c>
+      <c r="G12" s="4">
+        <v>0</v>
+      </c>
+      <c r="H12" s="4">
+        <v>1</v>
+      </c>
+      <c r="I12" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="J12" s="6"/>
+      <c r="K12" s="6" t="s">
         <v>128</v>
       </c>
-      <c r="D12" s="4" t="s">
-        <v>125</v>
-      </c>
-      <c r="E12" s="4" t="s">
-        <v>124</v>
-      </c>
-      <c r="F12" s="6"/>
-      <c r="G12" s="4" t="s">
-        <v>129</v>
-      </c>
-      <c r="H12" s="4">
-        <v>0</v>
-      </c>
-      <c r="I12" s="4">
-        <v>1</v>
-      </c>
-      <c r="J12" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="K12" s="6"/>
-      <c r="L12" s="6" t="s">
-        <v>132</v>
-      </c>
+      <c r="L12" s="6"/>
       <c r="M12" s="6"/>
       <c r="N12" s="6"/>
-      <c r="O12" s="6"/>
-      <c r="P12" s="4" t="s">
-        <v>127</v>
-      </c>
-      <c r="Q12" s="4"/>
+      <c r="O12" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="P12" s="4"/>
+      <c r="Q12" s="4">
+        <v>1</v>
+      </c>
       <c r="R12" s="4">
+        <v>3</v>
+      </c>
+      <c r="S12" s="4">
         <v>1</v>
       </c>
-      <c r="S12" s="4">
-        <v>3</v>
-      </c>
-      <c r="T12" s="4">
-        <v>1</v>
-      </c>
-      <c r="U12" s="4" t="s">
-        <v>130</v>
+      <c r="T12" s="4" t="s">
+        <v>126</v>
       </c>
     </row>
-    <row r="13" spans="1:43" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A13" s="4">
         <v>21301</v>
       </c>
@@ -1749,44 +1714,43 @@
       <c r="E13" s="4" t="s">
         <v>92</v>
       </c>
-      <c r="F13" s="6"/>
-      <c r="G13" s="4" t="s">
+      <c r="F13" s="4" t="s">
         <v>61</v>
       </c>
+      <c r="G13" s="4">
+        <v>0</v>
+      </c>
       <c r="H13" s="4">
-        <v>0</v>
-      </c>
-      <c r="I13" s="4">
         <v>3</v>
       </c>
-      <c r="J13" s="4" t="s">
+      <c r="I13" s="4" t="s">
         <v>58</v>
       </c>
-      <c r="K13" s="6" t="s">
+      <c r="J13" s="6" t="s">
         <v>79</v>
       </c>
+      <c r="K13" s="6"/>
       <c r="L13" s="6"/>
       <c r="M13" s="6"/>
       <c r="N13" s="6"/>
-      <c r="O13" s="6"/>
+      <c r="O13" s="4" t="s">
+        <v>47</v>
+      </c>
       <c r="P13" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="Q13" s="4" t="s">
-        <v>121</v>
-      </c>
-      <c r="R13" s="4"/>
+        <v>117</v>
+      </c>
+      <c r="Q13" s="4"/>
+      <c r="R13" s="4">
+        <v>9</v>
+      </c>
       <c r="S13" s="4">
-        <v>9</v>
-      </c>
-      <c r="T13" s="4">
         <v>3</v>
       </c>
-      <c r="U13" s="4" t="s">
-        <v>112</v>
+      <c r="T13" s="4" t="s">
+        <v>108</v>
       </c>
     </row>
-    <row r="14" spans="1:43" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A14" s="4">
         <v>21302</v>
       </c>
@@ -1802,145 +1766,142 @@
       <c r="E14" s="4" t="s">
         <v>92</v>
       </c>
-      <c r="F14" s="6"/>
-      <c r="G14" s="4" t="s">
+      <c r="F14" s="4" t="s">
         <v>63</v>
       </c>
+      <c r="G14" s="4">
+        <v>300</v>
+      </c>
       <c r="H14" s="4">
-        <v>300</v>
-      </c>
-      <c r="I14" s="4">
         <v>3</v>
       </c>
-      <c r="J14" s="4" t="s">
+      <c r="I14" s="4" t="s">
         <v>65</v>
       </c>
+      <c r="J14" s="6" t="s">
+        <v>75</v>
+      </c>
       <c r="K14" s="6" t="s">
-        <v>75</v>
+        <v>48</v>
       </c>
       <c r="L14" s="6" t="s">
-        <v>48</v>
+        <v>81</v>
       </c>
       <c r="M14" s="6" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="N14" s="6" t="s">
-        <v>76</v>
-      </c>
-      <c r="O14" s="6" t="s">
         <v>85</v>
       </c>
+      <c r="O14" s="4" t="s">
+        <v>64</v>
+      </c>
       <c r="P14" s="4" t="s">
-        <v>64</v>
-      </c>
-      <c r="Q14" s="4" t="s">
-        <v>121</v>
-      </c>
-      <c r="R14" s="4"/>
+        <v>117</v>
+      </c>
+      <c r="Q14" s="4"/>
+      <c r="R14" s="4">
+        <v>8</v>
+      </c>
       <c r="S14" s="4">
-        <v>8</v>
-      </c>
-      <c r="T14" s="4">
         <v>2</v>
       </c>
-      <c r="U14" s="4" t="s">
-        <v>110</v>
+      <c r="T14" s="4" t="s">
+        <v>106</v>
       </c>
     </row>
-    <row r="15" spans="1:43" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A15" s="4">
         <v>21401</v>
       </c>
       <c r="B15" s="4" t="s">
+        <v>130</v>
+      </c>
+      <c r="C15" s="4" t="s">
+        <v>131</v>
+      </c>
+      <c r="D15" s="4" t="s">
+        <v>132</v>
+      </c>
+      <c r="E15" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="F15" s="4" t="s">
         <v>134</v>
       </c>
-      <c r="C15" s="4" t="s">
-        <v>135</v>
-      </c>
-      <c r="D15" s="4" t="s">
-        <v>136</v>
-      </c>
-      <c r="E15" s="4" t="s">
-        <v>137</v>
-      </c>
-      <c r="F15" s="6"/>
-      <c r="G15" s="4" t="s">
-        <v>138</v>
+      <c r="G15" s="4">
+        <v>0</v>
       </c>
       <c r="H15" s="4">
-        <v>0</v>
-      </c>
-      <c r="I15" s="4">
         <v>1</v>
       </c>
-      <c r="J15" s="4"/>
+      <c r="I15" s="4"/>
+      <c r="J15" s="6"/>
       <c r="K15" s="6"/>
       <c r="L15" s="6"/>
       <c r="M15" s="6"/>
       <c r="N15" s="6"/>
-      <c r="O15" s="6"/>
-      <c r="P15" s="4" t="s">
-        <v>139</v>
-      </c>
-      <c r="Q15" s="4"/>
-      <c r="R15" s="4">
+      <c r="O15" s="4" t="s">
+        <v>135</v>
+      </c>
+      <c r="P15" s="4"/>
+      <c r="Q15" s="4">
         <v>2</v>
       </c>
+      <c r="R15" s="4"/>
       <c r="S15" s="4"/>
-      <c r="T15" s="4"/>
-      <c r="U15" s="4" t="s">
-        <v>140</v>
+      <c r="T15" s="4" t="s">
+        <v>136</v>
       </c>
     </row>
-    <row r="16" spans="1:43" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A16" s="4">
         <v>21402</v>
       </c>
       <c r="B16" s="4" t="s">
+        <v>130</v>
+      </c>
+      <c r="C16" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="D16" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="E16" s="4" t="s">
+        <v>137</v>
+      </c>
+      <c r="F16" s="4" t="s">
         <v>134</v>
       </c>
-      <c r="C16" s="4" t="s">
-        <v>142</v>
-      </c>
-      <c r="D16" s="4" t="s">
-        <v>143</v>
-      </c>
-      <c r="E16" s="4" t="s">
-        <v>141</v>
-      </c>
-      <c r="F16" s="6"/>
-      <c r="G16" s="4" t="s">
-        <v>138</v>
+      <c r="G16" s="4">
+        <v>100</v>
       </c>
       <c r="H16" s="4">
-        <v>100</v>
-      </c>
-      <c r="I16" s="4">
         <v>10</v>
       </c>
-      <c r="J16" s="4"/>
+      <c r="I16" s="4"/>
+      <c r="J16" s="6"/>
       <c r="K16" s="6"/>
       <c r="L16" s="6"/>
       <c r="M16" s="6"/>
       <c r="N16" s="6"/>
-      <c r="O16" s="6"/>
-      <c r="P16" s="4" t="s">
+      <c r="O16" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="Q16" s="4"/>
+      <c r="P16" s="4"/>
+      <c r="Q16" s="4">
+        <v>3</v>
+      </c>
       <c r="R16" s="4">
-        <v>3</v>
-      </c>
-      <c r="S16" s="4">
         <v>12</v>
       </c>
-      <c r="T16" s="4"/>
-      <c r="U16" s="4" t="s">
-        <v>140</v>
+      <c r="S16" s="4"/>
+      <c r="T16" s="4" t="s">
+        <v>136</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:U14">
+  <autoFilter ref="A4:T14">
     <sortState ref="A5:R13">
       <sortCondition ref="A4:A13"/>
     </sortState>

--- a/Design/config/CityDevConfig.xlsx
+++ b/Design/config/CityDevConfig.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="199" uniqueCount="149">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="199" uniqueCount="150">
   <si>
     <t>序列</t>
     <phoneticPr fontId="3" type="noConversion"/>
@@ -613,6 +613,10 @@
   </si>
   <si>
     <t>CityDevMove</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>praise</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -1871,7 +1875,7 @@
         <v>137</v>
       </c>
       <c r="F16" s="4" t="s">
-        <v>134</v>
+        <v>149</v>
       </c>
       <c r="G16" s="4">
         <v>100</v>

--- a/Design/config/CityDevConfig.xlsx
+++ b/Design/config/CityDevConfig.xlsx
@@ -1485,11 +1485,15 @@
         <v>64</v>
       </c>
       <c r="P8" s="4"/>
-      <c r="Q8" s="4"/>
+      <c r="Q8" s="4">
+        <v>28</v>
+      </c>
       <c r="R8" s="4">
         <v>4</v>
       </c>
-      <c r="S8" s="4"/>
+      <c r="S8" s="4">
+        <v>9</v>
+      </c>
       <c r="T8" s="4" t="s">
         <v>104</v>
       </c>

--- a/Design/config/CityDevConfig.xlsx
+++ b/Design/config/CityDevConfig.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="172" uniqueCount="136">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="170" uniqueCount="128">
   <si>
     <t>序列</t>
     <phoneticPr fontId="3" type="noConversion"/>
@@ -126,14 +126,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>ArchFood</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>ArchGold</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>GoldCost</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -198,10 +190,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>Secure</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>走访</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -266,10 +254,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>4,10</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>DevAttr2</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -286,46 +270,14 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>200,600</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>ArchPeople</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>300,800</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>1,3</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>3,9</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>-2,-5</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>6,15</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>DevAttr1</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>-500,-1500</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>20,100</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>出战</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -562,6 +514,22 @@
   </si>
   <si>
     <t>Icon</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>1,2</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Exp</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>5,10</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>2,5</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -988,52 +956,52 @@
         <v>10</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>83</v>
+        <v>71</v>
       </c>
       <c r="E1" s="3" t="s">
         <v>24</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>84</v>
+        <v>72</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>85</v>
+        <v>73</v>
       </c>
       <c r="H1" s="3" t="s">
         <v>14</v>
       </c>
       <c r="I1" s="3" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="J1" s="3" t="s">
         <v>14</v>
       </c>
       <c r="K1" s="3" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="L1" s="3" t="s">
         <v>14</v>
       </c>
       <c r="M1" s="3" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="N1" s="3" t="s">
         <v>14</v>
       </c>
       <c r="O1" s="3" t="s">
-        <v>109</v>
+        <v>97</v>
       </c>
       <c r="P1" s="3" t="s">
-        <v>130</v>
+        <v>118</v>
       </c>
       <c r="Q1" s="3" t="s">
-        <v>126</v>
+        <v>114</v>
       </c>
       <c r="R1" s="3" t="s">
-        <v>126</v>
+        <v>114</v>
       </c>
       <c r="S1" s="3" t="s">
         <v>11</v>
@@ -1047,52 +1015,52 @@
         <v>9</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>78</v>
+        <v>66</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>135</v>
+        <v>123</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>86</v>
+        <v>74</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>73</v>
+        <v>63</v>
       </c>
       <c r="I2" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="J2" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="K2" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="J2" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="K2" s="2" t="s">
-        <v>63</v>
-      </c>
       <c r="L2" s="2" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="M2" s="2" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="N2" s="2" t="s">
         <v>15</v>
       </c>
       <c r="O2" s="2" t="s">
-        <v>105</v>
+        <v>93</v>
       </c>
       <c r="P2" s="2" t="s">
-        <v>129</v>
+        <v>117</v>
       </c>
       <c r="Q2" s="2" t="s">
-        <v>127</v>
+        <v>115</v>
       </c>
       <c r="R2" s="2" t="s">
-        <v>132</v>
+        <v>120</v>
       </c>
       <c r="S2" s="2" t="s">
         <v>12</v>
@@ -1109,49 +1077,49 @@
         <v>21</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>79</v>
+        <v>67</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>3</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>87</v>
+        <v>75</v>
       </c>
       <c r="H3" s="2" t="s">
         <v>3</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="J3" s="2" t="s">
         <v>3</v>
       </c>
       <c r="K3" s="2" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="L3" s="2" t="s">
         <v>3</v>
       </c>
       <c r="M3" s="2" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="N3" s="2" t="s">
         <v>16</v>
       </c>
       <c r="O3" s="2" t="s">
-        <v>99</v>
+        <v>87</v>
       </c>
       <c r="P3" s="2" t="s">
-        <v>128</v>
+        <v>116</v>
       </c>
       <c r="Q3" s="2" t="s">
-        <v>128</v>
+        <v>116</v>
       </c>
       <c r="R3" s="2" t="s">
-        <v>128</v>
+        <v>116</v>
       </c>
       <c r="S3" s="2" t="s">
         <v>13</v>
@@ -1165,25 +1133,25 @@
         <v>5</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>80</v>
+        <v>68</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>4</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>88</v>
+        <v>76</v>
       </c>
       <c r="H4" s="2" t="s">
         <v>4</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="J4" s="2" t="s">
         <v>4</v>
@@ -1201,16 +1169,16 @@
         <v>17</v>
       </c>
       <c r="O4" s="2" t="s">
-        <v>100</v>
+        <v>88</v>
       </c>
       <c r="P4" s="2" t="s">
-        <v>131</v>
+        <v>119</v>
       </c>
       <c r="Q4" s="2" t="s">
-        <v>125</v>
+        <v>113</v>
       </c>
       <c r="R4" s="2" t="s">
-        <v>125</v>
+        <v>113</v>
       </c>
       <c r="S4" s="2" t="s">
         <v>8</v>
@@ -1224,10 +1192,10 @@
         <v>22</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>81</v>
+        <v>69</v>
       </c>
       <c r="E5" s="4" t="s">
         <v>20</v>
@@ -1239,16 +1207,16 @@
         <v>3</v>
       </c>
       <c r="H5" s="4" t="s">
-        <v>26</v>
+        <v>103</v>
       </c>
       <c r="I5" s="6" t="s">
-        <v>61</v>
+        <v>126</v>
       </c>
       <c r="J5" s="6" t="s">
-        <v>67</v>
+        <v>125</v>
       </c>
       <c r="K5" s="6" t="s">
-        <v>68</v>
+        <v>127</v>
       </c>
       <c r="L5" s="6"/>
       <c r="M5" s="6"/>
@@ -1256,7 +1224,7 @@
         <v>18</v>
       </c>
       <c r="O5" s="4" t="s">
-        <v>101</v>
+        <v>89</v>
       </c>
       <c r="P5" s="4">
         <v>11</v>
@@ -1264,7 +1232,7 @@
       <c r="Q5" s="4"/>
       <c r="R5" s="4"/>
       <c r="S5" s="4" t="s">
-        <v>106</v>
+        <v>94</v>
       </c>
     </row>
     <row r="6" spans="1:41" x14ac:dyDescent="0.2">
@@ -1275,10 +1243,10 @@
         <v>23</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>81</v>
+        <v>69</v>
       </c>
       <c r="E6" s="4" t="s">
         <v>25</v>
@@ -1290,16 +1258,16 @@
         <v>3</v>
       </c>
       <c r="H6" s="4" t="s">
-        <v>27</v>
+        <v>46</v>
       </c>
       <c r="I6" s="6" t="s">
-        <v>61</v>
+        <v>126</v>
       </c>
       <c r="J6" s="6" t="s">
-        <v>67</v>
+        <v>125</v>
       </c>
       <c r="K6" s="6" t="s">
-        <v>68</v>
+        <v>127</v>
       </c>
       <c r="L6" s="6"/>
       <c r="M6" s="6"/>
@@ -1307,7 +1275,7 @@
         <v>19</v>
       </c>
       <c r="O6" s="4" t="s">
-        <v>101</v>
+        <v>89</v>
       </c>
       <c r="P6" s="4">
         <v>10</v>
@@ -1315,7 +1283,7 @@
       <c r="Q6" s="4"/>
       <c r="R6" s="4"/>
       <c r="S6" s="4" t="s">
-        <v>97</v>
+        <v>85</v>
       </c>
     </row>
     <row r="7" spans="1:41" x14ac:dyDescent="0.2">
@@ -1323,16 +1291,16 @@
         <v>21101</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>81</v>
+        <v>69</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="F7" s="4">
         <v>200</v>
@@ -1341,24 +1309,24 @@
         <v>3</v>
       </c>
       <c r="H7" s="4" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="I7" s="6" t="s">
-        <v>72</v>
+        <v>126</v>
       </c>
       <c r="J7" s="6" t="s">
-        <v>44</v>
+        <v>125</v>
       </c>
       <c r="K7" s="6" t="s">
-        <v>69</v>
+        <v>127</v>
       </c>
       <c r="L7" s="6"/>
       <c r="M7" s="6"/>
       <c r="N7" s="4" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="O7" s="4" t="s">
-        <v>102</v>
+        <v>90</v>
       </c>
       <c r="P7" s="4">
         <v>30</v>
@@ -1368,7 +1336,7 @@
         <v>10</v>
       </c>
       <c r="S7" s="4" t="s">
-        <v>114</v>
+        <v>102</v>
       </c>
       <c r="AN7" s="5"/>
       <c r="AO7" s="5"/>
@@ -1378,16 +1346,16 @@
         <v>21102</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>98</v>
+        <v>86</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>133</v>
+        <v>121</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="F8" s="4">
         <v>0</v>
@@ -1402,7 +1370,7 @@
       <c r="L8" s="6"/>
       <c r="M8" s="6"/>
       <c r="N8" s="4" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="O8" s="4"/>
       <c r="P8" s="4">
@@ -1415,7 +1383,7 @@
         <v>9</v>
       </c>
       <c r="S8" s="4" t="s">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="AN8" s="5"/>
       <c r="AO8" s="5"/>
@@ -1425,16 +1393,16 @@
         <v>21103</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>76</v>
+        <v>64</v>
       </c>
       <c r="C9" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="D9" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="E9" s="4" t="s">
         <v>77</v>
-      </c>
-      <c r="D9" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="E9" s="4" t="s">
-        <v>89</v>
       </c>
       <c r="F9" s="4">
         <v>0</v>
@@ -1449,7 +1417,7 @@
       <c r="L9" s="6"/>
       <c r="M9" s="6"/>
       <c r="N9" s="4" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="O9" s="4"/>
       <c r="P9" s="4"/>
@@ -1458,7 +1426,7 @@
       </c>
       <c r="R9" s="4"/>
       <c r="S9" s="4" t="s">
-        <v>93</v>
+        <v>81</v>
       </c>
     </row>
     <row r="10" spans="1:41" x14ac:dyDescent="0.2">
@@ -1466,16 +1434,16 @@
         <v>21202</v>
       </c>
       <c r="B10" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="C10" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="D10" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="E10" s="4" t="s">
         <v>45</v>
-      </c>
-      <c r="C10" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="D10" s="4" t="s">
-        <v>81</v>
-      </c>
-      <c r="E10" s="4" t="s">
-        <v>48</v>
       </c>
       <c r="F10" s="4">
         <v>0</v>
@@ -1484,20 +1452,20 @@
         <v>10</v>
       </c>
       <c r="H10" s="4" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="I10" s="6" t="s">
-        <v>75</v>
+        <v>124</v>
       </c>
       <c r="J10" s="6"/>
       <c r="K10" s="6"/>
       <c r="L10" s="6"/>
       <c r="M10" s="6"/>
       <c r="N10" s="4" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="O10" s="4" t="s">
-        <v>103</v>
+        <v>91</v>
       </c>
       <c r="P10" s="4">
         <v>21</v>
@@ -1507,7 +1475,7 @@
         <v>11</v>
       </c>
       <c r="S10" s="4" t="s">
-        <v>96</v>
+        <v>84</v>
       </c>
     </row>
     <row r="11" spans="1:41" x14ac:dyDescent="0.2">
@@ -1515,16 +1483,16 @@
         <v>21203</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>111</v>
+        <v>99</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>108</v>
+        <v>96</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>107</v>
+        <v>95</v>
       </c>
       <c r="E11" s="4" t="s">
-        <v>112</v>
+        <v>100</v>
       </c>
       <c r="F11" s="4">
         <v>0</v>
@@ -1533,17 +1501,17 @@
         <v>1</v>
       </c>
       <c r="H11" s="4" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="I11" s="6"/>
       <c r="J11" s="6" t="s">
-        <v>115</v>
+        <v>103</v>
       </c>
       <c r="K11" s="6"/>
       <c r="L11" s="6"/>
       <c r="M11" s="6"/>
       <c r="N11" s="4" t="s">
-        <v>110</v>
+        <v>98</v>
       </c>
       <c r="O11" s="4"/>
       <c r="P11" s="4">
@@ -1556,7 +1524,7 @@
         <v>1</v>
       </c>
       <c r="S11" s="4" t="s">
-        <v>113</v>
+        <v>101</v>
       </c>
     </row>
     <row r="12" spans="1:41" x14ac:dyDescent="0.2">
@@ -1564,16 +1532,16 @@
         <v>21301</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>81</v>
+        <v>69</v>
       </c>
       <c r="E12" s="4" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="F12" s="4">
         <v>0</v>
@@ -1582,20 +1550,20 @@
         <v>3</v>
       </c>
       <c r="H12" s="4" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="I12" s="6" t="s">
-        <v>70</v>
+        <v>62</v>
       </c>
       <c r="J12" s="6"/>
       <c r="K12" s="6"/>
       <c r="L12" s="6"/>
       <c r="M12" s="6"/>
       <c r="N12" s="4" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="O12" s="4" t="s">
-        <v>104</v>
+        <v>92</v>
       </c>
       <c r="P12" s="4"/>
       <c r="Q12" s="4">
@@ -1605,7 +1573,7 @@
         <v>3</v>
       </c>
       <c r="S12" s="4" t="s">
-        <v>95</v>
+        <v>83</v>
       </c>
     </row>
     <row r="13" spans="1:41" x14ac:dyDescent="0.2">
@@ -1613,16 +1581,16 @@
         <v>21302</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>81</v>
+        <v>69</v>
       </c>
       <c r="E13" s="4" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="F13" s="4">
         <v>300</v>
@@ -1631,28 +1599,24 @@
         <v>3</v>
       </c>
       <c r="H13" s="4" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="I13" s="6" t="s">
-        <v>66</v>
+        <v>126</v>
       </c>
       <c r="J13" s="6" t="s">
-        <v>44</v>
+        <v>125</v>
       </c>
       <c r="K13" s="6" t="s">
-        <v>71</v>
-      </c>
-      <c r="L13" s="6" t="s">
-        <v>67</v>
-      </c>
-      <c r="M13" s="6" t="s">
-        <v>74</v>
-      </c>
+        <v>127</v>
+      </c>
+      <c r="L13" s="6"/>
+      <c r="M13" s="6"/>
       <c r="N13" s="4" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="O13" s="4" t="s">
-        <v>104</v>
+        <v>92</v>
       </c>
       <c r="P13" s="4"/>
       <c r="Q13" s="4">
@@ -1662,7 +1626,7 @@
         <v>2</v>
       </c>
       <c r="S13" s="4" t="s">
-        <v>94</v>
+        <v>82</v>
       </c>
     </row>
     <row r="14" spans="1:41" x14ac:dyDescent="0.2">
@@ -1670,16 +1634,16 @@
         <v>21401</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>116</v>
+        <v>104</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>117</v>
+        <v>105</v>
       </c>
       <c r="D14" s="4" t="s">
-        <v>118</v>
+        <v>106</v>
       </c>
       <c r="E14" s="4" t="s">
-        <v>119</v>
+        <v>107</v>
       </c>
       <c r="F14" s="4">
         <v>0</v>
@@ -1694,7 +1658,7 @@
       <c r="L14" s="6"/>
       <c r="M14" s="6"/>
       <c r="N14" s="4" t="s">
-        <v>120</v>
+        <v>108</v>
       </c>
       <c r="O14" s="4"/>
       <c r="P14" s="4">
@@ -1703,7 +1667,7 @@
       <c r="Q14" s="4"/>
       <c r="R14" s="4"/>
       <c r="S14" s="4" t="s">
-        <v>121</v>
+        <v>109</v>
       </c>
     </row>
     <row r="15" spans="1:41" x14ac:dyDescent="0.2">
@@ -1711,16 +1675,16 @@
         <v>21402</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>123</v>
+        <v>111</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>124</v>
+        <v>112</v>
       </c>
       <c r="D15" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="E15" s="4" t="s">
         <v>122</v>
-      </c>
-      <c r="E15" s="4" t="s">
-        <v>134</v>
       </c>
       <c r="F15" s="4">
         <v>100</v>
@@ -1735,7 +1699,7 @@
       <c r="L15" s="6"/>
       <c r="M15" s="6"/>
       <c r="N15" s="4" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="O15" s="4"/>
       <c r="P15" s="4">
@@ -1746,7 +1710,7 @@
       </c>
       <c r="R15" s="4"/>
       <c r="S15" s="4" t="s">
-        <v>121</v>
+        <v>109</v>
       </c>
     </row>
   </sheetData>

--- a/Design/config/CityDevConfig.xlsx
+++ b/Design/config/CityDevConfig.xlsx
@@ -110,426 +110,426 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
+    <t>发展商业</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>图片</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>market</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>GoldCost</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>int</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>cs</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>描述</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Des</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>cs</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>提升值</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>cs</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>加固城墙</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>发展农业,提升粮食产量</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>发展商业,提升金钱收入</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>提升城防</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Str</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Wall</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>wall</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>LeadShip|Str</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>走访</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>搜集人才和宝物</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Charm|Inte</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>find</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Gold</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Power</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>训练</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>提升军队士气</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>train</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>zhengbing</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>LeadShip|Charm</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Soldier</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>征兵</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>提升士兵数量</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>DevAttr1Value</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>int[]</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>DevAttr2</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>DevAttr2Value</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>DevAttr3</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>DevAttr3Value</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>3,9</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>出战</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>出兵攻打敌人</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Prefab</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>string</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>cs</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>CityDevNormal</t>
+  </si>
+  <si>
+    <t>CityDevBattle</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>对象</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>人均消耗黄金</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>最大参与人数</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>HeroCount</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>int</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>cs</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>battle</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>移动</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>move</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>move2.mp4</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>atk2.mp4</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>zhengbing2.mp4</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>train3.mp4</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>search2.mp4</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>shop3.mp4</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>移动到其他城市</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>string</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>cs</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>dev</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>def</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>find</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>sod</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>ActionName</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>farm.mp4</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>CityDevChange</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>交易钱粮</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>行动</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Inte</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>交易</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>change</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>change.mp4</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>fix4.mp4</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Food</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>登用</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>提拔在野武将</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>CityDevUseHero</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>wild</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Charm|Inte</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>wild.mp4</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>CityDevPraiseHero</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>褒奖</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>提升武将忠心度</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>cs</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>战时优先级</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>AiPriotyAtk</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>int</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>AiPriotyDev</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>发展时ai</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>cs</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>AiPriotyDef</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>CityDevMove</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>praise</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Icon</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>1,2</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Exp</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>5,10</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>2,5</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
     <t>发展农业</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>发展商业</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>图片</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>market</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>GoldCost</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>int</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>cs</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>描述</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Des</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>cs</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>提升值</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>cs</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>加固城墙</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>发展农业,提升粮食产量</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>发展商业,提升金钱收入</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>提升城防</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Str</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Wall</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>wall</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>LeadShip|Str</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>走访</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>搜集人才和宝物</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Charm|Inte</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>find</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Gold</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Power</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>训练</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>提升军队士气</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>train</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>zhengbing</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>LeadShip|Charm</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Soldier</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>征兵</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>提升士兵数量</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>DevAttr1Value</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>int[]</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>DevAttr2</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>DevAttr2Value</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>DevAttr3</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>DevAttr3Value</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>3,9</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>DevAttr1</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>出战</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>出兵攻打敌人</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Prefab</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>string</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>cs</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>CityDevNormal</t>
-  </si>
-  <si>
-    <t>CityDevBattle</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>对象</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>人均消耗黄金</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>最大参与人数</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>HeroCount</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>int</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>cs</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>battle</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>移动</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>move</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>move2.mp4</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>atk2.mp4</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>zhengbing2.mp4</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>train3.mp4</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>search2.mp4</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>shop3.mp4</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>移动到其他城市</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>string</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>cs</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>dev</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>def</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>find</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>sod</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>ActionName</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>farm.mp4</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>CityDevChange</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>交易钱粮</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>行动</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Inte</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>交易</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>change</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>change.mp4</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>fix4.mp4</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Food</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>登用</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>提拔在野武将</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>CityDevUseHero</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>wild</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Charm|Inte</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>wild.mp4</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>CityDevPraiseHero</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>褒奖</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>提升武将忠心度</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>cs</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>战时优先级</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>AiPriotyAtk</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>int</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>AiPriotyDev</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>发展时ai</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>cs</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>AiPriotyDef</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>CityDevMove</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>praise</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Icon</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>1,2</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Exp</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>5,10</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>2,5</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -956,52 +956,52 @@
         <v>10</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D1" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="G1" s="3" t="s">
         <v>71</v>
-      </c>
-      <c r="E1" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="F1" s="3" t="s">
-        <v>72</v>
-      </c>
-      <c r="G1" s="3" t="s">
-        <v>73</v>
       </c>
       <c r="H1" s="3" t="s">
         <v>14</v>
       </c>
       <c r="I1" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="J1" s="3" t="s">
         <v>14</v>
       </c>
       <c r="K1" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="L1" s="3" t="s">
         <v>14</v>
       </c>
       <c r="M1" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="N1" s="3" t="s">
         <v>14</v>
       </c>
       <c r="O1" s="3" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="P1" s="3" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="Q1" s="3" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="R1" s="3" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="S1" s="3" t="s">
         <v>11</v>
@@ -1015,52 +1015,52 @@
         <v>9</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>63</v>
+        <v>127</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="J2" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="K2" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="K2" s="2" t="s">
+      <c r="L2" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="L2" s="2" t="s">
+      <c r="M2" s="2" t="s">
         <v>60</v>
-      </c>
-      <c r="M2" s="2" t="s">
-        <v>61</v>
       </c>
       <c r="N2" s="2" t="s">
         <v>15</v>
       </c>
       <c r="O2" s="2" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="P2" s="2" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="Q2" s="2" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="R2" s="2" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="S2" s="2" t="s">
         <v>12</v>
@@ -1077,49 +1077,49 @@
         <v>21</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>3</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="H3" s="2" t="s">
         <v>3</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="J3" s="2" t="s">
         <v>3</v>
       </c>
       <c r="K3" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="L3" s="2" t="s">
         <v>3</v>
       </c>
       <c r="M3" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="N3" s="2" t="s">
         <v>16</v>
       </c>
       <c r="O3" s="2" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="P3" s="2" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="Q3" s="2" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="R3" s="2" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="S3" s="2" t="s">
         <v>13</v>
@@ -1133,25 +1133,25 @@
         <v>5</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>4</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="H4" s="2" t="s">
         <v>4</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="J4" s="2" t="s">
         <v>4</v>
@@ -1169,16 +1169,16 @@
         <v>17</v>
       </c>
       <c r="O4" s="2" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="P4" s="2" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="Q4" s="2" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="R4" s="2" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="S4" s="2" t="s">
         <v>8</v>
@@ -1189,13 +1189,13 @@
         <v>21001</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>22</v>
+        <v>126</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="E5" s="4" t="s">
         <v>20</v>
@@ -1207,16 +1207,16 @@
         <v>3</v>
       </c>
       <c r="H5" s="4" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="I5" s="6" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="J5" s="6" t="s">
+        <v>123</v>
+      </c>
+      <c r="K5" s="6" t="s">
         <v>125</v>
-      </c>
-      <c r="K5" s="6" t="s">
-        <v>127</v>
       </c>
       <c r="L5" s="6"/>
       <c r="M5" s="6"/>
@@ -1224,7 +1224,7 @@
         <v>18</v>
       </c>
       <c r="O5" s="4" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="P5" s="4">
         <v>11</v>
@@ -1232,7 +1232,7 @@
       <c r="Q5" s="4"/>
       <c r="R5" s="4"/>
       <c r="S5" s="4" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
     </row>
     <row r="6" spans="1:41" x14ac:dyDescent="0.2">
@@ -1240,16 +1240,16 @@
         <v>21002</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F6" s="4">
         <v>300</v>
@@ -1258,16 +1258,16 @@
         <v>3</v>
       </c>
       <c r="H6" s="4" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="I6" s="6" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="J6" s="6" t="s">
+        <v>123</v>
+      </c>
+      <c r="K6" s="6" t="s">
         <v>125</v>
-      </c>
-      <c r="K6" s="6" t="s">
-        <v>127</v>
       </c>
       <c r="L6" s="6"/>
       <c r="M6" s="6"/>
@@ -1275,7 +1275,7 @@
         <v>19</v>
       </c>
       <c r="O6" s="4" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="P6" s="4">
         <v>10</v>
@@ -1283,7 +1283,7 @@
       <c r="Q6" s="4"/>
       <c r="R6" s="4"/>
       <c r="S6" s="4" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
     </row>
     <row r="7" spans="1:41" x14ac:dyDescent="0.2">
@@ -1291,16 +1291,16 @@
         <v>21101</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F7" s="4">
         <v>200</v>
@@ -1309,24 +1309,24 @@
         <v>3</v>
       </c>
       <c r="H7" s="4" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="I7" s="6" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="J7" s="6" t="s">
+        <v>123</v>
+      </c>
+      <c r="K7" s="6" t="s">
         <v>125</v>
-      </c>
-      <c r="K7" s="6" t="s">
-        <v>127</v>
       </c>
       <c r="L7" s="6"/>
       <c r="M7" s="6"/>
       <c r="N7" s="4" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="O7" s="4" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="P7" s="4">
         <v>30</v>
@@ -1336,7 +1336,7 @@
         <v>10</v>
       </c>
       <c r="S7" s="4" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="AN7" s="5"/>
       <c r="AO7" s="5"/>
@@ -1346,16 +1346,16 @@
         <v>21102</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="F8" s="4">
         <v>0</v>
@@ -1370,7 +1370,7 @@
       <c r="L8" s="6"/>
       <c r="M8" s="6"/>
       <c r="N8" s="4" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="O8" s="4"/>
       <c r="P8" s="4">
@@ -1383,7 +1383,7 @@
         <v>9</v>
       </c>
       <c r="S8" s="4" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="AN8" s="5"/>
       <c r="AO8" s="5"/>
@@ -1393,16 +1393,16 @@
         <v>21103</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="F9" s="4">
         <v>0</v>
@@ -1417,7 +1417,7 @@
       <c r="L9" s="6"/>
       <c r="M9" s="6"/>
       <c r="N9" s="4" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="O9" s="4"/>
       <c r="P9" s="4"/>
@@ -1426,7 +1426,7 @@
       </c>
       <c r="R9" s="4"/>
       <c r="S9" s="4" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
     </row>
     <row r="10" spans="1:41" x14ac:dyDescent="0.2">
@@ -1434,16 +1434,16 @@
         <v>21202</v>
       </c>
       <c r="B10" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="C10" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="C10" s="4" t="s">
-        <v>43</v>
-      </c>
       <c r="D10" s="4" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F10" s="4">
         <v>0</v>
@@ -1452,20 +1452,20 @@
         <v>10</v>
       </c>
       <c r="H10" s="4" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="I10" s="6" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="J10" s="6"/>
       <c r="K10" s="6"/>
       <c r="L10" s="6"/>
       <c r="M10" s="6"/>
       <c r="N10" s="4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="O10" s="4" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="P10" s="4">
         <v>21</v>
@@ -1475,7 +1475,7 @@
         <v>11</v>
       </c>
       <c r="S10" s="4" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
     </row>
     <row r="11" spans="1:41" x14ac:dyDescent="0.2">
@@ -1483,16 +1483,16 @@
         <v>21203</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="E11" s="4" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="F11" s="4">
         <v>0</v>
@@ -1501,17 +1501,17 @@
         <v>1</v>
       </c>
       <c r="H11" s="4" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="I11" s="6"/>
       <c r="J11" s="6" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="K11" s="6"/>
       <c r="L11" s="6"/>
       <c r="M11" s="6"/>
       <c r="N11" s="4" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="O11" s="4"/>
       <c r="P11" s="4">
@@ -1524,7 +1524,7 @@
         <v>1</v>
       </c>
       <c r="S11" s="4" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
     </row>
     <row r="12" spans="1:41" x14ac:dyDescent="0.2">
@@ -1532,16 +1532,16 @@
         <v>21301</v>
       </c>
       <c r="B12" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="C12" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="C12" s="4" t="s">
+      <c r="D12" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="E12" s="4" t="s">
         <v>49</v>
-      </c>
-      <c r="D12" s="4" t="s">
-        <v>69</v>
-      </c>
-      <c r="E12" s="4" t="s">
-        <v>50</v>
       </c>
       <c r="F12" s="4">
         <v>0</v>
@@ -1550,20 +1550,20 @@
         <v>3</v>
       </c>
       <c r="H12" s="4" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="I12" s="6" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="J12" s="6"/>
       <c r="K12" s="6"/>
       <c r="L12" s="6"/>
       <c r="M12" s="6"/>
       <c r="N12" s="4" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="O12" s="4" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="P12" s="4"/>
       <c r="Q12" s="4">
@@ -1573,7 +1573,7 @@
         <v>3</v>
       </c>
       <c r="S12" s="4" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
     </row>
     <row r="13" spans="1:41" x14ac:dyDescent="0.2">
@@ -1581,16 +1581,16 @@
         <v>21302</v>
       </c>
       <c r="B13" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="C13" s="4" t="s">
         <v>54</v>
       </c>
-      <c r="C13" s="4" t="s">
-        <v>55</v>
-      </c>
       <c r="D13" s="4" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="E13" s="4" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="F13" s="4">
         <v>300</v>
@@ -1599,24 +1599,24 @@
         <v>3</v>
       </c>
       <c r="H13" s="4" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="I13" s="6" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="J13" s="6" t="s">
+        <v>123</v>
+      </c>
+      <c r="K13" s="6" t="s">
         <v>125</v>
-      </c>
-      <c r="K13" s="6" t="s">
-        <v>127</v>
       </c>
       <c r="L13" s="6"/>
       <c r="M13" s="6"/>
       <c r="N13" s="4" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="O13" s="4" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="P13" s="4"/>
       <c r="Q13" s="4">
@@ -1626,7 +1626,7 @@
         <v>2</v>
       </c>
       <c r="S13" s="4" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
     </row>
     <row r="14" spans="1:41" x14ac:dyDescent="0.2">
@@ -1634,16 +1634,16 @@
         <v>21401</v>
       </c>
       <c r="B14" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="C14" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="D14" s="4" t="s">
         <v>104</v>
       </c>
-      <c r="C14" s="4" t="s">
+      <c r="E14" s="4" t="s">
         <v>105</v>
-      </c>
-      <c r="D14" s="4" t="s">
-        <v>106</v>
-      </c>
-      <c r="E14" s="4" t="s">
-        <v>107</v>
       </c>
       <c r="F14" s="4">
         <v>0</v>
@@ -1658,7 +1658,7 @@
       <c r="L14" s="6"/>
       <c r="M14" s="6"/>
       <c r="N14" s="4" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="O14" s="4"/>
       <c r="P14" s="4">
@@ -1667,7 +1667,7 @@
       <c r="Q14" s="4"/>
       <c r="R14" s="4"/>
       <c r="S14" s="4" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
     </row>
     <row r="15" spans="1:41" x14ac:dyDescent="0.2">
@@ -1675,16 +1675,16 @@
         <v>21402</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="E15" s="4" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="F15" s="4">
         <v>100</v>
@@ -1699,7 +1699,7 @@
       <c r="L15" s="6"/>
       <c r="M15" s="6"/>
       <c r="N15" s="4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="O15" s="4"/>
       <c r="P15" s="4">
@@ -1710,7 +1710,7 @@
       </c>
       <c r="R15" s="4"/>
       <c r="S15" s="4" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
     </row>
   </sheetData>

--- a/Design/config/CityDevConfig.xlsx
+++ b/Design/config/CityDevConfig.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$4:$S$13</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$4:$T$13</definedName>
   </definedNames>
   <calcPr calcId="162913"/>
   <extLst>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="170" uniqueCount="128">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="181" uniqueCount="135">
   <si>
     <t>序列</t>
     <phoneticPr fontId="3" type="noConversion"/>
@@ -258,14 +258,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>DevAttr3</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>DevAttr3Value</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>3,9</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -453,83 +445,119 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
+    <t>褒奖</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>提升武将忠心度</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>cs</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>战时优先级</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>AiPriotyAtk</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>int</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>AiPriotyDev</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>发展时ai</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>cs</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>AiPriotyDef</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>CityDevMove</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>praise</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Icon</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>1,2</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Exp</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>5,10</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>2,5</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>发展农业</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>DevAttr1</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>SpecialAction</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>SpecialActionVal</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Type</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>string</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>cs</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>类型</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>normal</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
     <t>CityDevPraiseHero</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>褒奖</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>提升武将忠心度</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>cs</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>战时优先级</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>AiPriotyAtk</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>int</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>AiPriotyDev</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>发展时ai</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>cs</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>AiPriotyDef</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>CityDevMove</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>praise</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>Icon</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>1,2</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Exp</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>5,10</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>2,5</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>发展农业</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>DevAttr1</t>
+    <t>1,5</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -928,27 +956,22 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AO15"/>
+  <dimension ref="A1:AP15"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9.5" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="9.125" customWidth="1"/>
-    <col min="3" max="4" width="14" customWidth="1"/>
-    <col min="5" max="7" width="9.125" customWidth="1"/>
-    <col min="8" max="8" width="14" customWidth="1"/>
-    <col min="9" max="9" width="13.75" customWidth="1"/>
-    <col min="10" max="10" width="14" customWidth="1"/>
-    <col min="11" max="11" width="13.75" customWidth="1"/>
-    <col min="12" max="12" width="14" customWidth="1"/>
-    <col min="13" max="13" width="13.75" customWidth="1"/>
-    <col min="14" max="14" width="14" customWidth="1"/>
-    <col min="15" max="16" width="8" customWidth="1"/>
-    <col min="17" max="17" width="9" customWidth="1"/>
-    <col min="18" max="18" width="7.25" customWidth="1"/>
-    <col min="19" max="19" width="9.5" customWidth="1"/>
+    <col min="3" max="5" width="14" customWidth="1"/>
+    <col min="6" max="8" width="9.125" customWidth="1"/>
+    <col min="9" max="14" width="11.75" customWidth="1"/>
+    <col min="15" max="15" width="14" customWidth="1"/>
+    <col min="16" max="17" width="8" customWidth="1"/>
+    <col min="18" max="18" width="9" customWidth="1"/>
+    <col min="19" max="19" width="7.25" customWidth="1"/>
+    <col min="20" max="20" width="9.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:41" ht="57" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:42" ht="57" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -959,55 +982,58 @@
         <v>28</v>
       </c>
       <c r="D1" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="G1" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="H1" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="E1" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="F1" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="G1" s="3" t="s">
-        <v>71</v>
-      </c>
-      <c r="H1" s="3" t="s">
+      <c r="I1" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="I1" s="3" t="s">
+      <c r="J1" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="J1" s="3" t="s">
+      <c r="K1" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="K1" s="3" t="s">
+      <c r="L1" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="L1" s="3" t="s">
+      <c r="M1" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="M1" s="3" t="s">
+      <c r="N1" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="N1" s="3" t="s">
+      <c r="O1" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="O1" s="3" t="s">
-        <v>95</v>
-      </c>
       <c r="P1" s="3" t="s">
-        <v>116</v>
+        <v>93</v>
       </c>
       <c r="Q1" s="3" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="R1" s="3" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="S1" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="T1" s="3" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="2" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
@@ -1018,55 +1044,58 @@
         <v>29</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>64</v>
+        <v>127</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>121</v>
+        <v>62</v>
       </c>
       <c r="F2" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="G2" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="G2" s="2" t="s">
-        <v>72</v>
-      </c>
       <c r="H2" s="2" t="s">
-        <v>127</v>
+        <v>70</v>
       </c>
       <c r="I2" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="J2" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="J2" s="2" t="s">
+      <c r="K2" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="K2" s="2" t="s">
+      <c r="L2" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="L2" s="2" t="s">
-        <v>59</v>
-      </c>
       <c r="M2" s="2" t="s">
-        <v>60</v>
+        <v>125</v>
       </c>
       <c r="N2" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="O2" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="O2" s="2" t="s">
-        <v>91</v>
-      </c>
       <c r="P2" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="Q2" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="R2" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="S2" s="2" t="s">
         <v>115</v>
       </c>
-      <c r="Q2" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="R2" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="S2" s="2" t="s">
+      <c r="T2" s="2" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="3" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A3" s="2" t="s">
         <v>7</v>
       </c>
@@ -1077,55 +1106,58 @@
         <v>21</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>65</v>
+        <v>128</v>
       </c>
       <c r="E3" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="F3" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="F3" s="2" t="s">
+      <c r="G3" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="G3" s="2" t="s">
-        <v>73</v>
-      </c>
       <c r="H3" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="I3" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="I3" s="2" t="s">
+      <c r="J3" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="J3" s="2" t="s">
+      <c r="K3" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="K3" s="2" t="s">
+      <c r="L3" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="L3" s="2" t="s">
+      <c r="M3" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="M3" s="2" t="s">
+      <c r="N3" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="N3" s="2" t="s">
+      <c r="O3" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="O3" s="2" t="s">
-        <v>85</v>
-      </c>
       <c r="P3" s="2" t="s">
-        <v>114</v>
+        <v>83</v>
       </c>
       <c r="Q3" s="2" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="R3" s="2" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="S3" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="T3" s="2" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A4" s="2" t="s">
         <v>2</v>
       </c>
@@ -1136,25 +1168,25 @@
         <v>30</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>66</v>
+        <v>129</v>
       </c>
       <c r="E4" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="F4" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F4" s="2" t="s">
+      <c r="G4" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="G4" s="2" t="s">
-        <v>74</v>
-      </c>
       <c r="H4" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="I4" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="I4" s="2" t="s">
+      <c r="J4" s="2" t="s">
         <v>32</v>
-      </c>
-      <c r="J4" s="2" t="s">
-        <v>4</v>
       </c>
       <c r="K4" s="2" t="s">
         <v>4</v>
@@ -1166,76 +1198,82 @@
         <v>4</v>
       </c>
       <c r="N4" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="O4" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="O4" s="2" t="s">
-        <v>86</v>
-      </c>
       <c r="P4" s="2" t="s">
-        <v>117</v>
+        <v>84</v>
       </c>
       <c r="Q4" s="2" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="R4" s="2" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="S4" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="T4" s="2" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="5" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A5" s="4">
         <v>21001</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="C5" s="4" t="s">
         <v>34</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>67</v>
+        <v>131</v>
       </c>
       <c r="E5" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="F5" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="F5" s="4">
-        <v>300</v>
-      </c>
       <c r="G5" s="4">
+        <v>0</v>
+      </c>
+      <c r="H5" s="4">
         <v>3</v>
       </c>
-      <c r="H5" s="4" t="s">
-        <v>101</v>
-      </c>
-      <c r="I5" s="6" t="s">
-        <v>124</v>
+      <c r="I5" s="4" t="s">
+        <v>99</v>
       </c>
       <c r="J5" s="6" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="K5" s="6" t="s">
-        <v>125</v>
-      </c>
-      <c r="L5" s="6"/>
+        <v>120</v>
+      </c>
+      <c r="L5" s="6" t="s">
+        <v>122</v>
+      </c>
       <c r="M5" s="6"/>
-      <c r="N5" s="4" t="s">
+      <c r="N5" s="6"/>
+      <c r="O5" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="O5" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="P5" s="4">
+      <c r="P5" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="Q5" s="4">
         <v>11</v>
       </c>
-      <c r="Q5" s="4"/>
       <c r="R5" s="4"/>
-      <c r="S5" s="4" t="s">
-        <v>92</v>
+      <c r="S5" s="4"/>
+      <c r="T5" s="4" t="s">
+        <v>90</v>
       </c>
     </row>
-    <row r="6" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A6" s="4">
         <v>21002</v>
       </c>
@@ -1246,476 +1284,498 @@
         <v>35</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>67</v>
+        <v>131</v>
       </c>
       <c r="E6" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="F6" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="F6" s="4">
-        <v>300</v>
-      </c>
       <c r="G6" s="4">
+        <v>0</v>
+      </c>
+      <c r="H6" s="4">
         <v>3</v>
       </c>
-      <c r="H6" s="4" t="s">
+      <c r="I6" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="I6" s="6" t="s">
-        <v>124</v>
-      </c>
       <c r="J6" s="6" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="K6" s="6" t="s">
-        <v>125</v>
-      </c>
-      <c r="L6" s="6"/>
+        <v>120</v>
+      </c>
+      <c r="L6" s="6" t="s">
+        <v>122</v>
+      </c>
       <c r="M6" s="6"/>
-      <c r="N6" s="4" t="s">
+      <c r="N6" s="6"/>
+      <c r="O6" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="O6" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="P6" s="4">
+      <c r="P6" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="Q6" s="4">
         <v>10</v>
       </c>
-      <c r="Q6" s="4"/>
       <c r="R6" s="4"/>
-      <c r="S6" s="4" t="s">
-        <v>83</v>
+      <c r="S6" s="4"/>
+      <c r="T6" s="4" t="s">
+        <v>81</v>
       </c>
     </row>
-    <row r="7" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A7" s="4">
-        <v>21101</v>
+        <v>21003</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>33</v>
+        <v>53</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>36</v>
+        <v>54</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>67</v>
+        <v>131</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="F7" s="4">
-        <v>200</v>
+        <v>65</v>
+      </c>
+      <c r="F7" s="4" t="s">
+        <v>50</v>
       </c>
       <c r="G7" s="4">
+        <v>10</v>
+      </c>
+      <c r="H7" s="4">
         <v>3</v>
       </c>
-      <c r="H7" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="I7" s="6" t="s">
-        <v>124</v>
+      <c r="I7" s="4" t="s">
+        <v>52</v>
       </c>
       <c r="J7" s="6" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="K7" s="6" t="s">
-        <v>125</v>
-      </c>
-      <c r="L7" s="6"/>
+        <v>120</v>
+      </c>
+      <c r="L7" s="6" t="s">
+        <v>122</v>
+      </c>
       <c r="M7" s="6"/>
-      <c r="N7" s="4" t="s">
-        <v>37</v>
-      </c>
+      <c r="N7" s="6"/>
       <c r="O7" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="P7" s="4" t="s">
         <v>88</v>
-      </c>
-      <c r="P7" s="4">
-        <v>30</v>
       </c>
       <c r="Q7" s="4"/>
       <c r="R7" s="4">
-        <v>10</v>
-      </c>
-      <c r="S7" s="4" t="s">
-        <v>100</v>
-      </c>
-      <c r="AN7" s="5"/>
+        <v>8</v>
+      </c>
+      <c r="S7" s="4">
+        <v>2</v>
+      </c>
+      <c r="T7" s="4" t="s">
+        <v>78</v>
+      </c>
       <c r="AO7" s="5"/>
+      <c r="AP7" s="5"/>
     </row>
-    <row r="8" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A8" s="4">
-        <v>21102</v>
+        <v>21004</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>76</v>
+        <v>33</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>84</v>
+        <v>36</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>119</v>
+        <v>131</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>77</v>
-      </c>
-      <c r="F8" s="4">
-        <v>0</v>
+        <v>65</v>
+      </c>
+      <c r="F8" s="4" t="s">
+        <v>39</v>
       </c>
       <c r="G8" s="4">
         <v>10</v>
       </c>
-      <c r="H8" s="4"/>
-      <c r="I8" s="6"/>
-      <c r="J8" s="6"/>
-      <c r="K8" s="6"/>
-      <c r="L8" s="6"/>
+      <c r="H8" s="4">
+        <v>3</v>
+      </c>
+      <c r="I8" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="J8" s="6" t="s">
+        <v>121</v>
+      </c>
+      <c r="K8" s="6" t="s">
+        <v>120</v>
+      </c>
+      <c r="L8" s="6" t="s">
+        <v>122</v>
+      </c>
       <c r="M8" s="6"/>
-      <c r="N8" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="O8" s="4"/>
-      <c r="P8" s="4">
-        <v>28</v>
+      <c r="N8" s="6"/>
+      <c r="O8" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="P8" s="4" t="s">
+        <v>86</v>
       </c>
       <c r="Q8" s="4">
-        <v>4</v>
-      </c>
-      <c r="R8" s="4">
-        <v>9</v>
-      </c>
-      <c r="S8" s="4" t="s">
-        <v>78</v>
-      </c>
-      <c r="AN8" s="5"/>
+        <v>30</v>
+      </c>
+      <c r="R8" s="4"/>
+      <c r="S8" s="4">
+        <v>10</v>
+      </c>
+      <c r="T8" s="4" t="s">
+        <v>98</v>
+      </c>
       <c r="AO8" s="5"/>
+      <c r="AP8" s="5"/>
     </row>
-    <row r="9" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A9" s="4">
-        <v>21103</v>
+        <v>21005</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>62</v>
+        <v>47</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>63</v>
+        <v>48</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>68</v>
+        <v>131</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>75</v>
-      </c>
-      <c r="F9" s="4">
+        <v>65</v>
+      </c>
+      <c r="F9" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="G9" s="4">
         <v>0</v>
       </c>
-      <c r="G9" s="4">
-        <v>10</v>
-      </c>
-      <c r="H9" s="4"/>
-      <c r="I9" s="6"/>
-      <c r="J9" s="6"/>
+      <c r="H9" s="4">
+        <v>3</v>
+      </c>
+      <c r="I9" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="J9" s="6" t="s">
+        <v>59</v>
+      </c>
       <c r="K9" s="6"/>
       <c r="L9" s="6"/>
       <c r="M9" s="6"/>
-      <c r="N9" s="4" t="s">
+      <c r="N9" s="6"/>
+      <c r="O9" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="O9" s="4"/>
-      <c r="P9" s="4"/>
-      <c r="Q9" s="4">
-        <v>1</v>
-      </c>
-      <c r="R9" s="4"/>
-      <c r="S9" s="4" t="s">
+      <c r="P9" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="Q9" s="4"/>
+      <c r="R9" s="4">
+        <v>9</v>
+      </c>
+      <c r="S9" s="4">
+        <v>3</v>
+      </c>
+      <c r="T9" s="4" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="10" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A10" s="4">
-        <v>21202</v>
+        <v>21102</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>41</v>
+        <v>74</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="D10" s="4" t="s">
-        <v>67</v>
-      </c>
+        <v>82</v>
+      </c>
+      <c r="D10" s="4"/>
       <c r="E10" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="F10" s="4">
+        <v>116</v>
+      </c>
+      <c r="F10" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="G10" s="4">
         <v>0</v>
       </c>
-      <c r="G10" s="4">
+      <c r="H10" s="4">
         <v>10</v>
       </c>
-      <c r="H10" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="I10" s="6" t="s">
-        <v>122</v>
-      </c>
+      <c r="I10" s="4"/>
       <c r="J10" s="6"/>
       <c r="K10" s="6"/>
       <c r="L10" s="6"/>
       <c r="M10" s="6"/>
-      <c r="N10" s="4" t="s">
-        <v>43</v>
-      </c>
+      <c r="N10" s="6"/>
       <c r="O10" s="4" t="s">
-        <v>89</v>
-      </c>
-      <c r="P10" s="4">
-        <v>21</v>
-      </c>
-      <c r="Q10" s="4"/>
+        <v>51</v>
+      </c>
+      <c r="P10" s="4"/>
+      <c r="Q10" s="4">
+        <v>28</v>
+      </c>
       <c r="R10" s="4">
-        <v>11</v>
-      </c>
-      <c r="S10" s="4" t="s">
-        <v>82</v>
+        <v>4</v>
+      </c>
+      <c r="S10" s="4">
+        <v>9</v>
+      </c>
+      <c r="T10" s="4" t="s">
+        <v>76</v>
       </c>
     </row>
-    <row r="11" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A11" s="4">
-        <v>21203</v>
+        <v>21103</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>97</v>
+        <v>60</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="D11" s="4" t="s">
-        <v>93</v>
-      </c>
+        <v>61</v>
+      </c>
+      <c r="D11" s="4"/>
       <c r="E11" s="4" t="s">
-        <v>98</v>
-      </c>
-      <c r="F11" s="4">
+        <v>66</v>
+      </c>
+      <c r="F11" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="G11" s="4">
         <v>0</v>
       </c>
-      <c r="G11" s="4">
-        <v>1</v>
-      </c>
-      <c r="H11" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="I11" s="6"/>
-      <c r="J11" s="6" t="s">
-        <v>101</v>
-      </c>
+      <c r="H11" s="4">
+        <v>10</v>
+      </c>
+      <c r="I11" s="4"/>
+      <c r="J11" s="6"/>
       <c r="K11" s="6"/>
       <c r="L11" s="6"/>
       <c r="M11" s="6"/>
-      <c r="N11" s="4" t="s">
-        <v>96</v>
-      </c>
-      <c r="O11" s="4"/>
-      <c r="P11" s="4">
-        <v>1</v>
-      </c>
-      <c r="Q11" s="4">
-        <v>3</v>
-      </c>
+      <c r="N11" s="6"/>
+      <c r="O11" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="P11" s="4"/>
+      <c r="Q11" s="4"/>
       <c r="R11" s="4">
         <v>1</v>
       </c>
-      <c r="S11" s="4" t="s">
-        <v>99</v>
+      <c r="S11" s="4"/>
+      <c r="T11" s="4" t="s">
+        <v>77</v>
       </c>
     </row>
-    <row r="12" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A12" s="4">
-        <v>21301</v>
+        <v>21202</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>67</v>
+        <v>131</v>
       </c>
       <c r="E12" s="4" t="s">
-        <v>49</v>
-      </c>
-      <c r="F12" s="4">
+        <v>65</v>
+      </c>
+      <c r="F12" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="G12" s="4">
         <v>0</v>
       </c>
-      <c r="G12" s="4">
-        <v>3</v>
-      </c>
-      <c r="H12" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="I12" s="6" t="s">
-        <v>61</v>
-      </c>
-      <c r="J12" s="6"/>
+      <c r="H12" s="4">
+        <v>10</v>
+      </c>
+      <c r="I12" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="J12" s="6" t="s">
+        <v>119</v>
+      </c>
       <c r="K12" s="6"/>
       <c r="L12" s="6"/>
       <c r="M12" s="6"/>
-      <c r="N12" s="4" t="s">
-        <v>40</v>
-      </c>
+      <c r="N12" s="6"/>
       <c r="O12" s="4" t="s">
-        <v>90</v>
-      </c>
-      <c r="P12" s="4"/>
+        <v>43</v>
+      </c>
+      <c r="P12" s="4" t="s">
+        <v>87</v>
+      </c>
       <c r="Q12" s="4">
-        <v>9</v>
-      </c>
-      <c r="R12" s="4">
-        <v>3</v>
-      </c>
-      <c r="S12" s="4" t="s">
-        <v>81</v>
+        <v>21</v>
+      </c>
+      <c r="R12" s="4"/>
+      <c r="S12" s="4">
+        <v>11</v>
+      </c>
+      <c r="T12" s="4" t="s">
+        <v>80</v>
       </c>
     </row>
-    <row r="13" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A13" s="4">
-        <v>21302</v>
+        <v>21203</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>53</v>
+        <v>95</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="D13" s="4" t="s">
-        <v>67</v>
-      </c>
+        <v>92</v>
+      </c>
+      <c r="D13" s="4"/>
       <c r="E13" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="F13" s="4">
-        <v>300</v>
+        <v>91</v>
+      </c>
+      <c r="F13" s="4" t="s">
+        <v>96</v>
       </c>
       <c r="G13" s="4">
-        <v>3</v>
-      </c>
-      <c r="H13" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="I13" s="6" t="s">
-        <v>124</v>
-      </c>
-      <c r="J13" s="6" t="s">
-        <v>123</v>
-      </c>
-      <c r="K13" s="6" t="s">
-        <v>125</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="H13" s="4">
+        <v>1</v>
+      </c>
+      <c r="I13" s="4"/>
+      <c r="J13" s="6"/>
+      <c r="K13" s="6"/>
       <c r="L13" s="6"/>
       <c r="M13" s="6"/>
-      <c r="N13" s="4" t="s">
-        <v>51</v>
-      </c>
+      <c r="N13" s="6"/>
       <c r="O13" s="4" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="P13" s="4"/>
       <c r="Q13" s="4">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="R13" s="4">
-        <v>2</v>
-      </c>
-      <c r="S13" s="4" t="s">
-        <v>80</v>
+        <v>3</v>
+      </c>
+      <c r="S13" s="4">
+        <v>1</v>
+      </c>
+      <c r="T13" s="4" t="s">
+        <v>97</v>
       </c>
     </row>
-    <row r="14" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A14" s="4">
         <v>21401</v>
       </c>
       <c r="B14" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="C14" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="D14" s="4"/>
+      <c r="E14" s="4" t="s">
         <v>102</v>
       </c>
-      <c r="C14" s="4" t="s">
+      <c r="F14" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="D14" s="4" t="s">
-        <v>104</v>
-      </c>
-      <c r="E14" s="4" t="s">
-        <v>105</v>
-      </c>
-      <c r="F14" s="4">
+      <c r="G14" s="4">
         <v>0</v>
       </c>
-      <c r="G14" s="4">
+      <c r="H14" s="4">
         <v>1</v>
       </c>
-      <c r="H14" s="4"/>
-      <c r="I14" s="6"/>
+      <c r="I14" s="4"/>
       <c r="J14" s="6"/>
       <c r="K14" s="6"/>
       <c r="L14" s="6"/>
       <c r="M14" s="6"/>
-      <c r="N14" s="4" t="s">
-        <v>106</v>
-      </c>
-      <c r="O14" s="4"/>
-      <c r="P14" s="4">
+      <c r="N14" s="6"/>
+      <c r="O14" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="P14" s="4"/>
+      <c r="Q14" s="4">
         <v>2</v>
       </c>
-      <c r="Q14" s="4"/>
       <c r="R14" s="4"/>
-      <c r="S14" s="4" t="s">
-        <v>107</v>
+      <c r="S14" s="4"/>
+      <c r="T14" s="4" t="s">
+        <v>105</v>
       </c>
     </row>
-    <row r="15" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A15" s="4">
         <v>21402</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>108</v>
+        <v>131</v>
       </c>
       <c r="E15" s="4" t="s">
-        <v>120</v>
-      </c>
-      <c r="F15" s="4">
-        <v>100</v>
+        <v>132</v>
+      </c>
+      <c r="F15" s="4" t="s">
+        <v>117</v>
       </c>
       <c r="G15" s="4">
         <v>10</v>
       </c>
-      <c r="H15" s="4"/>
-      <c r="I15" s="6"/>
+      <c r="H15" s="4">
+        <v>5</v>
+      </c>
+      <c r="I15" s="4"/>
       <c r="J15" s="6"/>
       <c r="K15" s="6"/>
       <c r="L15" s="6"/>
-      <c r="M15" s="6"/>
-      <c r="N15" s="4" t="s">
+      <c r="M15" s="6" t="s">
+        <v>133</v>
+      </c>
+      <c r="N15" s="6" t="s">
+        <v>134</v>
+      </c>
+      <c r="O15" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="O15" s="4"/>
-      <c r="P15" s="4">
+      <c r="P15" s="4"/>
+      <c r="Q15" s="4">
         <v>3</v>
       </c>
-      <c r="Q15" s="4">
+      <c r="R15" s="4">
         <v>12</v>
       </c>
-      <c r="R15" s="4"/>
-      <c r="S15" s="4" t="s">
-        <v>107</v>
+      <c r="S15" s="4"/>
+      <c r="T15" s="4" t="s">
+        <v>105</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:S13">
-    <sortState ref="A5:R13">
+  <autoFilter ref="A4:T13">
+    <sortState ref="A5:T15">
       <sortCondition ref="A4:A13"/>
     </sortState>
   </autoFilter>

--- a/Design/config/CityDevConfig.xlsx
+++ b/Design/config/CityDevConfig.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="181" uniqueCount="135">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="205" uniqueCount="146">
   <si>
     <t>序列</t>
     <phoneticPr fontId="3" type="noConversion"/>
@@ -110,10 +110,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>发展商业</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>图片</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -158,14 +154,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>发展农业,提升粮食产量</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>发展商业,提升金钱收入</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>提升城防</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -174,10 +162,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>Wall</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>wall</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -202,14 +186,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>Gold</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Power</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>训练</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -230,10 +206,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>Soldier</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>征兵</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -417,10 +389,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>Food</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>登用</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -513,10 +481,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>发展农业</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>DevAttr1</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -558,6 +522,85 @@
   </si>
   <si>
     <t>1,5</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>food</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>gold</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>soldier</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>power</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>stone</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>采石场</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>提升石料</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>horse</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>马场</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>提升马场</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>wood</t>
+  </si>
+  <si>
+    <t>木材场</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>提升木材</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>steel</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>铁匠铺</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>提升铁</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>农田</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>提升粮食产量</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>提升金钱收入</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>市场</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -956,7 +999,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AP15"/>
+  <dimension ref="A1:AP19"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9.5" bestFit="1" customWidth="1"/>
@@ -979,55 +1022,55 @@
         <v>10</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>130</v>
+        <v>121</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>67</v>
+        <v>60</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="H1" s="3" t="s">
-        <v>69</v>
+        <v>62</v>
       </c>
       <c r="I1" s="3" t="s">
         <v>14</v>
       </c>
       <c r="J1" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="K1" s="3" t="s">
         <v>14</v>
       </c>
       <c r="L1" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="M1" s="3" t="s">
         <v>14</v>
       </c>
       <c r="N1" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="O1" s="3" t="s">
         <v>14</v>
       </c>
       <c r="P1" s="3" t="s">
-        <v>93</v>
+        <v>86</v>
       </c>
       <c r="Q1" s="3" t="s">
-        <v>113</v>
+        <v>105</v>
       </c>
       <c r="R1" s="3" t="s">
-        <v>109</v>
+        <v>101</v>
       </c>
       <c r="S1" s="3" t="s">
-        <v>109</v>
+        <v>101</v>
       </c>
       <c r="T1" s="3" t="s">
         <v>11</v>
@@ -1041,55 +1084,55 @@
         <v>9</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>127</v>
+        <v>118</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>62</v>
+        <v>55</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>118</v>
+        <v>110</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>124</v>
+        <v>115</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="K2" s="2" t="s">
-        <v>57</v>
+        <v>50</v>
       </c>
       <c r="L2" s="2" t="s">
-        <v>58</v>
+        <v>51</v>
       </c>
       <c r="M2" s="2" t="s">
-        <v>125</v>
+        <v>116</v>
       </c>
       <c r="N2" s="2" t="s">
-        <v>126</v>
+        <v>117</v>
       </c>
       <c r="O2" s="2" t="s">
         <v>15</v>
       </c>
       <c r="P2" s="2" t="s">
-        <v>89</v>
+        <v>82</v>
       </c>
       <c r="Q2" s="2" t="s">
-        <v>112</v>
+        <v>104</v>
       </c>
       <c r="R2" s="2" t="s">
-        <v>110</v>
+        <v>102</v>
       </c>
       <c r="S2" s="2" t="s">
-        <v>115</v>
+        <v>107</v>
       </c>
       <c r="T2" s="2" t="s">
         <v>12</v>
@@ -1106,52 +1149,52 @@
         <v>21</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>128</v>
+        <v>119</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>63</v>
+        <v>56</v>
       </c>
       <c r="F3" s="2" t="s">
         <v>3</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>71</v>
+        <v>64</v>
       </c>
       <c r="I3" s="2" t="s">
         <v>3</v>
       </c>
       <c r="J3" s="2" t="s">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="K3" s="2" t="s">
         <v>3</v>
       </c>
       <c r="L3" s="2" t="s">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="M3" s="2" t="s">
         <v>3</v>
       </c>
       <c r="N3" s="2" t="s">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="O3" s="2" t="s">
         <v>16</v>
       </c>
       <c r="P3" s="2" t="s">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="Q3" s="2" t="s">
-        <v>111</v>
+        <v>103</v>
       </c>
       <c r="R3" s="2" t="s">
-        <v>111</v>
+        <v>103</v>
       </c>
       <c r="S3" s="2" t="s">
-        <v>111</v>
+        <v>103</v>
       </c>
       <c r="T3" s="2" t="s">
         <v>13</v>
@@ -1165,28 +1208,28 @@
         <v>5</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>129</v>
+        <v>120</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="F4" s="2" t="s">
         <v>4</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>72</v>
+        <v>65</v>
       </c>
       <c r="I4" s="2" t="s">
         <v>4</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="K4" s="2" t="s">
         <v>4</v>
@@ -1204,16 +1247,16 @@
         <v>17</v>
       </c>
       <c r="P4" s="2" t="s">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="Q4" s="2" t="s">
-        <v>114</v>
+        <v>106</v>
       </c>
       <c r="R4" s="2" t="s">
-        <v>108</v>
+        <v>100</v>
       </c>
       <c r="S4" s="2" t="s">
-        <v>108</v>
+        <v>100</v>
       </c>
       <c r="T4" s="2" t="s">
         <v>8</v>
@@ -1224,16 +1267,16 @@
         <v>21001</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>123</v>
+        <v>142</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>34</v>
+        <v>143</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>131</v>
+        <v>122</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>65</v>
+        <v>58</v>
       </c>
       <c r="F5" s="4" t="s">
         <v>20</v>
@@ -1245,16 +1288,16 @@
         <v>3</v>
       </c>
       <c r="I5" s="4" t="s">
-        <v>99</v>
+        <v>126</v>
       </c>
       <c r="J5" s="6" t="s">
-        <v>121</v>
+        <v>113</v>
       </c>
       <c r="K5" s="6" t="s">
-        <v>120</v>
+        <v>112</v>
       </c>
       <c r="L5" s="6" t="s">
-        <v>122</v>
+        <v>114</v>
       </c>
       <c r="M5" s="6"/>
       <c r="N5" s="6"/>
@@ -1262,7 +1305,7 @@
         <v>18</v>
       </c>
       <c r="P5" s="4" t="s">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="Q5" s="4">
         <v>11</v>
@@ -1270,7 +1313,7 @@
       <c r="R5" s="4"/>
       <c r="S5" s="4"/>
       <c r="T5" s="4" t="s">
-        <v>90</v>
+        <v>83</v>
       </c>
     </row>
     <row r="6" spans="1:42" x14ac:dyDescent="0.2">
@@ -1278,19 +1321,19 @@
         <v>21002</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>22</v>
+        <v>145</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>35</v>
+        <v>144</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>131</v>
+        <v>122</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>65</v>
+        <v>58</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G6" s="4">
         <v>0</v>
@@ -1299,16 +1342,16 @@
         <v>3</v>
       </c>
       <c r="I6" s="4" t="s">
-        <v>45</v>
+        <v>127</v>
       </c>
       <c r="J6" s="6" t="s">
-        <v>121</v>
+        <v>113</v>
       </c>
       <c r="K6" s="6" t="s">
-        <v>120</v>
+        <v>112</v>
       </c>
       <c r="L6" s="6" t="s">
-        <v>122</v>
+        <v>114</v>
       </c>
       <c r="M6" s="6"/>
       <c r="N6" s="6"/>
@@ -1316,7 +1359,7 @@
         <v>19</v>
       </c>
       <c r="P6" s="4" t="s">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="Q6" s="4">
         <v>10</v>
@@ -1324,7 +1367,7 @@
       <c r="R6" s="4"/>
       <c r="S6" s="4"/>
       <c r="T6" s="4" t="s">
-        <v>81</v>
+        <v>74</v>
       </c>
     </row>
     <row r="7" spans="1:42" x14ac:dyDescent="0.2">
@@ -1332,19 +1375,19 @@
         <v>21003</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>53</v>
+        <v>46</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>54</v>
+        <v>47</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>131</v>
+        <v>122</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>65</v>
+        <v>58</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="G7" s="4">
         <v>10</v>
@@ -1353,24 +1396,24 @@
         <v>3</v>
       </c>
       <c r="I7" s="4" t="s">
-        <v>52</v>
+        <v>128</v>
       </c>
       <c r="J7" s="6" t="s">
-        <v>121</v>
+        <v>113</v>
       </c>
       <c r="K7" s="6" t="s">
-        <v>120</v>
+        <v>112</v>
       </c>
       <c r="L7" s="6" t="s">
-        <v>122</v>
+        <v>114</v>
       </c>
       <c r="M7" s="6"/>
       <c r="N7" s="6"/>
       <c r="O7" s="4" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="P7" s="4" t="s">
-        <v>88</v>
+        <v>81</v>
       </c>
       <c r="Q7" s="4"/>
       <c r="R7" s="4">
@@ -1380,7 +1423,7 @@
         <v>2</v>
       </c>
       <c r="T7" s="4" t="s">
-        <v>78</v>
+        <v>71</v>
       </c>
       <c r="AO7" s="5"/>
       <c r="AP7" s="5"/>
@@ -1390,19 +1433,19 @@
         <v>21004</v>
       </c>
       <c r="B8" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="C8" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="C8" s="4" t="s">
-        <v>36</v>
-      </c>
       <c r="D8" s="4" t="s">
-        <v>131</v>
+        <v>122</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>65</v>
+        <v>58</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="G8" s="4">
         <v>10</v>
@@ -1411,24 +1454,24 @@
         <v>3</v>
       </c>
       <c r="I8" s="4" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="J8" s="6" t="s">
-        <v>121</v>
+        <v>113</v>
       </c>
       <c r="K8" s="6" t="s">
-        <v>120</v>
+        <v>112</v>
       </c>
       <c r="L8" s="6" t="s">
-        <v>122</v>
+        <v>114</v>
       </c>
       <c r="M8" s="6"/>
       <c r="N8" s="6"/>
       <c r="O8" s="4" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="P8" s="4" t="s">
-        <v>86</v>
+        <v>79</v>
       </c>
       <c r="Q8" s="4">
         <v>30</v>
@@ -1438,7 +1481,7 @@
         <v>10</v>
       </c>
       <c r="T8" s="4" t="s">
-        <v>98</v>
+        <v>91</v>
       </c>
       <c r="AO8" s="5"/>
       <c r="AP8" s="5"/>
@@ -1448,19 +1491,19 @@
         <v>21005</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>131</v>
+        <v>122</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>65</v>
+        <v>58</v>
       </c>
       <c r="F9" s="4" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="G9" s="4">
         <v>0</v>
@@ -1469,20 +1512,20 @@
         <v>3</v>
       </c>
       <c r="I9" s="4" t="s">
-        <v>46</v>
+        <v>129</v>
       </c>
       <c r="J9" s="6" t="s">
-        <v>59</v>
+        <v>52</v>
       </c>
       <c r="K9" s="6"/>
       <c r="L9" s="6"/>
       <c r="M9" s="6"/>
       <c r="N9" s="6"/>
       <c r="O9" s="4" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="P9" s="4" t="s">
-        <v>88</v>
+        <v>81</v>
       </c>
       <c r="Q9" s="4"/>
       <c r="R9" s="4">
@@ -1492,7 +1535,7 @@
         <v>3</v>
       </c>
       <c r="T9" s="4" t="s">
-        <v>79</v>
+        <v>72</v>
       </c>
     </row>
     <row r="10" spans="1:42" x14ac:dyDescent="0.2">
@@ -1500,17 +1543,17 @@
         <v>21102</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>74</v>
+        <v>67</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="D10" s="4"/>
       <c r="E10" s="4" t="s">
-        <v>116</v>
+        <v>108</v>
       </c>
       <c r="F10" s="4" t="s">
-        <v>75</v>
+        <v>68</v>
       </c>
       <c r="G10" s="4">
         <v>0</v>
@@ -1525,7 +1568,7 @@
       <c r="M10" s="6"/>
       <c r="N10" s="6"/>
       <c r="O10" s="4" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="P10" s="4"/>
       <c r="Q10" s="4">
@@ -1538,7 +1581,7 @@
         <v>9</v>
       </c>
       <c r="T10" s="4" t="s">
-        <v>76</v>
+        <v>69</v>
       </c>
     </row>
     <row r="11" spans="1:42" x14ac:dyDescent="0.2">
@@ -1546,17 +1589,17 @@
         <v>21103</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>60</v>
+        <v>53</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>61</v>
+        <v>54</v>
       </c>
       <c r="D11" s="4"/>
       <c r="E11" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="F11" s="4" t="s">
         <v>66</v>
-      </c>
-      <c r="F11" s="4" t="s">
-        <v>73</v>
       </c>
       <c r="G11" s="4">
         <v>0</v>
@@ -1571,7 +1614,7 @@
       <c r="M11" s="6"/>
       <c r="N11" s="6"/>
       <c r="O11" s="4" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="P11" s="4"/>
       <c r="Q11" s="4"/>
@@ -1580,7 +1623,7 @@
       </c>
       <c r="S11" s="4"/>
       <c r="T11" s="4" t="s">
-        <v>77</v>
+        <v>70</v>
       </c>
     </row>
     <row r="12" spans="1:42" x14ac:dyDescent="0.2">
@@ -1588,19 +1631,19 @@
         <v>21202</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>131</v>
+        <v>122</v>
       </c>
       <c r="E12" s="4" t="s">
-        <v>65</v>
+        <v>58</v>
       </c>
       <c r="F12" s="4" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="G12" s="4">
         <v>0</v>
@@ -1609,20 +1652,20 @@
         <v>10</v>
       </c>
       <c r="I12" s="4" t="s">
-        <v>45</v>
+        <v>127</v>
       </c>
       <c r="J12" s="6" t="s">
-        <v>119</v>
+        <v>111</v>
       </c>
       <c r="K12" s="6"/>
       <c r="L12" s="6"/>
       <c r="M12" s="6"/>
       <c r="N12" s="6"/>
       <c r="O12" s="4" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="P12" s="4" t="s">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="Q12" s="4">
         <v>21</v>
@@ -1632,7 +1675,7 @@
         <v>11</v>
       </c>
       <c r="T12" s="4" t="s">
-        <v>80</v>
+        <v>73</v>
       </c>
     </row>
     <row r="13" spans="1:42" x14ac:dyDescent="0.2">
@@ -1640,17 +1683,17 @@
         <v>21203</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>95</v>
+        <v>88</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>92</v>
+        <v>85</v>
       </c>
       <c r="D13" s="4"/>
       <c r="E13" s="4" t="s">
-        <v>91</v>
+        <v>84</v>
       </c>
       <c r="F13" s="4" t="s">
-        <v>96</v>
+        <v>89</v>
       </c>
       <c r="G13" s="4">
         <v>0</v>
@@ -1665,7 +1708,7 @@
       <c r="M13" s="6"/>
       <c r="N13" s="6"/>
       <c r="O13" s="4" t="s">
-        <v>94</v>
+        <v>87</v>
       </c>
       <c r="P13" s="4"/>
       <c r="Q13" s="4">
@@ -1678,7 +1721,7 @@
         <v>1</v>
       </c>
       <c r="T13" s="4" t="s">
-        <v>97</v>
+        <v>90</v>
       </c>
     </row>
     <row r="14" spans="1:42" x14ac:dyDescent="0.2">
@@ -1686,17 +1729,17 @@
         <v>21401</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>100</v>
+        <v>92</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>101</v>
+        <v>93</v>
       </c>
       <c r="D14" s="4"/>
       <c r="E14" s="4" t="s">
-        <v>102</v>
+        <v>94</v>
       </c>
       <c r="F14" s="4" t="s">
-        <v>103</v>
+        <v>95</v>
       </c>
       <c r="G14" s="4">
         <v>0</v>
@@ -1711,7 +1754,7 @@
       <c r="M14" s="6"/>
       <c r="N14" s="6"/>
       <c r="O14" s="4" t="s">
-        <v>104</v>
+        <v>96</v>
       </c>
       <c r="P14" s="4"/>
       <c r="Q14" s="4">
@@ -1720,7 +1763,7 @@
       <c r="R14" s="4"/>
       <c r="S14" s="4"/>
       <c r="T14" s="4" t="s">
-        <v>105</v>
+        <v>97</v>
       </c>
     </row>
     <row r="15" spans="1:42" x14ac:dyDescent="0.2">
@@ -1728,19 +1771,19 @@
         <v>21402</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>106</v>
+        <v>98</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>107</v>
+        <v>99</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>131</v>
+        <v>122</v>
       </c>
       <c r="E15" s="4" t="s">
-        <v>132</v>
+        <v>123</v>
       </c>
       <c r="F15" s="4" t="s">
-        <v>117</v>
+        <v>109</v>
       </c>
       <c r="G15" s="4">
         <v>10</v>
@@ -1753,13 +1796,13 @@
       <c r="K15" s="6"/>
       <c r="L15" s="6"/>
       <c r="M15" s="6" t="s">
-        <v>133</v>
+        <v>124</v>
       </c>
       <c r="N15" s="6" t="s">
-        <v>134</v>
+        <v>125</v>
       </c>
       <c r="O15" s="4" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="P15" s="4"/>
       <c r="Q15" s="4">
@@ -1770,7 +1813,167 @@
       </c>
       <c r="S15" s="4"/>
       <c r="T15" s="4" t="s">
-        <v>105</v>
+        <v>97</v>
+      </c>
+    </row>
+    <row r="16" spans="1:42" x14ac:dyDescent="0.2">
+      <c r="A16" s="4">
+        <v>21403</v>
+      </c>
+      <c r="B16" s="4" t="s">
+        <v>131</v>
+      </c>
+      <c r="C16" s="4" t="s">
+        <v>132</v>
+      </c>
+      <c r="D16" s="4" t="s">
+        <v>122</v>
+      </c>
+      <c r="E16" s="4"/>
+      <c r="F16" s="4" t="s">
+        <v>130</v>
+      </c>
+      <c r="G16" s="4">
+        <v>0</v>
+      </c>
+      <c r="H16" s="4">
+        <v>1</v>
+      </c>
+      <c r="I16" s="4"/>
+      <c r="J16" s="6"/>
+      <c r="K16" s="6"/>
+      <c r="L16" s="6"/>
+      <c r="M16" s="6"/>
+      <c r="N16" s="6"/>
+      <c r="O16" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="P16" s="4"/>
+      <c r="Q16" s="4"/>
+      <c r="R16" s="4"/>
+      <c r="S16" s="4"/>
+      <c r="T16" s="4" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="17" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="A17" s="4">
+        <v>21404</v>
+      </c>
+      <c r="B17" s="4" t="s">
+        <v>134</v>
+      </c>
+      <c r="C17" s="4" t="s">
+        <v>135</v>
+      </c>
+      <c r="D17" s="4" t="s">
+        <v>122</v>
+      </c>
+      <c r="E17" s="4"/>
+      <c r="F17" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="G17" s="4">
+        <v>0</v>
+      </c>
+      <c r="H17" s="4">
+        <v>1</v>
+      </c>
+      <c r="I17" s="4"/>
+      <c r="J17" s="6"/>
+      <c r="K17" s="6"/>
+      <c r="L17" s="6"/>
+      <c r="M17" s="6"/>
+      <c r="N17" s="6"/>
+      <c r="O17" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="P17" s="4"/>
+      <c r="Q17" s="4"/>
+      <c r="R17" s="4"/>
+      <c r="S17" s="4"/>
+      <c r="T17" s="4" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="18" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="A18" s="4">
+        <v>21405</v>
+      </c>
+      <c r="B18" s="4" t="s">
+        <v>137</v>
+      </c>
+      <c r="C18" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="D18" s="4" t="s">
+        <v>122</v>
+      </c>
+      <c r="E18" s="4"/>
+      <c r="F18" s="4" t="s">
+        <v>136</v>
+      </c>
+      <c r="G18" s="4">
+        <v>0</v>
+      </c>
+      <c r="H18" s="4">
+        <v>1</v>
+      </c>
+      <c r="I18" s="4"/>
+      <c r="J18" s="6"/>
+      <c r="K18" s="6"/>
+      <c r="L18" s="6"/>
+      <c r="M18" s="6"/>
+      <c r="N18" s="6"/>
+      <c r="O18" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="P18" s="4"/>
+      <c r="Q18" s="4"/>
+      <c r="R18" s="4"/>
+      <c r="S18" s="4"/>
+      <c r="T18" s="4" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="19" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="A19" s="4">
+        <v>21406</v>
+      </c>
+      <c r="B19" s="4" t="s">
+        <v>140</v>
+      </c>
+      <c r="C19" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="D19" s="4" t="s">
+        <v>122</v>
+      </c>
+      <c r="E19" s="4"/>
+      <c r="F19" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="G19" s="4">
+        <v>0</v>
+      </c>
+      <c r="H19" s="4">
+        <v>1</v>
+      </c>
+      <c r="I19" s="4"/>
+      <c r="J19" s="6"/>
+      <c r="K19" s="6"/>
+      <c r="L19" s="6"/>
+      <c r="M19" s="6"/>
+      <c r="N19" s="6"/>
+      <c r="O19" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="P19" s="4"/>
+      <c r="Q19" s="4"/>
+      <c r="R19" s="4"/>
+      <c r="S19" s="4"/>
+      <c r="T19" s="4" t="s">
+        <v>97</v>
       </c>
     </row>
   </sheetData>

--- a/Design/config/CityDevConfig.xlsx
+++ b/Design/config/CityDevConfig.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="205" uniqueCount="146">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="213" uniqueCount="151">
   <si>
     <t>序列</t>
     <phoneticPr fontId="3" type="noConversion"/>
@@ -601,6 +601,26 @@
   </si>
   <si>
     <t>市场</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>stone</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>3,3</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>horse</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>wood</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>steel</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -1839,8 +1859,12 @@
       <c r="H16" s="4">
         <v>1</v>
       </c>
-      <c r="I16" s="4"/>
-      <c r="J16" s="6"/>
+      <c r="I16" s="4" t="s">
+        <v>146</v>
+      </c>
+      <c r="J16" s="6" t="s">
+        <v>147</v>
+      </c>
       <c r="K16" s="6"/>
       <c r="L16" s="6"/>
       <c r="M16" s="6"/>
@@ -1879,8 +1903,12 @@
       <c r="H17" s="4">
         <v>1</v>
       </c>
-      <c r="I17" s="4"/>
-      <c r="J17" s="6"/>
+      <c r="I17" s="4" t="s">
+        <v>148</v>
+      </c>
+      <c r="J17" s="6" t="s">
+        <v>147</v>
+      </c>
       <c r="K17" s="6"/>
       <c r="L17" s="6"/>
       <c r="M17" s="6"/>
@@ -1919,8 +1947,12 @@
       <c r="H18" s="4">
         <v>1</v>
       </c>
-      <c r="I18" s="4"/>
-      <c r="J18" s="6"/>
+      <c r="I18" s="4" t="s">
+        <v>149</v>
+      </c>
+      <c r="J18" s="6" t="s">
+        <v>147</v>
+      </c>
       <c r="K18" s="6"/>
       <c r="L18" s="6"/>
       <c r="M18" s="6"/>
@@ -1959,8 +1991,12 @@
       <c r="H19" s="4">
         <v>1</v>
       </c>
-      <c r="I19" s="4"/>
-      <c r="J19" s="6"/>
+      <c r="I19" s="4" t="s">
+        <v>150</v>
+      </c>
+      <c r="J19" s="6" t="s">
+        <v>147</v>
+      </c>
       <c r="K19" s="6"/>
       <c r="L19" s="6"/>
       <c r="M19" s="6"/>

--- a/Design/config/CityDevConfig.xlsx
+++ b/Design/config/CityDevConfig.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="213" uniqueCount="151">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="213" uniqueCount="150">
   <si>
     <t>序列</t>
     <phoneticPr fontId="3" type="noConversion"/>
@@ -230,10 +230,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>3,9</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>出战</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -465,22 +461,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>1,2</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Exp</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>5,10</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>2,5</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>DevAttr1</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -537,10 +517,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>power</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>stone</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -621,6 +597,26 @@
   </si>
   <si>
     <t>steel</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>exp</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>5,5</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>3,3</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>happy</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>2,2</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -1045,19 +1041,19 @@
         <v>27</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>121</v>
+        <v>116</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="F1" s="3" t="s">
         <v>22</v>
       </c>
       <c r="G1" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="H1" s="3" t="s">
         <v>61</v>
-      </c>
-      <c r="H1" s="3" t="s">
-        <v>62</v>
       </c>
       <c r="I1" s="3" t="s">
         <v>14</v>
@@ -1081,16 +1077,16 @@
         <v>14</v>
       </c>
       <c r="P1" s="3" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="Q1" s="3" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="R1" s="3" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="S1" s="3" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="T1" s="3" t="s">
         <v>11</v>
@@ -1107,22 +1103,22 @@
         <v>28</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>118</v>
+        <v>113</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="G2" s="2" t="s">
         <v>24</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>115</v>
+        <v>110</v>
       </c>
       <c r="J2" s="2" t="s">
         <v>48</v>
@@ -1134,25 +1130,25 @@
         <v>51</v>
       </c>
       <c r="M2" s="2" t="s">
-        <v>116</v>
+        <v>111</v>
       </c>
       <c r="N2" s="2" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="O2" s="2" t="s">
         <v>15</v>
       </c>
       <c r="P2" s="2" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="Q2" s="2" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="R2" s="2" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="S2" s="2" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="T2" s="2" t="s">
         <v>12</v>
@@ -1169,10 +1165,10 @@
         <v>21</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="F3" s="2" t="s">
         <v>3</v>
@@ -1181,7 +1177,7 @@
         <v>25</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="I3" s="2" t="s">
         <v>3</v>
@@ -1205,16 +1201,16 @@
         <v>16</v>
       </c>
       <c r="P3" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="Q3" s="2" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="R3" s="2" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="S3" s="2" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="T3" s="2" t="s">
         <v>13</v>
@@ -1231,10 +1227,10 @@
         <v>29</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="F4" s="2" t="s">
         <v>4</v>
@@ -1243,7 +1239,7 @@
         <v>26</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="I4" s="2" t="s">
         <v>4</v>
@@ -1267,16 +1263,16 @@
         <v>17</v>
       </c>
       <c r="P4" s="2" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="Q4" s="2" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="R4" s="2" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="S4" s="2" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="T4" s="2" t="s">
         <v>8</v>
@@ -1287,16 +1283,16 @@
         <v>21001</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>142</v>
+        <v>136</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>143</v>
+        <v>137</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="F5" s="4" t="s">
         <v>20</v>
@@ -1308,16 +1304,16 @@
         <v>3</v>
       </c>
       <c r="I5" s="4" t="s">
-        <v>126</v>
+        <v>121</v>
       </c>
       <c r="J5" s="6" t="s">
-        <v>113</v>
+        <v>146</v>
       </c>
       <c r="K5" s="6" t="s">
-        <v>112</v>
+        <v>145</v>
       </c>
       <c r="L5" s="6" t="s">
-        <v>114</v>
+        <v>149</v>
       </c>
       <c r="M5" s="6"/>
       <c r="N5" s="6"/>
@@ -1325,7 +1321,7 @@
         <v>18</v>
       </c>
       <c r="P5" s="4" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="Q5" s="4">
         <v>11</v>
@@ -1333,7 +1329,7 @@
       <c r="R5" s="4"/>
       <c r="S5" s="4"/>
       <c r="T5" s="4" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="6" spans="1:42" x14ac:dyDescent="0.2">
@@ -1341,16 +1337,16 @@
         <v>21002</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>145</v>
+        <v>139</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>144</v>
+        <v>138</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="F6" s="4" t="s">
         <v>23</v>
@@ -1362,16 +1358,16 @@
         <v>3</v>
       </c>
       <c r="I6" s="4" t="s">
-        <v>127</v>
+        <v>122</v>
       </c>
       <c r="J6" s="6" t="s">
-        <v>113</v>
+        <v>146</v>
       </c>
       <c r="K6" s="6" t="s">
-        <v>112</v>
+        <v>145</v>
       </c>
       <c r="L6" s="6" t="s">
-        <v>114</v>
+        <v>149</v>
       </c>
       <c r="M6" s="6"/>
       <c r="N6" s="6"/>
@@ -1379,7 +1375,7 @@
         <v>19</v>
       </c>
       <c r="P6" s="4" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="Q6" s="4">
         <v>10</v>
@@ -1387,7 +1383,7 @@
       <c r="R6" s="4"/>
       <c r="S6" s="4"/>
       <c r="T6" s="4" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="7" spans="1:42" x14ac:dyDescent="0.2">
@@ -1401,10 +1397,10 @@
         <v>47</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="F7" s="4" t="s">
         <v>44</v>
@@ -1416,16 +1412,16 @@
         <v>3</v>
       </c>
       <c r="I7" s="4" t="s">
-        <v>128</v>
+        <v>123</v>
       </c>
       <c r="J7" s="6" t="s">
-        <v>113</v>
+        <v>146</v>
       </c>
       <c r="K7" s="6" t="s">
-        <v>112</v>
+        <v>145</v>
       </c>
       <c r="L7" s="6" t="s">
-        <v>114</v>
+        <v>149</v>
       </c>
       <c r="M7" s="6"/>
       <c r="N7" s="6"/>
@@ -1433,7 +1429,7 @@
         <v>45</v>
       </c>
       <c r="P7" s="4" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="Q7" s="4"/>
       <c r="R7" s="4">
@@ -1443,7 +1439,7 @@
         <v>2</v>
       </c>
       <c r="T7" s="4" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="AO7" s="5"/>
       <c r="AP7" s="5"/>
@@ -1459,10 +1455,10 @@
         <v>33</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="F8" s="4" t="s">
         <v>35</v>
@@ -1477,13 +1473,13 @@
         <v>35</v>
       </c>
       <c r="J8" s="6" t="s">
-        <v>113</v>
+        <v>146</v>
       </c>
       <c r="K8" s="6" t="s">
-        <v>112</v>
+        <v>145</v>
       </c>
       <c r="L8" s="6" t="s">
-        <v>114</v>
+        <v>149</v>
       </c>
       <c r="M8" s="6"/>
       <c r="N8" s="6"/>
@@ -1491,7 +1487,7 @@
         <v>34</v>
       </c>
       <c r="P8" s="4" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="Q8" s="4">
         <v>30</v>
@@ -1501,7 +1497,7 @@
         <v>10</v>
       </c>
       <c r="T8" s="4" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="AO8" s="5"/>
       <c r="AP8" s="5"/>
@@ -1517,10 +1513,10 @@
         <v>42</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="F9" s="4" t="s">
         <v>43</v>
@@ -1532,10 +1528,10 @@
         <v>3</v>
       </c>
       <c r="I9" s="4" t="s">
-        <v>129</v>
+        <v>148</v>
       </c>
       <c r="J9" s="6" t="s">
-        <v>52</v>
+        <v>147</v>
       </c>
       <c r="K9" s="6"/>
       <c r="L9" s="6"/>
@@ -1545,7 +1541,7 @@
         <v>36</v>
       </c>
       <c r="P9" s="4" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="Q9" s="4"/>
       <c r="R9" s="4">
@@ -1555,7 +1551,7 @@
         <v>3</v>
       </c>
       <c r="T9" s="4" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="10" spans="1:42" x14ac:dyDescent="0.2">
@@ -1563,17 +1559,17 @@
         <v>21102</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D10" s="4"/>
       <c r="E10" s="4" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="F10" s="4" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G10" s="4">
         <v>0</v>
@@ -1601,7 +1597,7 @@
         <v>9</v>
       </c>
       <c r="T10" s="4" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="11" spans="1:42" x14ac:dyDescent="0.2">
@@ -1609,17 +1605,17 @@
         <v>21103</v>
       </c>
       <c r="B11" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="C11" s="4" t="s">
         <v>53</v>
-      </c>
-      <c r="C11" s="4" t="s">
-        <v>54</v>
       </c>
       <c r="D11" s="4"/>
       <c r="E11" s="4" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="F11" s="4" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="G11" s="4">
         <v>0</v>
@@ -1643,7 +1639,7 @@
       </c>
       <c r="S11" s="4"/>
       <c r="T11" s="4" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="12" spans="1:42" x14ac:dyDescent="0.2">
@@ -1657,10 +1653,10 @@
         <v>38</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="E12" s="4" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="F12" s="4" t="s">
         <v>40</v>
@@ -1672,10 +1668,10 @@
         <v>10</v>
       </c>
       <c r="I12" s="4" t="s">
-        <v>127</v>
+        <v>122</v>
       </c>
       <c r="J12" s="6" t="s">
-        <v>111</v>
+        <v>149</v>
       </c>
       <c r="K12" s="6"/>
       <c r="L12" s="6"/>
@@ -1685,7 +1681,7 @@
         <v>39</v>
       </c>
       <c r="P12" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="Q12" s="4">
         <v>21</v>
@@ -1695,7 +1691,7 @@
         <v>11</v>
       </c>
       <c r="T12" s="4" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="13" spans="1:42" x14ac:dyDescent="0.2">
@@ -1703,17 +1699,17 @@
         <v>21203</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D13" s="4"/>
       <c r="E13" s="4" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="F13" s="4" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="G13" s="4">
         <v>0</v>
@@ -1728,7 +1724,7 @@
       <c r="M13" s="6"/>
       <c r="N13" s="6"/>
       <c r="O13" s="4" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="P13" s="4"/>
       <c r="Q13" s="4">
@@ -1741,7 +1737,7 @@
         <v>1</v>
       </c>
       <c r="T13" s="4" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="14" spans="1:42" x14ac:dyDescent="0.2">
@@ -1749,17 +1745,17 @@
         <v>21401</v>
       </c>
       <c r="B14" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="C14" s="4" t="s">
         <v>92</v>
-      </c>
-      <c r="C14" s="4" t="s">
-        <v>93</v>
       </c>
       <c r="D14" s="4"/>
       <c r="E14" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="F14" s="4" t="s">
         <v>94</v>
-      </c>
-      <c r="F14" s="4" t="s">
-        <v>95</v>
       </c>
       <c r="G14" s="4">
         <v>0</v>
@@ -1774,7 +1770,7 @@
       <c r="M14" s="6"/>
       <c r="N14" s="6"/>
       <c r="O14" s="4" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="P14" s="4"/>
       <c r="Q14" s="4">
@@ -1783,7 +1779,7 @@
       <c r="R14" s="4"/>
       <c r="S14" s="4"/>
       <c r="T14" s="4" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="15" spans="1:42" x14ac:dyDescent="0.2">
@@ -1791,19 +1787,19 @@
         <v>21402</v>
       </c>
       <c r="B15" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="C15" s="4" t="s">
         <v>98</v>
       </c>
-      <c r="C15" s="4" t="s">
-        <v>99</v>
-      </c>
       <c r="D15" s="4" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="E15" s="4" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="F15" s="4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="G15" s="4">
         <v>10</v>
@@ -1816,10 +1812,10 @@
       <c r="K15" s="6"/>
       <c r="L15" s="6"/>
       <c r="M15" s="6" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
       <c r="N15" s="6" t="s">
-        <v>125</v>
+        <v>120</v>
       </c>
       <c r="O15" s="4" t="s">
         <v>39</v>
@@ -1833,7 +1829,7 @@
       </c>
       <c r="S15" s="4"/>
       <c r="T15" s="4" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="16" spans="1:42" x14ac:dyDescent="0.2">
@@ -1841,17 +1837,17 @@
         <v>21403</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>131</v>
+        <v>125</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
       <c r="D16" s="4" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="E16" s="4"/>
       <c r="F16" s="4" t="s">
-        <v>130</v>
+        <v>124</v>
       </c>
       <c r="G16" s="4">
         <v>0</v>
@@ -1860,10 +1856,10 @@
         <v>1</v>
       </c>
       <c r="I16" s="4" t="s">
-        <v>146</v>
+        <v>140</v>
       </c>
       <c r="J16" s="6" t="s">
-        <v>147</v>
+        <v>141</v>
       </c>
       <c r="K16" s="6"/>
       <c r="L16" s="6"/>
@@ -1877,7 +1873,7 @@
       <c r="R16" s="4"/>
       <c r="S16" s="4"/>
       <c r="T16" s="4" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="17" spans="1:20" x14ac:dyDescent="0.2">
@@ -1885,17 +1881,17 @@
         <v>21404</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>134</v>
+        <v>128</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>135</v>
+        <v>129</v>
       </c>
       <c r="D17" s="4" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="E17" s="4"/>
       <c r="F17" s="4" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="G17" s="4">
         <v>0</v>
@@ -1904,10 +1900,10 @@
         <v>1</v>
       </c>
       <c r="I17" s="4" t="s">
-        <v>148</v>
+        <v>142</v>
       </c>
       <c r="J17" s="6" t="s">
-        <v>147</v>
+        <v>141</v>
       </c>
       <c r="K17" s="6"/>
       <c r="L17" s="6"/>
@@ -1921,7 +1917,7 @@
       <c r="R17" s="4"/>
       <c r="S17" s="4"/>
       <c r="T17" s="4" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="18" spans="1:20" x14ac:dyDescent="0.2">
@@ -1929,17 +1925,17 @@
         <v>21405</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>137</v>
+        <v>131</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>138</v>
+        <v>132</v>
       </c>
       <c r="D18" s="4" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="E18" s="4"/>
       <c r="F18" s="4" t="s">
-        <v>136</v>
+        <v>130</v>
       </c>
       <c r="G18" s="4">
         <v>0</v>
@@ -1948,10 +1944,10 @@
         <v>1</v>
       </c>
       <c r="I18" s="4" t="s">
-        <v>149</v>
+        <v>143</v>
       </c>
       <c r="J18" s="6" t="s">
-        <v>147</v>
+        <v>141</v>
       </c>
       <c r="K18" s="6"/>
       <c r="L18" s="6"/>
@@ -1965,7 +1961,7 @@
       <c r="R18" s="4"/>
       <c r="S18" s="4"/>
       <c r="T18" s="4" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="19" spans="1:20" x14ac:dyDescent="0.2">
@@ -1973,17 +1969,17 @@
         <v>21406</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>140</v>
+        <v>134</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>141</v>
+        <v>135</v>
       </c>
       <c r="D19" s="4" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="E19" s="4"/>
       <c r="F19" s="4" t="s">
-        <v>139</v>
+        <v>133</v>
       </c>
       <c r="G19" s="4">
         <v>0</v>
@@ -1992,10 +1988,10 @@
         <v>1</v>
       </c>
       <c r="I19" s="4" t="s">
-        <v>150</v>
+        <v>144</v>
       </c>
       <c r="J19" s="6" t="s">
-        <v>147</v>
+        <v>141</v>
       </c>
       <c r="K19" s="6"/>
       <c r="L19" s="6"/>
@@ -2009,7 +2005,7 @@
       <c r="R19" s="4"/>
       <c r="S19" s="4"/>
       <c r="T19" s="4" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
   </sheetData>

--- a/Design/config/CityDevConfig.xlsx
+++ b/Design/config/CityDevConfig.xlsx
@@ -1301,7 +1301,7 @@
         <v>0</v>
       </c>
       <c r="H5" s="4">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I5" s="4" t="s">
         <v>121</v>
@@ -1355,7 +1355,7 @@
         <v>0</v>
       </c>
       <c r="H6" s="4">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I6" s="4" t="s">
         <v>122</v>
@@ -1409,7 +1409,7 @@
         <v>10</v>
       </c>
       <c r="H7" s="4">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I7" s="4" t="s">
         <v>123</v>
@@ -1467,7 +1467,7 @@
         <v>10</v>
       </c>
       <c r="H8" s="4">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I8" s="4" t="s">
         <v>35</v>
@@ -1525,7 +1525,7 @@
         <v>0</v>
       </c>
       <c r="H9" s="4">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I9" s="4" t="s">
         <v>148</v>
@@ -1665,7 +1665,7 @@
         <v>0</v>
       </c>
       <c r="H12" s="4">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="I12" s="4" t="s">
         <v>122</v>

--- a/Design/config/CityDevConfig.xlsx
+++ b/Design/config/CityDevConfig.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="213" uniqueCount="150">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="213" uniqueCount="149">
   <si>
     <t>序列</t>
     <phoneticPr fontId="3" type="noConversion"/>
@@ -584,10 +584,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>3,3</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>horse</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -604,19 +600,19 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>5,5</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>3,3</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>happy</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>2,2</t>
+    <t>float[]</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>3,2.7,2.3,2</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>1,0.8,0.6,0.5</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -1183,13 +1179,13 @@
         <v>3</v>
       </c>
       <c r="J3" s="2" t="s">
-        <v>49</v>
+        <v>146</v>
       </c>
       <c r="K3" s="2" t="s">
         <v>3</v>
       </c>
       <c r="L3" s="2" t="s">
-        <v>49</v>
+        <v>146</v>
       </c>
       <c r="M3" s="2" t="s">
         <v>3</v>
@@ -1307,13 +1303,13 @@
         <v>121</v>
       </c>
       <c r="J5" s="6" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="K5" s="6" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="L5" s="6" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="M5" s="6"/>
       <c r="N5" s="6"/>
@@ -1361,13 +1357,13 @@
         <v>122</v>
       </c>
       <c r="J6" s="6" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="K6" s="6" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="L6" s="6" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="M6" s="6"/>
       <c r="N6" s="6"/>
@@ -1415,13 +1411,13 @@
         <v>123</v>
       </c>
       <c r="J7" s="6" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="K7" s="6" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="L7" s="6" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="M7" s="6"/>
       <c r="N7" s="6"/>
@@ -1473,13 +1469,13 @@
         <v>35</v>
       </c>
       <c r="J8" s="6" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="K8" s="6" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="L8" s="6" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="M8" s="6"/>
       <c r="N8" s="6"/>
@@ -1528,7 +1524,7 @@
         <v>1</v>
       </c>
       <c r="I9" s="4" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="J9" s="6" t="s">
         <v>147</v>
@@ -1671,7 +1667,7 @@
         <v>122</v>
       </c>
       <c r="J12" s="6" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="K12" s="6"/>
       <c r="L12" s="6"/>
@@ -1859,7 +1855,7 @@
         <v>140</v>
       </c>
       <c r="J16" s="6" t="s">
-        <v>141</v>
+        <v>147</v>
       </c>
       <c r="K16" s="6"/>
       <c r="L16" s="6"/>
@@ -1900,10 +1896,10 @@
         <v>1</v>
       </c>
       <c r="I17" s="4" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="J17" s="6" t="s">
-        <v>141</v>
+        <v>147</v>
       </c>
       <c r="K17" s="6"/>
       <c r="L17" s="6"/>
@@ -1944,10 +1940,10 @@
         <v>1</v>
       </c>
       <c r="I18" s="4" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="J18" s="6" t="s">
-        <v>141</v>
+        <v>147</v>
       </c>
       <c r="K18" s="6"/>
       <c r="L18" s="6"/>
@@ -1988,10 +1984,10 @@
         <v>1</v>
       </c>
       <c r="I19" s="4" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="J19" s="6" t="s">
-        <v>141</v>
+        <v>147</v>
       </c>
       <c r="K19" s="6"/>
       <c r="L19" s="6"/>
